--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3685FB-2D2A-4527-986C-2DE440732FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091A7014-DF7E-4517-BB03-A0C9DE3A111B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="3" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="8" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="50">
   <si>
     <t>Booking</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>Yasir</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -25287,7 +25290,7 @@
     <col min="7" max="9" width="5.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
@@ -25573,29 +25576,45 @@
       <c r="N8" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>40</v>
+      </c>
+      <c r="P8" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>100</v>
+      </c>
+      <c r="T8" s="11">
+        <v>100</v>
+      </c>
+      <c r="U8" s="11">
+        <v>120</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="W8" s="12">
+        <v>19</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -25620,29 +25639,45 @@
       <c r="N9" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>72</v>
+      </c>
+      <c r="P9" s="11">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>27</v>
+      </c>
+      <c r="R9" s="11">
+        <v>133</v>
+      </c>
+      <c r="S9" s="11">
+        <v>79</v>
+      </c>
+      <c r="T9" s="11">
+        <v>12</v>
+      </c>
+      <c r="U9" s="11">
+        <v>101</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>12.725</v>
+      </c>
+      <c r="W9" s="12">
+        <v>16</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>12.725</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>-12.725</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -25667,29 +25702,45 @@
       <c r="N10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>132</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>5</v>
+      </c>
+      <c r="T10" s="11">
+        <v>16</v>
+      </c>
+      <c r="U10" s="11">
+        <v>45</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>4.95</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -25714,29 +25765,45 @@
       <c r="N11" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>92</v>
+      </c>
+      <c r="P11" s="11">
+        <v>55</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>50</v>
+      </c>
+      <c r="R11" s="11">
+        <v>55</v>
+      </c>
+      <c r="S11" s="11">
+        <v>183</v>
+      </c>
+      <c r="T11" s="11">
+        <v>173</v>
+      </c>
+      <c r="U11" s="11">
+        <v>186</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>19.850000000000001</v>
+      </c>
+      <c r="W11" s="12">
+        <v>17</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-19.850000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -25761,29 +25828,45 @@
       <c r="N12" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>100</v>
+      </c>
+      <c r="P12" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>58</v>
+      </c>
+      <c r="R12" s="11">
+        <v>52</v>
+      </c>
+      <c r="S12" s="11">
+        <v>86</v>
+      </c>
+      <c r="T12" s="11">
+        <v>40</v>
+      </c>
+      <c r="U12" s="11">
+        <v>78</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>11.35</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11.35</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-11.35</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -25812,12 +25895,18 @@
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="S13" s="11">
+        <v>40</v>
+      </c>
+      <c r="T13" s="11">
+        <v>40</v>
+      </c>
+      <c r="U13" s="11">
+        <v>40</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
@@ -26016,35 +26105,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>2475</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -26053,11 +26142,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>58.875000000000007</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>-58.875000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26105,35 +26194,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.375</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12.324999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.5250000000000004</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>61.875</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -26142,11 +26231,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.4718750000000003</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>-1.4718750000000003</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
@@ -26448,13 +26537,13 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="70">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
@@ -26465,13 +26554,13 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
       <c r="V8" s="70">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
@@ -26495,13 +26584,13 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="70">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
@@ -26512,13 +26601,13 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
       <c r="V9" s="70">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
@@ -26542,13 +26631,13 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -26559,13 +26648,13 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
       <c r="V10" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -26589,13 +26678,13 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -26606,13 +26695,13 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
       <c r="V11" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -26636,13 +26725,13 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -26655,13 +26744,13 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
       <c r="V12" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -26685,13 +26774,13 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
       <c r="J13" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -26702,13 +26791,13 @@
       <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
       <c r="V13" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -26723,13 +26812,13 @@
       <c r="B14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
       <c r="J14" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -26740,13 +26829,13 @@
       <c r="N14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
       <c r="V14" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -26761,13 +26850,13 @@
       <c r="B15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
       <c r="J15" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -26778,13 +26867,13 @@
       <c r="N15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
       <c r="V15" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -26799,13 +26888,13 @@
       <c r="B16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -26816,13 +26905,13 @@
       <c r="N16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
       <c r="V16" s="70">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -26835,37 +26924,29 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
       <c r="J17" s="70"/>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="11">
-        <v>1600</v>
-      </c>
+      <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
-      <c r="S17" s="11">
-        <v>600</v>
-      </c>
-      <c r="T17" s="11">
-        <v>800</v>
-      </c>
-      <c r="U17" s="11">
-        <v>1000</v>
-      </c>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="70">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W17" s="12">
         <v>1</v>
@@ -26876,11 +26957,11 @@
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -26923,7 +27004,7 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -26939,19 +27020,19 @@
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -26960,11 +27041,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27011,7 +27092,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -27027,19 +27108,19 @@
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V19" s="69">
         <f t="shared" si="8"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -27048,11 +27129,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-2.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27090,7 +27171,7 @@
     <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -27339,45 +27420,73 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>120</v>
+      </c>
+      <c r="H8" s="11">
+        <v>80</v>
+      </c>
+      <c r="I8" s="11">
+        <v>120</v>
+      </c>
       <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <f>SUM(C8:I8)</f>
+        <v>360</v>
+      </c>
+      <c r="K8" s="12">
+        <v>15</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>40</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>120</v>
+      </c>
+      <c r="T8" s="11">
+        <v>80</v>
+      </c>
+      <c r="U8" s="11">
+        <v>120</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>15</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -27385,42 +27494,74 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>80</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>80</v>
+      </c>
+      <c r="F9" s="11">
+        <v>120</v>
+      </c>
+      <c r="G9" s="11">
+        <v>10</v>
+      </c>
+      <c r="H9" s="11">
+        <v>10</v>
+      </c>
+      <c r="I9" s="11">
+        <v>20</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <v>8</v>
+      </c>
+      <c r="K9" s="12">
+        <v>18</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>80</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>80</v>
+      </c>
+      <c r="R9" s="11">
+        <v>120</v>
+      </c>
+      <c r="S9" s="11">
+        <v>10</v>
+      </c>
+      <c r="T9" s="11">
+        <v>10</v>
+      </c>
+      <c r="U9" s="11">
+        <v>20</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
+        <v>8</v>
+      </c>
+      <c r="W9" s="12">
+        <v>19</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
@@ -27433,45 +27574,74 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>80</v>
+      </c>
+      <c r="F10" s="11">
+        <v>80</v>
+      </c>
+      <c r="G10" s="11">
+        <v>15</v>
+      </c>
+      <c r="H10" s="11">
+        <v>40</v>
+      </c>
+      <c r="I10" s="11">
+        <v>23</v>
+      </c>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K10" s="12">
+        <v>4</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>0</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>80</v>
+      </c>
+      <c r="R10" s="11">
+        <v>80</v>
+      </c>
+      <c r="S10" s="11">
+        <v>15</v>
+      </c>
+      <c r="T10" s="11">
+        <v>30</v>
+      </c>
+      <c r="U10" s="11">
+        <v>13</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>5.45</v>
+      </c>
+      <c r="W10" s="12">
+        <v>3</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.54999999999999982</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -27479,46 +27649,78 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>88</v>
+      </c>
+      <c r="D11" s="11">
+        <v>22</v>
+      </c>
+      <c r="E11" s="11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="11">
+        <v>12</v>
+      </c>
+      <c r="G11" s="11">
+        <v>66</v>
+      </c>
+      <c r="H11" s="11">
+        <v>21</v>
+      </c>
+      <c r="I11" s="11">
+        <v>21</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K11" s="12">
+        <v>13</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>48</v>
+      </c>
+      <c r="P11" s="11">
+        <v>22</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="11">
+        <v>12</v>
+      </c>
+      <c r="S11" s="11">
+        <v>26</v>
+      </c>
+      <c r="T11" s="11">
+        <v>21</v>
+      </c>
+      <c r="U11" s="11">
+        <v>21</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="W11" s="12">
+        <v>9</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -27526,64 +27728,77 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>63</v>
+      </c>
+      <c r="D12" s="11">
+        <v>16</v>
+      </c>
+      <c r="E12" s="11">
+        <v>29</v>
+      </c>
+      <c r="F12" s="11">
+        <v>32</v>
+      </c>
+      <c r="G12" s="11">
+        <v>13</v>
+      </c>
+      <c r="H12" s="11">
+        <v>15</v>
+      </c>
+      <c r="I12" s="11">
+        <v>15</v>
+      </c>
       <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
       <c r="O12" s="11">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="P12" s="11">
-        <f>281-40</f>
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="11">
-        <v>403</v>
+        <v>19</v>
       </c>
       <c r="R12" s="11">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="S12" s="11">
-        <f>383-20</f>
-        <v>363</v>
+        <v>13</v>
       </c>
       <c r="T12" s="11">
-        <f>281-20</f>
-        <v>261</v>
+        <v>15</v>
       </c>
       <c r="U12" s="11">
-        <f>561-20</f>
-        <v>541</v>
+        <v>15</v>
       </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>49.325000000000003</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>3.9750000000000001</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>49.325000000000003</v>
+        <v>3.9750000000000001</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-49.325000000000003</v>
+        <v>1.0249999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -27592,34 +27807,64 @@
         <v>16</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="D13" s="11">
+        <v>360</v>
+      </c>
+      <c r="E13" s="11">
+        <v>240</v>
+      </c>
+      <c r="F13" s="11">
+        <v>200</v>
+      </c>
+      <c r="G13" s="11">
+        <v>400</v>
+      </c>
+      <c r="H13" s="11">
+        <v>360</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1280</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>71</v>
+      </c>
+      <c r="K13" s="12">
+        <v>6</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="O13" s="11">
+        <v>385</v>
+      </c>
+      <c r="P13" s="11">
+        <v>400</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>320</v>
+      </c>
+      <c r="R13" s="11">
+        <v>280</v>
+      </c>
+      <c r="S13" s="11">
+        <v>320</v>
+      </c>
+      <c r="T13" s="11">
+        <v>320</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1200</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>80.625</v>
+      </c>
+      <c r="W13" s="12">
+        <v>6</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -27637,10 +27882,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="K14" s="12">
+        <v>10</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -27675,10 +27921,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="K15" s="12">
+        <v>12</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -27713,10 +27960,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K16" s="12">
+        <v>4</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -27751,27 +27999,42 @@
       <c r="J17" s="15"/>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="11"/>
+      <c r="N17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="O17" s="11">
+        <v>1600</v>
+      </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="18"/>
+      <c r="S17" s="11">
+        <v>600</v>
+      </c>
+      <c r="T17" s="11">
+        <v>1000</v>
+      </c>
+      <c r="U17" s="11">
+        <v>800</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="W17" s="18">
+        <v>1</v>
+      </c>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -27779,83 +28042,83 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1479</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>4181</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
-        <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>3</v>
+        <f>SUM(O8:O16)</f>
+        <v>568</v>
       </c>
       <c r="P18" s="25">
-        <f t="shared" si="6"/>
-        <v>241</v>
+        <f t="shared" ref="P18:U18" si="6">SUM(P8:P16)</f>
+        <v>438</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>403</v>
+        <v>549</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>161</v>
+        <v>518</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>363</v>
+        <v>504</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>541</v>
+        <v>1389</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1973</v>
+        <v>4442</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>49.325000000000003</v>
+        <v>130.42500000000001</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-49.325000000000003</v>
+        <v>254.57499999999999</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27864,36 +28127,36 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <f t="shared" ref="C19:I19" si="7">C18/40</f>
+        <v>5.7750000000000004</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11.975</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.15</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>36.975000000000001</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>SUM(J8:J16)</f>
+        <v>493</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -27902,48 +28165,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>7.4999999999999997E-2</v>
+        <v>14.2</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>6.0250000000000004</v>
+        <v>10.95</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>10.074999999999999</v>
+        <v>13.725</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>4.0250000000000004</v>
+        <v>12.95</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>9.0749999999999993</v>
+        <v>12.6</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>6.5250000000000004</v>
+        <v>11.9</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>13.525</v>
+        <v>34.725000000000001</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>49.325000000000003</v>
+        <v>111.05</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>9.625</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>1.233125</v>
+        <v>3.2606250000000001</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-1.233125</v>
+        <v>6.3643749999999999</v>
       </c>
     </row>
   </sheetData>
@@ -28228,46 +28491,78 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>200</v>
+      </c>
+      <c r="D8" s="11">
+        <v>40</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>20</v>
+      </c>
+      <c r="H8" s="11">
+        <v>15</v>
+      </c>
+      <c r="I8" s="11">
+        <v>25</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>7.5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>12</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>120</v>
+      </c>
+      <c r="P8" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>20</v>
+      </c>
+      <c r="T8" s="11">
+        <v>15</v>
+      </c>
+      <c r="U8" s="11">
+        <v>20</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>5.375</v>
+      </c>
+      <c r="W8" s="12">
+        <v>11</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>5.375</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -28275,46 +28570,76 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>40</v>
+      </c>
+      <c r="D9" s="11">
+        <v>45</v>
+      </c>
+      <c r="E9" s="11">
+        <v>30</v>
+      </c>
+      <c r="F9" s="11">
+        <v>10</v>
+      </c>
+      <c r="G9" s="11">
+        <v>142</v>
+      </c>
+      <c r="H9" s="11">
+        <v>71</v>
+      </c>
+      <c r="I9" s="11">
+        <v>111</v>
+      </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
+        <v>11.225</v>
+      </c>
+      <c r="K9" s="12">
+        <v>15</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>6</v>
+      </c>
+      <c r="R9" s="11">
+        <v>9</v>
+      </c>
+      <c r="S9" s="11">
+        <v>152</v>
+      </c>
+      <c r="T9" s="11">
+        <v>81</v>
+      </c>
+      <c r="U9" s="11">
+        <v>118</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>9.5250000000000004</v>
+      </c>
+      <c r="W9" s="12">
+        <v>14</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>11.225</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>9.5250000000000004</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>1.6999999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -28322,46 +28647,78 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>352</v>
+      </c>
+      <c r="D10" s="11">
+        <v>18</v>
+      </c>
+      <c r="E10" s="11">
+        <v>6</v>
+      </c>
+      <c r="F10" s="11">
+        <v>6</v>
+      </c>
+      <c r="G10" s="11">
+        <v>21</v>
+      </c>
+      <c r="H10" s="11">
+        <v>27</v>
+      </c>
+      <c r="I10" s="11">
+        <v>16</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>11.15</v>
+      </c>
+      <c r="K10" s="12">
+        <v>13</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>320</v>
+      </c>
+      <c r="P10" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>6</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>21</v>
+      </c>
+      <c r="T10" s="11">
+        <v>27</v>
+      </c>
+      <c r="U10" s="11">
+        <v>16</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>9.9</v>
+      </c>
+      <c r="W10" s="12">
+        <v>11</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.15</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -28369,42 +28726,74 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>30</v>
+      </c>
+      <c r="D11" s="11">
+        <v>25</v>
+      </c>
+      <c r="E11" s="11">
+        <v>19</v>
+      </c>
+      <c r="F11" s="11">
+        <v>24</v>
+      </c>
+      <c r="G11" s="11">
+        <v>76</v>
+      </c>
+      <c r="H11" s="11">
+        <v>19</v>
+      </c>
+      <c r="I11" s="11">
+        <v>51</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>6.1</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>30</v>
+      </c>
+      <c r="P11" s="11">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>19</v>
+      </c>
+      <c r="R11" s="11">
+        <v>24</v>
+      </c>
+      <c r="S11" s="11">
+        <v>76</v>
+      </c>
+      <c r="T11" s="11">
+        <v>19</v>
+      </c>
+      <c r="U11" s="11">
+        <v>51</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>6.1</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
@@ -28416,60 +28805,78 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>193</v>
+      </c>
+      <c r="D12" s="11">
+        <v>21</v>
+      </c>
+      <c r="E12" s="11">
+        <v>61</v>
+      </c>
+      <c r="F12" s="11">
+        <v>10</v>
+      </c>
+      <c r="G12" s="11">
+        <v>51</v>
+      </c>
+      <c r="H12" s="11">
+        <v>35</v>
+      </c>
+      <c r="I12" s="11">
+        <v>16</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>9.6750000000000007</v>
+      </c>
+      <c r="K12" s="12">
+        <v>12</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
       <c r="O12" s="11">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="P12" s="11">
-        <v>864</v>
+        <v>15</v>
       </c>
       <c r="Q12" s="11">
-        <v>1004</v>
+        <v>55</v>
       </c>
       <c r="R12" s="11">
-        <v>3399</v>
+        <v>10</v>
       </c>
       <c r="S12" s="11">
-        <v>1158</v>
+        <v>51</v>
       </c>
       <c r="T12" s="11">
-        <v>1436</v>
+        <v>35</v>
       </c>
       <c r="U12" s="11">
-        <v>2720</v>
+        <v>16</v>
       </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>267.52499999999998</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>9.0749999999999993</v>
+      </c>
+      <c r="W12" s="12">
+        <v>11</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.6750000000000007</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>267.52499999999998</v>
+        <v>9.0749999999999993</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-267.52499999999998</v>
+        <v>0.60000000000000142</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -28478,17 +28885,31 @@
         <v>16</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="D13" s="11">
+        <v>440</v>
+      </c>
+      <c r="E13" s="11">
+        <v>280</v>
+      </c>
+      <c r="F13" s="11">
+        <v>280</v>
+      </c>
+      <c r="G13" s="11">
+        <v>440</v>
+      </c>
+      <c r="H13" s="11">
+        <v>400</v>
+      </c>
+      <c r="I13" s="11">
+        <v>840</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>67</v>
+      </c>
+      <c r="K13" s="12">
+        <v>6</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -28523,10 +28944,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="K14" s="12">
+        <v>13</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -28561,10 +28983,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K15" s="12">
+        <v>8</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -28599,10 +29022,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="K16" s="12">
+        <v>13</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -28665,83 +29089,83 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>4506</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>120</v>
+        <v>651</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>864</v>
+        <v>101</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>1004</v>
+        <v>86</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>3399</v>
+        <v>43</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>1158</v>
+        <v>320</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>1436</v>
+        <v>177</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>2720</v>
+        <v>221</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>10701</v>
+        <v>1599</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>45.650000000000006</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>267.52499999999998</v>
+        <v>39.974999999999994</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-267.52499999999998</v>
+        <v>5.6750000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28750,36 +29174,36 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <f t="shared" ref="C19:I19" si="7">C18/40</f>
+        <v>20.375</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.725</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.175000000000001</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>26.475000000000001</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>SUM(J8:J16)</f>
+        <v>142.65</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -28788,48 +29212,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>3</v>
+        <v>16.274999999999999</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>21.6</v>
+        <v>2.5249999999999999</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>25.1</v>
+        <v>2.15</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>84.974999999999994</v>
+        <v>1.075</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>28.95</v>
+        <v>8</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>35.9</v>
+        <v>4.4249999999999998</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>68</v>
+        <v>5.5250000000000004</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>267.52499999999998</v>
+        <v>39.975000000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>1.1412500000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>6.6881249999999994</v>
+        <v>0.9993749999999999</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-6.6881249999999994</v>
+        <v>0.14187500000000003</v>
       </c>
     </row>
   </sheetData>
@@ -28848,7 +29272,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FF78AC-42E1-47D8-9009-F093134445D4}">
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -29115,38 +29539,39 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="71">
-        <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="15">
+        <v>58</v>
+      </c>
+      <c r="K8" s="12">
+        <v>18</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="71">
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -29154,7 +29579,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -29162,38 +29587,54 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="71">
+      <c r="C9" s="11">
+        <v>130</v>
+      </c>
+      <c r="D9" s="11">
+        <v>40</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11">
+        <v>80</v>
+      </c>
+      <c r="H9" s="11">
+        <v>85</v>
+      </c>
+      <c r="I9" s="11">
+        <v>85</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>10.8</v>
+      </c>
+      <c r="K9" s="12">
+        <v>21</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="71">
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -29201,7 +29642,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -29209,38 +29650,54 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="71">
+      <c r="C10" s="11">
+        <v>152</v>
+      </c>
+      <c r="D10" s="11">
+        <v>50</v>
+      </c>
+      <c r="E10" s="11">
+        <v>50</v>
+      </c>
+      <c r="F10" s="11">
+        <v>60</v>
+      </c>
+      <c r="G10" s="11">
+        <v>127</v>
+      </c>
+      <c r="H10" s="11">
+        <v>170</v>
+      </c>
+      <c r="I10" s="11">
+        <v>147</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="K10" s="12">
+        <v>11</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="71">
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -29248,7 +29705,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>18.899999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -29256,38 +29713,54 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="71">
+      <c r="C11" s="11">
+        <v>38</v>
+      </c>
+      <c r="D11" s="11">
+        <v>24</v>
+      </c>
+      <c r="E11" s="11">
+        <v>4</v>
+      </c>
+      <c r="F11" s="11">
+        <v>24</v>
+      </c>
+      <c r="G11" s="11">
+        <v>57</v>
+      </c>
+      <c r="H11" s="11">
+        <v>25</v>
+      </c>
+      <c r="I11" s="11">
+        <v>77</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>6.2249999999999996</v>
+      </c>
+      <c r="K11" s="12">
+        <v>6</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="71">
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -29295,7 +29768,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.2249999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -29303,38 +29776,39 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="71">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="15">
+        <v>5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="71">
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -29342,7 +29816,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -29350,31 +29824,32 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="71">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="15">
+        <v>192</v>
+      </c>
+      <c r="K13" s="12">
+        <v>8</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="71">
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -29388,31 +29863,32 @@
       <c r="B14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="71">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="15">
+        <v>12</v>
+      </c>
+      <c r="K14" s="12">
+        <v>12</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="71">
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -29426,31 +29902,32 @@
       <c r="B15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="71">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="15">
+        <v>10</v>
+      </c>
+      <c r="K15" s="12">
+        <v>12</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="71">
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -29464,31 +29941,32 @@
       <c r="B16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="71">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="15">
+        <v>6</v>
+      </c>
+      <c r="K16" s="12">
+        <v>8</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="71">
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -29500,25 +29978,25 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="71"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="15"/>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="71"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="15"/>
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
@@ -29538,35 +30016,35 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1437</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -29606,7 +30084,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>98.924999999999983</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -29614,7 +30092,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>98.924999999999983</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29624,35 +30102,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>SUM(J8:J16)</f>
+        <v>318.92499999999995</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -29694,7 +30172,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>2.4731249999999996</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -29702,7 +30180,12 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>2.4731249999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="J22" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091A7014-DF7E-4517-BB03-A0C9DE3A111B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5184C775-5074-4684-BD39-02A82D627907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="8" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -2344,10 +2344,11 @@
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="K8" s="12">
+        <v>14</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -2367,7 +2368,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -2375,7 +2376,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -2383,18 +2384,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>80</v>
+      </c>
+      <c r="D9" s="11">
+        <v>40</v>
+      </c>
+      <c r="E9" s="11">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11">
+        <v>80</v>
+      </c>
+      <c r="G9" s="11">
+        <v>80</v>
+      </c>
+      <c r="H9" s="11">
+        <v>80</v>
+      </c>
+      <c r="I9" s="11">
+        <v>80</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="K9" s="12">
+        <v>21</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -2414,7 +2431,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -2422,7 +2439,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -2430,7 +2447,9 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="11">
+        <v>530</v>
+      </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -2439,9 +2458,11 @@
       <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>13.25</v>
+      </c>
+      <c r="K10" s="12">
+        <v>6</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -2461,7 +2482,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -2469,7 +2490,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -2477,18 +2498,34 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>119</v>
+      </c>
+      <c r="D11" s="11">
+        <v>13</v>
+      </c>
+      <c r="E11" s="11">
+        <v>13</v>
+      </c>
+      <c r="F11" s="11">
+        <v>14</v>
+      </c>
+      <c r="G11" s="11">
+        <v>78</v>
+      </c>
+      <c r="H11" s="11">
+        <v>53</v>
+      </c>
+      <c r="I11" s="11">
+        <v>71</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>9.0250000000000004</v>
+      </c>
+      <c r="K11" s="12">
+        <v>11</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -2508,7 +2545,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -2516,7 +2553,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.0250000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -2524,58 +2561,62 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>60</v>
+      </c>
+      <c r="D12" s="11">
+        <v>30</v>
+      </c>
+      <c r="E12" s="11">
+        <v>44</v>
+      </c>
+      <c r="F12" s="11">
+        <v>44</v>
+      </c>
+      <c r="G12" s="11">
+        <v>22</v>
+      </c>
+      <c r="H12" s="11">
+        <v>23</v>
+      </c>
+      <c r="I12" s="11">
+        <v>23</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>6.15</v>
+      </c>
+      <c r="K12" s="12">
+        <v>10</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11">
-        <v>200</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>440</v>
-      </c>
-      <c r="R12" s="11">
-        <v>760</v>
-      </c>
-      <c r="S12" s="11">
-        <v>400</v>
-      </c>
-      <c r="T12" s="11">
-        <v>520</v>
-      </c>
-      <c r="U12" s="11">
-        <v>800</v>
-      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-78</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -2583,18 +2624,34 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="11">
+        <v>200</v>
+      </c>
+      <c r="D13" s="11">
+        <v>340</v>
+      </c>
+      <c r="E13" s="11">
+        <v>320</v>
+      </c>
+      <c r="F13" s="11">
+        <v>440</v>
+      </c>
+      <c r="G13" s="11">
+        <v>380</v>
+      </c>
+      <c r="H13" s="11">
+        <v>360</v>
+      </c>
+      <c r="I13" s="11">
+        <v>600</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>66</v>
+      </c>
+      <c r="K13" s="12">
+        <v>5</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -2629,10 +2686,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="12">
+        <v>14</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -2667,10 +2725,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="K15" s="12">
+        <v>10</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -2705,10 +2764,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K16" s="12">
+        <v>5</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -2779,35 +2839,35 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>989</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>4257</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -2818,44 +2878,44 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>770</v>
+        <v>10</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>3160</v>
+        <v>40</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>53.424999999999997</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-78</v>
+        <v>53.424999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2865,35 +2925,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <v>24.725000000000001</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.574999999999999</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.425000000000001</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.45</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>106.425</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -2906,44 +2966,44 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>5.25</v>
+        <v>0.25</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>19.25</v>
+        <v>0.25</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>1.3356249999999998</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-1.95</v>
+        <v>1.3356249999999998</v>
       </c>
     </row>
   </sheetData>
@@ -28916,17 +28976,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>200</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>160</v>
+      </c>
+      <c r="R13" s="11">
+        <v>200</v>
+      </c>
+      <c r="S13" s="11">
+        <v>398</v>
+      </c>
+      <c r="T13" s="11">
+        <v>280</v>
+      </c>
+      <c r="U13" s="11">
+        <v>560</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>44.95</v>
+      </c>
+      <c r="W13" s="12">
+        <v>5</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -29128,31 +29202,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>101</v>
+        <v>301</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>86</v>
+        <v>246</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>243</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>320</v>
+        <v>718</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>177</v>
+        <v>457</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>221</v>
+        <v>781</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1599</v>
+        <v>3397</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -29216,31 +29290,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>2.5249999999999999</v>
+        <v>7.5250000000000004</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.15</v>
+        <v>6.15</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>1.075</v>
+        <v>6.0750000000000002</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>17.95</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>4.4249999999999998</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>5.5250000000000004</v>
+        <v>19.524999999999999</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>39.975000000000001</v>
+        <v>84.924999999999997</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -29539,47 +29613,78 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>50</v>
+      </c>
+      <c r="D8" s="11">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>843</v>
+      </c>
+      <c r="H8" s="11">
+        <v>448</v>
+      </c>
+      <c r="I8" s="11">
+        <v>875</v>
+      </c>
       <c r="J8" s="15">
-        <v>58</v>
+        <f>SUM(C8:I8)/40</f>
+        <v>57.15</v>
       </c>
       <c r="K8" s="12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>50</v>
+      </c>
+      <c r="P8" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>40</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>843</v>
+      </c>
+      <c r="T8" s="11">
+        <v>448</v>
+      </c>
+      <c r="U8" s="11">
+        <v>875</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>57.15</v>
+      </c>
+      <c r="W8" s="12">
+        <v>19</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>58</v>
+        <v>57.15</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>57.15</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -29609,7 +29714,7 @@
         <v>85</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>10.8</v>
       </c>
       <c r="K9" s="12">
@@ -29620,29 +29725,45 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>130</v>
+      </c>
+      <c r="P9" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>12</v>
+      </c>
+      <c r="S9" s="11">
+        <v>80</v>
+      </c>
+      <c r="T9" s="11">
+        <v>80</v>
+      </c>
+      <c r="U9" s="11">
+        <v>80</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>10.55</v>
+      </c>
+      <c r="W9" s="12">
+        <v>20</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>10.8</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>10.55</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>10.8</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -29683,29 +29804,45 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>112</v>
+      </c>
+      <c r="P10" s="11">
+        <v>49</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>49</v>
+      </c>
+      <c r="R10" s="11">
+        <v>60</v>
+      </c>
+      <c r="S10" s="11">
+        <v>127</v>
+      </c>
+      <c r="T10" s="11">
+        <v>170</v>
+      </c>
+      <c r="U10" s="11">
+        <v>147</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>17.850000000000001</v>
+      </c>
+      <c r="W10" s="12">
+        <v>11</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>18.899999999999999</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>18.899999999999999</v>
+        <v>1.0499999999999972</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -29746,29 +29883,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>20</v>
+      </c>
+      <c r="P11" s="11">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>4</v>
+      </c>
+      <c r="R11" s="11">
+        <v>24</v>
+      </c>
+      <c r="S11" s="11">
+        <v>52</v>
+      </c>
+      <c r="T11" s="11">
+        <v>20</v>
+      </c>
+      <c r="U11" s="11">
+        <v>72</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>5.4</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>6.2249999999999996</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>6.2249999999999996</v>
+        <v>0.82499999999999929</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -29776,47 +29929,78 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>104</v>
+      </c>
+      <c r="D12" s="11">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11">
+        <v>32</v>
+      </c>
+      <c r="F12" s="11">
+        <v>32</v>
+      </c>
+      <c r="G12" s="11">
+        <v>26</v>
+      </c>
+      <c r="H12" s="11">
+        <v>32</v>
+      </c>
+      <c r="I12" s="11">
+        <v>32</v>
+      </c>
       <c r="J12" s="15">
+        <f t="shared" si="0"/>
+        <v>7.25</v>
+      </c>
+      <c r="K12" s="12">
         <v>5</v>
-      </c>
-      <c r="K12" s="12">
-        <v>6</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>12</v>
+      </c>
+      <c r="P12" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>12</v>
+      </c>
+      <c r="R12" s="11">
+        <v>12</v>
+      </c>
+      <c r="S12" s="11">
+        <v>6</v>
+      </c>
+      <c r="T12" s="11">
+        <v>12</v>
+      </c>
+      <c r="U12" s="11">
+        <v>12</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>1.95</v>
+      </c>
+      <c r="W12" s="12">
+        <v>2</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7.25</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -30016,83 +30200,83 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>320</v>
+        <v>474</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>264</v>
+        <v>1133</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>280</v>
+        <v>760</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>309</v>
+        <v>1216</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1437</v>
+        <v>4013</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1108</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1186</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>3716</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>98.924999999999983</v>
+        <v>100.32499999999999</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>92.90000000000002</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>98.924999999999983</v>
+        <v>7.4249999999999963</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30101,36 +30285,36 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>8</v>
+        <f t="shared" ref="C19:I19" si="7">C18/40</f>
+        <v>11.85</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>2.85</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>6.6</v>
+        <v>28.324999999999999</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>7.7249999999999996</v>
+        <v>30.4</v>
       </c>
       <c r="J19" s="22">
         <f>SUM(J8:J16)</f>
-        <v>318.92499999999995</v>
+        <v>320.32499999999999</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -30139,48 +30323,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.875</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.625</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>27.7</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>29.65</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>92.9</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>2.4731249999999996</v>
+        <v>2.5081249999999997</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>2.3225000000000007</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>2.4731249999999996</v>
+        <v>0.1856249999999999</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5184C775-5074-4684-BD39-02A82D627907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F18CA7A-5612-49E3-B485-6C453AF9D79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="9" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="10" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="51">
   <si>
     <t>Booking</t>
   </si>
@@ -206,12 +206,15 @@
   <si>
     <t>.</t>
   </si>
+  <si>
+    <t>Leave</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +329,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -365,7 +376,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -517,11 +528,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -702,6 +750,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2336,13 +2393,27 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>10</v>
+      </c>
+      <c r="D8" s="11">
+        <v>95</v>
+      </c>
+      <c r="E8" s="11">
+        <v>75</v>
+      </c>
+      <c r="F8" s="11">
+        <v>20</v>
+      </c>
+      <c r="G8" s="11">
+        <v>85</v>
+      </c>
+      <c r="H8" s="11">
+        <v>60</v>
+      </c>
+      <c r="I8" s="11">
+        <v>75</v>
+      </c>
       <c r="J8" s="15">
         <v>13</v>
       </c>
@@ -2354,29 +2425,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>10</v>
+      </c>
+      <c r="P8" s="11">
+        <v>90</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>90</v>
+      </c>
+      <c r="R8" s="11">
+        <v>45</v>
+      </c>
+      <c r="S8" s="11">
+        <v>75</v>
+      </c>
+      <c r="T8" s="11">
+        <v>60</v>
+      </c>
+      <c r="U8" s="11">
+        <v>75</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>11.125</v>
+      </c>
+      <c r="W8" s="12">
+        <v>14</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>13</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>11.125</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>13</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -2406,7 +2493,7 @@
         <v>80</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J13" si="0">SUM(C9:I9)/40</f>
         <v>12</v>
       </c>
       <c r="K9" s="12">
@@ -2417,29 +2504,45 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>82</v>
+      </c>
+      <c r="P9" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>40</v>
+      </c>
+      <c r="R9" s="11">
+        <v>80</v>
+      </c>
+      <c r="S9" s="11">
+        <v>80</v>
+      </c>
+      <c r="T9" s="11">
+        <v>80</v>
+      </c>
+      <c r="U9" s="11">
+        <v>80</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>12.05</v>
+      </c>
+      <c r="W9" s="12">
+        <v>21</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>12</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>12.05</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>12</v>
+        <v>-5.0000000000000711E-2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -2468,7 +2571,9 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
+      <c r="O10" s="11">
+        <v>530</v>
+      </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -2477,7 +2582,7 @@
       <c r="U10" s="11"/>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
@@ -2486,11 +2591,11 @@
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>13.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -2531,29 +2636,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>79</v>
+      </c>
+      <c r="P11" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>13</v>
+      </c>
+      <c r="R11" s="11">
+        <v>14</v>
+      </c>
+      <c r="S11" s="11">
+        <v>65</v>
+      </c>
+      <c r="T11" s="11">
+        <v>40</v>
+      </c>
+      <c r="U11" s="11">
+        <v>57</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>7.0250000000000004</v>
+      </c>
+      <c r="W11" s="12">
+        <v>10</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>9.0250000000000004</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.0250000000000004</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>9.0250000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -2594,29 +2715,45 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>54</v>
+      </c>
+      <c r="P12" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>44</v>
+      </c>
+      <c r="R12" s="11">
+        <v>44</v>
+      </c>
+      <c r="S12" s="11">
+        <v>22</v>
+      </c>
+      <c r="T12" s="11">
+        <v>23</v>
+      </c>
+      <c r="U12" s="11">
+        <v>23</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W12" s="12">
+        <v>9</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>6.15</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.15</v>
+        <v>0.15000000000000036</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -2839,70 +2976,70 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>423</v>
+        <v>518</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>417</v>
+        <v>492</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>560</v>
+        <v>645</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>516</v>
+        <v>576</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>774</v>
+        <v>849</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>4257</v>
+        <v>4677</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>183</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>40</v>
+        <v>2018</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -2911,11 +3048,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>49.449999999999996</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>53.424999999999997</v>
+        <v>3.9749999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2925,35 +3062,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>24.725000000000001</v>
+        <v>24.975000000000001</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>10.574999999999999</v>
+        <v>12.95</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>10.425000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>14.45</v>
+        <v>14.95</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>16.125</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>19.350000000000001</v>
+        <v>21.225000000000001</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>106.425</v>
+        <v>116.925</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -2962,35 +3099,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>18.875</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>4.5750000000000002</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>5.1749999999999998</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>4.8250000000000002</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.0750000000000002</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.875</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>50.45</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -2999,11 +3136,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.2362499999999998</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.3356249999999998</v>
+        <v>9.9374999999999991E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3289,18 +3426,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>80</v>
+      </c>
+      <c r="D8" s="11">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11">
+        <v>20</v>
+      </c>
+      <c r="G8" s="11">
+        <v>15</v>
+      </c>
+      <c r="H8" s="11">
+        <v>10</v>
+      </c>
+      <c r="I8" s="11">
+        <v>15</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>8</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -3320,7 +3473,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -3328,7 +3481,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -3337,17 +3490,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>94</v>
+      </c>
+      <c r="H9" s="11">
+        <v>40</v>
+      </c>
+      <c r="I9" s="11">
+        <v>186</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="K9" s="12">
+        <v>15</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -3367,7 +3534,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -3375,21 +3542,23 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="83"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3430,18 +3599,34 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>120</v>
+      </c>
+      <c r="D11" s="11">
+        <v>15</v>
+      </c>
+      <c r="E11" s="11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="11">
+        <v>15</v>
+      </c>
+      <c r="G11" s="11">
+        <v>97</v>
+      </c>
+      <c r="H11" s="11">
+        <v>92</v>
+      </c>
+      <c r="I11" s="11">
+        <v>99</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>11.2</v>
+      </c>
+      <c r="K11" s="12">
+        <v>6</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -3461,7 +3646,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -3469,7 +3654,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -3477,58 +3662,62 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>124</v>
+      </c>
+      <c r="D12" s="11">
+        <v>29</v>
+      </c>
+      <c r="E12" s="11">
+        <v>24</v>
+      </c>
+      <c r="F12" s="11">
+        <v>29</v>
+      </c>
+      <c r="G12" s="11">
+        <v>23</v>
+      </c>
+      <c r="H12" s="11">
+        <v>18</v>
+      </c>
+      <c r="I12" s="11">
+        <v>23</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>6.75</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11">
-        <v>79</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>120</v>
-      </c>
-      <c r="R12" s="11">
-        <v>120</v>
-      </c>
-      <c r="S12" s="11">
-        <v>160</v>
-      </c>
-      <c r="T12" s="11">
-        <v>200</v>
-      </c>
-      <c r="U12" s="11">
-        <v>160</v>
-      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>20.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>20.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-20.975000000000001</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -3544,10 +3733,11 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>90</v>
+      </c>
+      <c r="K13" s="12">
+        <v>4</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -3582,10 +3772,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>16</v>
+      </c>
+      <c r="K14" s="12">
+        <v>14</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -3620,10 +3811,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="K15" s="12">
+        <v>10</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -3658,10 +3850,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K16" s="12">
+        <v>5</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -3685,9 +3878,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
-      <c r="B17" s="17" t="s">
-        <v>32</v>
-      </c>
+      <c r="B17" s="17"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -3695,10 +3886,7 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="J17" s="15"/>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
@@ -3748,35 +3936,35 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1238</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -3787,44 +3975,44 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>899</v>
+        <v>60</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>30.95</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>22.475000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-22.475000000000001</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3834,35 +4022,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.7249999999999996</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.0749999999999993</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>SUM(J8:J16)</f>
+        <v>151.94999999999999</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -3875,48 +4063,49 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>1.9750000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>4.25</v>
+        <v>0.25</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>5.25</v>
+        <v>0.25</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>22.475000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.77374999999999994</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.56187500000000001</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-0.56187500000000001</v>
+        <v>0.73624999999999996</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="C10:I10"/>
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -29362,10 +29551,10 @@
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -30027,17 +30216,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>540</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>730</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1370</v>
+      </c>
+      <c r="S13" s="11">
+        <v>720</v>
+      </c>
+      <c r="T13" s="11">
+        <v>1320</v>
+      </c>
+      <c r="U13" s="11">
+        <v>2120</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>170</v>
+      </c>
+      <c r="W13" s="12">
+        <v>2</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -30239,31 +30442,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>695</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>105</v>
+        <v>835</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>108</v>
+        <v>1478</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>1108</v>
+        <v>1828</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>730</v>
+        <v>2050</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>1186</v>
+        <v>3306</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>3716</v>
+        <v>10516</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -30327,31 +30530,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>3.875</v>
+        <v>17.375</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.625</v>
+        <v>20.875</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>2.7</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>27.7</v>
+        <v>45.7</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>18.25</v>
+        <v>51.25</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>29.65</v>
+        <v>82.65</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>92.9</v>
+        <v>262.89999999999998</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F18CA7A-5612-49E3-B485-6C453AF9D79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A4C776-6491-4786-B601-E592C7FBAE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="10" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -2584,7 +2584,9 @@
         <f t="shared" si="1"/>
         <v>13.25</v>
       </c>
-      <c r="W10" s="12"/>
+      <c r="W10" s="12">
+        <v>4</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>13.25</v>
@@ -2795,17 +2797,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>80</v>
+      </c>
+      <c r="R13" s="11">
+        <v>200</v>
+      </c>
+      <c r="S13" s="11">
+        <v>140</v>
+      </c>
+      <c r="T13" s="11">
+        <v>120</v>
+      </c>
+      <c r="U13" s="11">
+        <v>360</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>25</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -2944,15 +2960,9 @@
         <v>33</v>
       </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="11">
-        <v>10</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>20</v>
-      </c>
-      <c r="R17" s="11">
-        <v>10</v>
-      </c>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
@@ -3015,31 +3025,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>183</v>
+        <v>273</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>193</v>
+        <v>383</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>203</v>
+        <v>323</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>235</v>
+        <v>595</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>2018</v>
+        <v>2978</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -3103,31 +3113,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>4.5750000000000002</v>
+        <v>6.8250000000000002</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>5.1749999999999998</v>
+        <v>6.6749999999999998</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>4.8250000000000002</v>
+        <v>9.5749999999999993</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>6.05</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>5.0750000000000002</v>
+        <v>8.0749999999999993</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>5.875</v>
+        <v>14.875</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>50.45</v>
+        <v>74.45</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -3509,7 +3519,7 @@
         <v>186</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>8</v>
       </c>
       <c r="K9" s="12">
@@ -3521,28 +3531,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>94</v>
+      </c>
+      <c r="T9" s="11">
+        <v>40</v>
+      </c>
+      <c r="U9" s="11">
+        <v>186</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="W9" s="12">
+        <v>15</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>8</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
@@ -3632,29 +3656,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>120</v>
+      </c>
+      <c r="P11" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>9</v>
+      </c>
+      <c r="R11" s="11">
+        <v>15</v>
+      </c>
+      <c r="S11" s="11">
+        <v>91</v>
+      </c>
+      <c r="T11" s="11">
+        <v>86</v>
+      </c>
+      <c r="U11" s="11">
+        <v>93</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>10.725</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>11.2</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.725</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>11.2</v>
+        <v>0.47499999999999964</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -3892,43 +3932,29 @@
       <c r="N17" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O17" s="11">
-        <v>20</v>
-      </c>
-      <c r="P17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>0</v>
-      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
-      <c r="S17" s="11">
-        <v>10</v>
-      </c>
-      <c r="T17" s="11">
-        <v>10</v>
-      </c>
-      <c r="U17" s="11">
-        <v>20</v>
-      </c>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="15">
         <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="W17" s="12">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W17" s="12"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -3971,35 +3997,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>185</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>279</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>60</v>
+        <v>749</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -4008,11 +4034,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>1.5</v>
+        <v>18.725000000000001</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>29.45</v>
+        <v>12.225</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4021,7 +4047,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
+        <f t="shared" ref="C19:I19" si="7">C18/40</f>
         <v>8.1</v>
       </c>
       <c r="D19" s="21">
@@ -4059,35 +4085,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>4.625</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>3.15</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>1.5</v>
+        <v>18.725000000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -4096,11 +4122,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>3.7499999999999999E-2</v>
+        <v>0.46812500000000001</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.73624999999999996</v>
+        <v>0.30562499999999998</v>
       </c>
     </row>
   </sheetData>
@@ -4386,18 +4412,34 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>80</v>
+      </c>
+      <c r="D8" s="11">
+        <v>60</v>
+      </c>
+      <c r="E8" s="11">
+        <v>60</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>80</v>
+      </c>
+      <c r="H8" s="11">
+        <v>80</v>
+      </c>
+      <c r="I8" s="11">
+        <v>240</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="K8" s="12">
+        <v>13</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -4417,7 +4459,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -4425,7 +4467,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -4433,18 +4475,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>70</v>
+      </c>
+      <c r="D9" s="11">
+        <v>131</v>
+      </c>
+      <c r="E9" s="11">
+        <v>31</v>
+      </c>
+      <c r="F9" s="11">
+        <v>21</v>
+      </c>
+      <c r="G9" s="11">
+        <v>170</v>
+      </c>
+      <c r="H9" s="11">
+        <v>140</v>
+      </c>
+      <c r="I9" s="11">
+        <v>190</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>18.824999999999999</v>
+      </c>
+      <c r="K9" s="12">
+        <v>9</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -4464,7 +4522,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>18.824999999999999</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -4472,7 +4530,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>18.824999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -4480,18 +4538,34 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="11">
+        <v>118</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>45</v>
+      </c>
+      <c r="H10" s="11">
+        <v>34</v>
+      </c>
+      <c r="I10" s="11">
+        <v>28</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>5.625</v>
+      </c>
+      <c r="K10" s="12">
+        <v>10</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -4511,7 +4585,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.625</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -4519,7 +4593,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -4527,18 +4601,34 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>106</v>
+      </c>
+      <c r="D11" s="11">
+        <v>6</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>86</v>
+      </c>
+      <c r="H11" s="11">
+        <v>52</v>
+      </c>
+      <c r="I11" s="11">
+        <v>133</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>9.5749999999999993</v>
+      </c>
+      <c r="K11" s="12">
+        <v>11</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -4558,7 +4648,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.5749999999999993</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -4566,7 +4656,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.5749999999999993</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -4574,63 +4664,62 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>24</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>25</v>
+      </c>
+      <c r="H12" s="11">
+        <v>20</v>
+      </c>
+      <c r="I12" s="11">
+        <v>35</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>2.6</v>
+      </c>
+      <c r="K12" s="12">
+        <v>2</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>4040</v>
-      </c>
-      <c r="P12" s="11">
-        <v>2200</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>1960</v>
-      </c>
-      <c r="R12" s="11">
-        <v>1280</v>
-      </c>
-      <c r="S12" s="11">
-        <f>4520+880</f>
-        <v>5400</v>
-      </c>
-      <c r="T12" s="11">
-        <f>3580+640</f>
-        <v>4220</v>
-      </c>
-      <c r="U12" s="11">
-        <f>3400+880+2000</f>
-        <v>6280</v>
-      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>634.5</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>634.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-634.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -4638,18 +4727,34 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="11">
+        <v>200</v>
+      </c>
+      <c r="D13" s="11">
+        <v>600</v>
+      </c>
+      <c r="E13" s="11">
+        <v>480</v>
+      </c>
+      <c r="F13" s="11">
+        <v>600</v>
+      </c>
+      <c r="G13" s="11">
+        <v>1080</v>
+      </c>
+      <c r="H13" s="11">
+        <v>800</v>
+      </c>
+      <c r="I13" s="11">
+        <v>720</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>112</v>
+      </c>
+      <c r="K13" s="12">
+        <v>5</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -4806,30 +4911,16 @@
       <c r="N17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="O17" s="11">
-        <v>24</v>
-      </c>
-      <c r="P17" s="11">
-        <v>16</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>16</v>
-      </c>
-      <c r="R17" s="11">
-        <v>4</v>
-      </c>
-      <c r="S17" s="11">
-        <v>4</v>
-      </c>
-      <c r="T17" s="11">
-        <v>4</v>
-      </c>
-      <c r="U17" s="11">
-        <v>4</v>
-      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="15">
         <f t="shared" si="1"/>
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W17" s="12">
         <v>2</v>
@@ -4840,11 +4931,11 @@
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>-1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -4852,83 +4943,83 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1486</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1126</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1346</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>6545</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>4064</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>2216</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>1976</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>5404</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>4224</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>6284</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>25452</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>51.625000000000007</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>636.29999999999995</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-636.29999999999995</v>
+        <v>51.625000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4938,35 +5029,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <v>14.95</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19.925000000000001</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.275</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.525</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>37.15</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>28.15</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>33.65</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>163.625</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -4975,48 +5066,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>101.6</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>55.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>49.4</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>135.1</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>105.6</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>157.1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>636.29999999999995</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>1.2906250000000001</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>15.907499999999999</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-15.907499999999999</v>
+        <v>1.2906250000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A4C776-6491-4786-B601-E592C7FBAE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A75938-311A-4581-B77C-6D90E932A1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="10" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -3470,28 +3470,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>30</v>
+      </c>
+      <c r="R8" s="11">
+        <v>20</v>
+      </c>
+      <c r="S8" s="11">
+        <v>15</v>
+      </c>
+      <c r="T8" s="11">
+        <v>10</v>
+      </c>
+      <c r="U8" s="11">
+        <v>15</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="W8" s="12">
+        <v>7</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -3735,29 +3749,45 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>112</v>
+      </c>
+      <c r="P12" s="11">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>24</v>
+      </c>
+      <c r="R12" s="11">
+        <v>29</v>
+      </c>
+      <c r="S12" s="11">
+        <v>23</v>
+      </c>
+      <c r="T12" s="11">
+        <v>18</v>
+      </c>
+      <c r="U12" s="11">
+        <v>23</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>6.45</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>6.75</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.75</v>
+        <v>0.29999999999999982</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -3997,35 +4027,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>120</v>
+        <v>232</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>749</v>
+        <v>1127</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -4034,11 +4064,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>18.725000000000001</v>
+        <v>28.175000000000001</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>12.225</v>
+        <v>2.7749999999999995</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4085,35 +4115,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.375</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0.22500000000000001</v>
+        <v>1.575</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0.375</v>
+        <v>1.6</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>4.625</v>
+        <v>5.5750000000000002</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>6.9749999999999996</v>
+        <v>7.9249999999999998</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>18.725000000000001</v>
+        <v>28.175000000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -4122,11 +4152,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.46812500000000001</v>
+        <v>0.70437499999999997</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.30562499999999998</v>
+        <v>6.9374999999999992E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A75938-311A-4581-B77C-6D90E932A1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144BEC19-04E4-4E5A-AABD-94DC4F286434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="10" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -3188,7 +3188,7 @@
     <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -3814,17 +3814,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>240</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>360</v>
+      </c>
+      <c r="R13" s="11">
+        <v>720</v>
+      </c>
+      <c r="S13" s="11">
+        <v>480</v>
+      </c>
+      <c r="T13" s="11">
+        <v>560</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1200</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>89</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -4031,31 +4045,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>74</v>
+        <v>314</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>63</v>
+        <v>423</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>784</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>223</v>
+        <v>703</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>154</v>
+        <v>714</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>317</v>
+        <v>1517</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1127</v>
+        <v>4687</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -4119,31 +4133,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>1.85</v>
+        <v>7.85</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>1.575</v>
+        <v>10.574999999999999</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>1.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>5.5750000000000002</v>
+        <v>17.574999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>3.85</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>7.9249999999999998</v>
+        <v>37.924999999999997</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>28.175000000000001</v>
+        <v>117.175</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D110638-2D49-4CE4-B04B-F153F7E59D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0BECD4-24AA-406C-90A7-388FDD6FE669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="15" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="16" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <sheet name="31" sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -7493,29 +7494,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>83</v>
+      </c>
+      <c r="P8" s="11">
+        <v>106</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>86</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>40</v>
+      </c>
+      <c r="T8" s="11">
+        <v>42</v>
+      </c>
+      <c r="U8" s="11">
+        <v>52</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>10.225</v>
+      </c>
+      <c r="W8" s="12">
+        <v>21</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>12.025</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>10.225</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>12.025</v>
+        <v>1.8000000000000007</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -7635,29 +7652,52 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <f>202+264</f>
+        <v>466</v>
+      </c>
+      <c r="P10" s="11">
+        <f>120+6</f>
+        <v>126</v>
+      </c>
+      <c r="Q10" s="11">
+        <f>132+6</f>
+        <v>138</v>
+      </c>
+      <c r="R10" s="11">
+        <v>160</v>
+      </c>
+      <c r="S10" s="11">
+        <f>148+24</f>
+        <v>172</v>
+      </c>
+      <c r="T10" s="11">
+        <f>134+53</f>
+        <v>187</v>
+      </c>
+      <c r="U10" s="11">
+        <f>214+23</f>
+        <v>237</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>37.15</v>
+      </c>
+      <c r="W10" s="12">
+        <f>7+9</f>
+        <v>16</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>10.7</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>37.15</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>10.7</v>
+        <v>-26.45</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -7778,28 +7818,42 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>25</v>
+      </c>
+      <c r="R12" s="11">
+        <v>25</v>
+      </c>
+      <c r="S12" s="11">
+        <v>25</v>
+      </c>
+      <c r="T12" s="11">
+        <v>25</v>
+      </c>
+      <c r="U12" s="11">
+        <v>30</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="W12" s="12">
+        <v>1</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>12.925000000000001</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>12.925000000000001</v>
+        <v>8.9250000000000007</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -7825,17 +7879,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>478</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>320</v>
+      </c>
+      <c r="R13" s="11">
+        <v>440</v>
+      </c>
+      <c r="S13" s="11">
+        <v>297</v>
+      </c>
+      <c r="T13" s="11">
+        <v>417</v>
+      </c>
+      <c r="U13" s="11">
+        <v>180</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>53.3</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -8040,35 +8108,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>188</v>
+        <v>737</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>124</v>
+        <v>864</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>669</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>109</v>
+        <v>734</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>142</v>
+        <v>676</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>765</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>147</v>
+        <v>646</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>904</v>
+        <v>5091</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -8077,11 +8145,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>22.6</v>
+        <v>73.974999999999994</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>37.650000000000006</v>
+        <v>-13.724999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8128,35 +8196,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>4.7</v>
+        <v>18.425000000000001</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>3.1</v>
+        <v>21.6</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.5</v>
+        <v>16.725000000000001</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>2.7250000000000001</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>3.55</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>2.35</v>
+        <v>19.125</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>3.6749999999999998</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>22.6</v>
+        <v>127.27500000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -8165,11 +8233,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.56500000000000006</v>
+        <v>1.8493749999999998</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.94125000000000014</v>
+        <v>-0.34312499999999996</v>
       </c>
     </row>
   </sheetData>
@@ -8518,18 +8586,33 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>80</v>
+      </c>
+      <c r="D9" s="11">
+        <v>52</v>
+      </c>
+      <c r="E9" s="11">
+        <v>18</v>
+      </c>
+      <c r="F9" s="11">
+        <v>35</v>
+      </c>
+      <c r="G9" s="11">
+        <v>157</v>
+      </c>
+      <c r="H9" s="11">
+        <v>153</v>
+      </c>
+      <c r="I9" s="11">
+        <v>185</v>
+      </c>
       <c r="J9" s="15">
-        <v>18</v>
+        <f>SUM(C9:I9)/40</f>
+        <v>17</v>
       </c>
       <c r="K9" s="12">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -8550,7 +8633,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="1">J9</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="2">V9</f>
@@ -8558,7 +8641,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="3">Y9-Z9</f>
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -8588,7 +8671,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" ref="J9:J16" si="4">SUM(C10:I10)/40</f>
+        <f t="shared" ref="J10:J16" si="4">SUM(C10:I10)/40</f>
         <v>7.7750000000000004</v>
       </c>
       <c r="K10" s="12">
@@ -8629,18 +8712,33 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>44</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>40</v>
+      </c>
+      <c r="G11" s="11">
+        <v>50</v>
+      </c>
+      <c r="H11" s="11">
+        <v>50</v>
+      </c>
+      <c r="I11" s="11">
+        <v>100</v>
+      </c>
       <c r="J11" s="15">
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>7.1</v>
       </c>
       <c r="K11" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
@@ -8661,7 +8759,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="2"/>
@@ -8669,7 +8767,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -8930,35 +9028,35 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>657</v>
+        <v>781</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>106</v>
+        <v>313</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>93</v>
+        <v>296</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>103</v>
+        <v>388</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1196</v>
+        <v>2160</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -8998,7 +9096,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>52.9</v>
+        <v>54.000000000000007</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -9006,7 +9104,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>52.9</v>
+        <v>54.000000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9016,35 +9114,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>16.425000000000001</v>
+        <v>19.524999999999999</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>2.5499999999999998</v>
+        <v>3.85</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>2.5750000000000002</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0.8</v>
+        <v>2.6749999999999998</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>2.65</v>
+        <v>7.8250000000000002</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>2.3250000000000002</v>
+        <v>7.4</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>2.5750000000000002</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>29.9</v>
+        <v>54</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -9086,7 +9184,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>1.3225</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -9094,7 +9192,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.3225</v>
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
@@ -9427,18 +9525,34 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="11">
+        <v>80</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>80</v>
+      </c>
+      <c r="F9" s="11">
+        <v>80</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>20</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>12</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -9458,7 +9572,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -9466,7 +9580,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9521,18 +9635,34 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="11">
+        <v>284</v>
+      </c>
+      <c r="D11" s="11">
+        <v>12</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>60</v>
+      </c>
+      <c r="H11" s="11">
+        <v>55</v>
+      </c>
+      <c r="I11" s="11">
+        <v>121</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>13.3</v>
+      </c>
+      <c r="K11" s="12">
+        <v>11</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -9552,7 +9682,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -9560,7 +9690,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -9568,60 +9698,62 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="11">
+        <v>205</v>
+      </c>
+      <c r="D12" s="11">
+        <v>4</v>
+      </c>
+      <c r="E12" s="11">
+        <v>36</v>
+      </c>
+      <c r="F12" s="11">
+        <v>36</v>
+      </c>
+      <c r="G12" s="11">
+        <v>3</v>
+      </c>
+      <c r="H12" s="11">
+        <v>20</v>
+      </c>
+      <c r="I12" s="11">
+        <v>38</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="K12" s="12">
+        <v>8</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>40</v>
-      </c>
-      <c r="P12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>0</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11">
-        <v>70</v>
-      </c>
-      <c r="T12" s="11">
-        <v>60</v>
-      </c>
-      <c r="U12" s="11">
-        <v>70</v>
-      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-6</v>
+        <v>8.5500000000000007</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -9797,30 +9929,16 @@
       <c r="N17" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O17" s="11">
-        <v>12</v>
-      </c>
-      <c r="P17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>12</v>
-      </c>
-      <c r="R17" s="11">
-        <v>0</v>
-      </c>
-      <c r="S17" s="11">
-        <v>15</v>
-      </c>
-      <c r="T17" s="11">
-        <v>0</v>
-      </c>
-      <c r="U17" s="11">
-        <v>0</v>
-      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="15">
         <f t="shared" si="1"/>
-        <v>0.97499999999999998</v>
+        <v>0</v>
       </c>
       <c r="W17" s="12">
         <v>3</v>
@@ -9831,11 +9949,11 @@
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>0.97499999999999998</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>-0.97499999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -9843,42 +9961,42 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1134</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
@@ -9886,7 +10004,7 @@
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
@@ -9894,32 +10012,32 @@
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>28.35</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>6.9749999999999996</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-6.9749999999999996</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9929,35 +10047,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <v>14.225</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.575</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.875</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>28.35</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -9966,7 +10084,7 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
@@ -9974,7 +10092,7 @@
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
@@ -9982,32 +10100,32 @@
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>2.125</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>6.9749999999999996</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.70874999999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.174375</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-0.174375</v>
+        <v>0.70874999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0BECD4-24AA-406C-90A7-388FDD6FE669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE4987A-2472-4111-AA2E-4D316288623E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="16" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -46,7 +46,6 @@
     <sheet name="31" sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -8556,29 +8555,45 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>135</v>
+      </c>
+      <c r="P8" s="11">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>56</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>70</v>
+      </c>
+      <c r="T8" s="11">
+        <v>65</v>
+      </c>
+      <c r="U8" s="11">
+        <v>80</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>11.55</v>
+      </c>
+      <c r="W8" s="12">
+        <v>21</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>14.8</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>11.55</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>14.8</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -8619,29 +8634,45 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>80</v>
+      </c>
+      <c r="P9" s="11">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>8</v>
+      </c>
+      <c r="R9" s="11">
+        <v>20</v>
+      </c>
+      <c r="S9" s="11">
+        <v>137</v>
+      </c>
+      <c r="T9" s="11">
+        <v>123</v>
+      </c>
+      <c r="U9" s="11">
+        <v>150</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>14.25</v>
+      </c>
+      <c r="W9" s="12">
+        <v>21</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="1">J9</f>
         <v>17</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="2">V9</f>
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="3">Y9-Z9</f>
-        <v>17</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -8682,29 +8713,45 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="O10" s="11">
+        <v>212</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>15</v>
+      </c>
+      <c r="T10" s="11">
+        <v>13</v>
+      </c>
+      <c r="U10" s="11">
+        <v>13</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>6.3250000000000002</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="1"/>
         <v>7.7750000000000004</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.3250000000000002</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="3"/>
-        <v>7.7750000000000004</v>
+        <v>1.4500000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -8745,29 +8792,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>44</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>25</v>
+      </c>
+      <c r="T11" s="11">
+        <v>20</v>
+      </c>
+      <c r="U11" s="11">
+        <v>35</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>3.1</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="1"/>
         <v>7.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="3"/>
-        <v>7.1</v>
+        <v>3.9999999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -8808,29 +8871,45 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>70</v>
+      </c>
+      <c r="P12" s="11">
+        <v>34</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>22</v>
+      </c>
+      <c r="R12" s="11">
+        <v>20</v>
+      </c>
+      <c r="S12" s="11">
+        <v>5</v>
+      </c>
+      <c r="T12" s="11">
+        <v>5</v>
+      </c>
+      <c r="U12" s="11">
+        <v>10</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="1"/>
         <v>7.3250000000000002</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="3"/>
-        <v>7.3250000000000002</v>
+        <v>3.1749999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -8857,17 +8936,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>40</v>
+      </c>
+      <c r="R13" s="11">
+        <v>40</v>
+      </c>
+      <c r="S13" s="11">
+        <v>40</v>
+      </c>
+      <c r="T13" s="11">
+        <v>40</v>
+      </c>
+      <c r="U13" s="11">
+        <v>40</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W13" s="12">
+        <v>1</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -9063,35 +9156,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1815</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -9100,11 +9193,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>39.375</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>54.000000000000007</v>
+        <v>14.625</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9151,35 +9244,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>13.525</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45.375</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -9188,11 +9281,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.984375</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1.35</v>
+        <v>0.36562499999999998</v>
       </c>
     </row>
   </sheetData>
@@ -9479,17 +9572,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>30</v>
+      </c>
+      <c r="H8" s="11">
+        <v>60</v>
+      </c>
+      <c r="I8" s="11">
+        <v>30</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="12">
+        <v>4</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -9509,7 +9616,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -9517,7 +9624,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -9589,17 +9696,31 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>99</v>
+      </c>
+      <c r="H10" s="11">
+        <v>76</v>
+      </c>
+      <c r="I10" s="11">
+        <v>131</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>7.65</v>
+      </c>
+      <c r="K10" s="12">
+        <v>7</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -9619,7 +9740,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -9627,7 +9748,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -9965,11 +10086,11 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
@@ -9977,19 +10098,19 @@
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>75</v>
+        <v>211</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>179</v>
+        <v>340</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>1134</v>
+        <v>1600</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -10029,7 +10150,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>28.35</v>
+        <v>40</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -10037,7 +10158,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>28.35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10051,11 +10172,11 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
@@ -10063,19 +10184,19 @@
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>1.575</v>
+        <v>4.8</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>1.875</v>
+        <v>5.2750000000000004</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>4.4749999999999996</v>
+        <v>8.5</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>28.35</v>
+        <v>40</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -10117,7 +10238,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.70874999999999999</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -10125,7 +10246,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.70874999999999999</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE4987A-2472-4111-AA2E-4D316288623E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BCA35C-2FE4-4143-BE60-C6F99E9F52AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="16" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -9603,28 +9603,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>30</v>
+      </c>
+      <c r="T8" s="11">
+        <v>60</v>
+      </c>
+      <c r="U8" s="11">
+        <v>30</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="W8" s="12">
+        <v>4</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>4</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -9665,29 +9679,45 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>80</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>80</v>
+      </c>
+      <c r="R9" s="11">
+        <v>80</v>
+      </c>
+      <c r="S9" s="11">
+        <v>0</v>
+      </c>
+      <c r="T9" s="11">
+        <v>0</v>
+      </c>
+      <c r="U9" s="11">
+        <v>20</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="W9" s="12">
+        <v>12</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>6.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -9727,28 +9757,42 @@
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>98</v>
+      </c>
+      <c r="T10" s="11">
+        <v>76</v>
+      </c>
+      <c r="U10" s="11">
+        <v>131</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>7.625</v>
+      </c>
+      <c r="W10" s="12">
+        <v>7</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>7.65</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.625</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>7.65</v>
+        <v>2.5000000000000355E-2</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -9789,29 +9833,45 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="O11" s="11">
+        <v>244</v>
+      </c>
+      <c r="P11" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>55</v>
+      </c>
+      <c r="T11" s="11">
+        <v>50</v>
+      </c>
+      <c r="U11" s="11">
+        <v>91</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>11.3</v>
+      </c>
+      <c r="W11" s="12">
+        <v>10</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>13.3</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>13.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -9852,29 +9912,45 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="O12" s="11">
+        <v>145</v>
+      </c>
+      <c r="P12" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>16</v>
+      </c>
+      <c r="R12" s="11">
+        <v>16</v>
+      </c>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>18</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>4.9749999999999996</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>8.5500000000000007</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.9749999999999996</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>8.5500000000000007</v>
+        <v>3.5750000000000011</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -10117,35 +10193,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1336</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -10154,11 +10230,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>33.4</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>40</v>
+        <v>6.6000000000000014</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10205,35 +10281,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>11.725</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.5750000000000002</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>33.4</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -10242,11 +10318,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>1</v>
+        <v>0.16500000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -10540,10 +10616,11 @@
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15">
-        <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>6</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -10563,7 +10640,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -10571,7 +10648,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -10580,17 +10657,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>20</v>
+      </c>
+      <c r="E9" s="11">
+        <v>44</v>
+      </c>
+      <c r="F9" s="11">
+        <v>64</v>
+      </c>
+      <c r="G9" s="11">
+        <v>40</v>
+      </c>
+      <c r="H9" s="11">
+        <v>28</v>
+      </c>
+      <c r="I9" s="11">
+        <v>32</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>5.7</v>
+      </c>
+      <c r="K9" s="12">
+        <v>12</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -10610,7 +10701,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -10618,7 +10709,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -10728,50 +10819,39 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11">
-        <v>280</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>288</v>
-      </c>
-      <c r="R12" s="11">
-        <v>680</v>
-      </c>
-      <c r="S12" s="11">
-        <v>440</v>
-      </c>
-      <c r="T12" s="11">
-        <v>599</v>
-      </c>
-      <c r="U12" s="11">
-        <v>600</v>
-      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>72.174999999999997</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>72.174999999999997</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-72.174999999999997</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -10971,31 +11051,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -11006,44 +11086,44 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>2887</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>72.174999999999997</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-72.174999999999997</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11057,31 +11137,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -11094,44 +11174,44 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>14.975</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>72.174999999999997</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.36749999999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>1.8043749999999998</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-1.8043749999999998</v>
+        <v>0.36749999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BCA35C-2FE4-4143-BE60-C6F99E9F52AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043FD6C6-FCBA-490B-BEE0-5B848FCEA894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="16" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="17" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -9319,11 +9319,10 @@
     <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -9976,17 +9975,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>1358</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1356</v>
+      </c>
+      <c r="R13" s="11">
+        <v>2520</v>
+      </c>
+      <c r="S13" s="11">
+        <v>2519</v>
+      </c>
+      <c r="T13" s="11">
+        <v>1301</v>
+      </c>
+      <c r="U13" s="11">
+        <v>2698</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>293.8</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -10197,31 +10210,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>1374</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>96</v>
+        <v>1452</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>96</v>
+        <v>2616</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>183</v>
+        <v>2702</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>186</v>
+        <v>1487</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>290</v>
+        <v>2988</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1336</v>
+        <v>13088</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -10285,31 +10298,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.4</v>
+        <v>34.35</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.4</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>2.4</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>4.5750000000000002</v>
+        <v>67.55</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>4.6500000000000004</v>
+        <v>37.174999999999997</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>7.25</v>
+        <v>74.7</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>33.4</v>
+        <v>327.2</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -10609,17 +10622,30 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>45</v>
+      </c>
+      <c r="E8" s="11">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11">
+        <v>35</v>
+      </c>
+      <c r="G8" s="11">
+        <v>40</v>
+      </c>
+      <c r="H8" s="11">
+        <v>30</v>
+      </c>
+      <c r="I8" s="11">
+        <v>50</v>
+      </c>
       <c r="J8" s="15">
-        <v>5</v>
+        <f>SUM(C8:I8)/40</f>
+        <v>6</v>
       </c>
       <c r="K8" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
@@ -10627,28 +10653,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>45</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>40</v>
+      </c>
+      <c r="R8" s="11">
+        <v>35</v>
+      </c>
+      <c r="S8" s="11">
+        <v>40</v>
+      </c>
+      <c r="T8" s="11">
+        <v>30</v>
+      </c>
+      <c r="U8" s="11">
+        <v>50</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W8" s="12">
+        <v>7</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -10687,29 +10727,45 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="O9" s="11">
+        <v>40</v>
+      </c>
+      <c r="P9" s="11">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>32</v>
+      </c>
+      <c r="R9" s="11">
+        <v>64</v>
+      </c>
+      <c r="S9" s="11">
+        <v>40</v>
+      </c>
+      <c r="T9" s="11">
+        <v>28</v>
+      </c>
+      <c r="U9" s="11">
+        <v>32</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>6.7</v>
+      </c>
+      <c r="W9" s="12">
+        <v>13</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>5.7</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>5.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -10718,45 +10774,73 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>15</v>
+      </c>
+      <c r="E10" s="11">
+        <v>13</v>
+      </c>
+      <c r="F10" s="11">
+        <v>12</v>
+      </c>
+      <c r="G10" s="11">
+        <v>36</v>
+      </c>
+      <c r="H10" s="11">
+        <v>30</v>
+      </c>
+      <c r="I10" s="11">
+        <v>32</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>3.45</v>
+      </c>
+      <c r="K10" s="12">
+        <v>4</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>13</v>
+      </c>
+      <c r="R10" s="11">
+        <v>12</v>
+      </c>
+      <c r="S10" s="11">
+        <v>21</v>
+      </c>
+      <c r="T10" s="11">
+        <v>18</v>
+      </c>
+      <c r="U10" s="11">
+        <v>19</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W10" s="12">
+        <v>3</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -10765,17 +10849,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>12</v>
+      </c>
+      <c r="E11" s="11">
+        <v>12</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>25</v>
+      </c>
+      <c r="H11" s="11">
+        <v>25</v>
+      </c>
+      <c r="I11" s="11">
+        <v>70</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="K11" s="12">
+        <v>3</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -10795,7 +10893,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -10803,7 +10901,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -10812,17 +10910,30 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>10</v>
+      </c>
+      <c r="E12" s="11">
+        <v>30</v>
+      </c>
+      <c r="F12" s="11">
+        <v>20</v>
+      </c>
+      <c r="G12" s="11">
+        <v>52</v>
+      </c>
+      <c r="H12" s="11">
+        <v>72</v>
+      </c>
+      <c r="I12" s="11">
+        <v>92</v>
+      </c>
       <c r="J12" s="15">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>6.9</v>
       </c>
       <c r="K12" s="12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -10830,28 +10941,42 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>30</v>
+      </c>
+      <c r="R12" s="11">
+        <v>20</v>
+      </c>
+      <c r="S12" s="11">
+        <v>52</v>
+      </c>
+      <c r="T12" s="11">
+        <v>60</v>
+      </c>
+      <c r="U12" s="11">
+        <v>80</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>6.3</v>
+      </c>
+      <c r="W12" s="12">
+        <v>4</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>0.60000000000000053</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -11051,79 +11176,79 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>228</v>
+        <v>1026</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>14.7</v>
+        <v>25.65</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>21.45</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>14.7</v>
+        <v>4.2000000000000011</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11137,31 +11262,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>1.1000000000000001</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>1.6</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>4.8250000000000002</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0.7</v>
+        <v>4.625</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>5.7</v>
+        <v>25.65</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -11170,48 +11295,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.8250000000000002</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.5250000000000004</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21.45</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0.36749999999999999</v>
+        <v>0.64124999999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.53625</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.36749999999999999</v>
+        <v>0.10500000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -11498,17 +11623,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>15</v>
+      </c>
+      <c r="E8" s="11">
+        <v>10</v>
+      </c>
+      <c r="F8" s="11">
+        <v>15</v>
+      </c>
+      <c r="G8" s="11">
+        <v>90</v>
+      </c>
+      <c r="H8" s="11">
+        <v>90</v>
+      </c>
+      <c r="I8" s="11">
+        <v>220</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="K8" s="12">
+        <v>12</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -11528,7 +11667,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -11536,7 +11675,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -11545,17 +11684,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>83</v>
+      </c>
+      <c r="H9" s="11">
+        <v>82</v>
+      </c>
+      <c r="I9" s="11">
+        <v>99</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>6.6</v>
+      </c>
+      <c r="K9" s="12">
+        <v>20</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -11575,7 +11728,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -11583,7 +11736,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -11592,17 +11745,31 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>20</v>
+      </c>
+      <c r="G10" s="11">
+        <v>65</v>
+      </c>
+      <c r="H10" s="11">
+        <v>12</v>
+      </c>
+      <c r="I10" s="11">
+        <v>83</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>4.5</v>
+      </c>
+      <c r="K10" s="12">
+        <v>4</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -11622,7 +11789,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -11630,7 +11797,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -11639,17 +11806,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>40</v>
+      </c>
+      <c r="E11" s="11">
+        <v>40</v>
+      </c>
+      <c r="F11" s="11">
+        <v>64</v>
+      </c>
+      <c r="G11" s="11">
+        <v>115</v>
+      </c>
+      <c r="H11" s="11">
+        <v>105</v>
+      </c>
+      <c r="I11" s="11">
+        <v>120</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>12.1</v>
+      </c>
+      <c r="K11" s="12">
+        <v>7</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -11669,7 +11850,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -11677,7 +11858,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -11924,31 +12105,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -11988,7 +12169,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -11996,7 +12177,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12010,31 +12191,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.8249999999999993</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.05</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -12076,7 +12257,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.85500000000000009</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -12084,7 +12265,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>0.85500000000000009</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043FD6C6-FCBA-490B-BEE0-5B848FCEA894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD41FC2-1BE4-4F5D-8AFB-11885458D8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="17" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="18" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -11002,17 +11002,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>173</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>213</v>
+      </c>
+      <c r="R13" s="11">
+        <v>294</v>
+      </c>
+      <c r="S13" s="11">
+        <v>573</v>
+      </c>
+      <c r="T13" s="11">
+        <v>413</v>
+      </c>
+      <c r="U13" s="11">
+        <v>334</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -11211,31 +11225,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>115</v>
+        <v>328</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>131</v>
+        <v>425</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>153</v>
+        <v>726</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>136</v>
+        <v>549</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>181</v>
+        <v>515</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>858</v>
+        <v>2858</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -11299,31 +11313,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>2.5499999999999998</v>
+        <v>6.875</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.875</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>3.2749999999999999</v>
+        <v>10.625</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>3.8250000000000002</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>3.4</v>
+        <v>13.725</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>4.5250000000000004</v>
+        <v>12.875</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>21.45</v>
+        <v>71.45</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD41FC2-1BE4-4F5D-8AFB-11885458D8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAA2206-4CED-4F01-BBEB-3F8FCD713499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="18" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -11384,11 +11384,11 @@
     <col min="14" max="14" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -11668,28 +11668,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>10</v>
+      </c>
+      <c r="R8" s="11">
+        <v>15</v>
+      </c>
+      <c r="S8" s="11">
+        <v>90</v>
+      </c>
+      <c r="T8" s="11">
+        <v>90</v>
+      </c>
+      <c r="U8" s="11">
+        <v>220</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="W8" s="12">
+        <v>12</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>11</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -11729,28 +11743,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>43</v>
+      </c>
+      <c r="T9" s="11">
+        <v>42</v>
+      </c>
+      <c r="U9" s="11">
+        <v>59</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="W9" s="12">
+        <v>19</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>6.6</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>6.6</v>
+        <v>2.9999999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -11790,28 +11818,42 @@
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>20</v>
+      </c>
+      <c r="S10" s="11">
+        <v>50</v>
+      </c>
+      <c r="T10" s="11">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11">
+        <v>30</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="W10" s="12">
+        <v>3</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>4.5</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>4.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -11851,28 +11893,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>24</v>
+      </c>
+      <c r="S11" s="11">
+        <v>40</v>
+      </c>
+      <c r="T11" s="11">
+        <v>40</v>
+      </c>
+      <c r="U11" s="11">
+        <v>40</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="W11" s="12">
+        <v>3</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>12.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>12.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -11945,17 +12001,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>200</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>360</v>
+      </c>
+      <c r="R13" s="11">
+        <v>640</v>
+      </c>
+      <c r="S13" s="11">
+        <v>400</v>
+      </c>
+      <c r="T13" s="11">
+        <v>440</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1120</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>79</v>
+      </c>
+      <c r="W13" s="12">
+        <v>8</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -12154,31 +12224,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1469</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>3988</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -12187,11 +12257,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>20.700000000000003</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>34.200000000000003</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12242,31 +12312,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.375</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17.475000000000001</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15.574999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36.725000000000001</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>99.7</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -12275,11 +12345,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.51750000000000007</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.85500000000000009</v>
+        <v>0.33750000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">
@@ -13655,24 +13725,16 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>40</v>
-      </c>
+      <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
-      <c r="S12" s="11">
-        <v>1</v>
-      </c>
-      <c r="T12" s="11">
-        <v>1</v>
-      </c>
-      <c r="U12" s="11">
-        <v>1</v>
-      </c>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>1.075</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
@@ -13681,11 +13743,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>1.075</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-1.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -13861,30 +13923,16 @@
       <c r="N17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="11">
-        <v>69</v>
-      </c>
-      <c r="P17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>22</v>
-      </c>
-      <c r="R17" s="11">
-        <v>0</v>
-      </c>
-      <c r="S17" s="11">
-        <v>23</v>
-      </c>
-      <c r="T17" s="11">
-        <v>10</v>
-      </c>
-      <c r="U17" s="11">
-        <v>20</v>
-      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="15">
         <f t="shared" si="1"/>
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W17" s="18">
         <v>5</v>
@@ -13895,11 +13943,11 @@
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>-3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -13907,30 +13955,16 @@
       <c r="B18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="11">
-        <v>80</v>
-      </c>
-      <c r="D18" s="11">
-        <v>320</v>
-      </c>
-      <c r="E18" s="11">
-        <v>160</v>
-      </c>
-      <c r="F18" s="11">
-        <v>600</v>
-      </c>
-      <c r="G18" s="11">
-        <v>360</v>
-      </c>
-      <c r="H18" s="11">
-        <v>160</v>
-      </c>
-      <c r="I18" s="11">
-        <v>760</v>
-      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
       <c r="J18" s="15">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K18" s="18"/>
       <c r="M18" s="16"/>
@@ -13938,40 +13972,28 @@
         <v>16</v>
       </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="11">
-        <v>160</v>
-      </c>
-      <c r="Q18" s="11">
-        <v>120</v>
-      </c>
-      <c r="R18" s="11">
-        <v>840</v>
-      </c>
-      <c r="S18" s="11">
-        <v>319</v>
-      </c>
-      <c r="T18" s="11">
-        <v>160</v>
-      </c>
-      <c r="U18" s="11">
-        <v>680</v>
-      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
       <c r="V18" s="15">
         <f>SUM(O18:U18)/40</f>
-        <v>56.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="W18" s="18"/>
       <c r="Y18" s="36">
         <f t="shared" ref="Y18" si="5">J18</f>
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="37">
         <f t="shared" ref="Z18" si="6">V18</f>
-        <v>56.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="38">
         <f t="shared" ref="AA18" si="7">Y18-Z18</f>
-        <v>4.0249999999999986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
@@ -13979,70 +14001,70 @@
       <c r="B19" s="7"/>
       <c r="C19" s="25">
         <f t="shared" ref="C19:I19" si="8">SUM(C8:C18)</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D19" s="25">
         <f t="shared" si="8"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="E19" s="25">
         <f t="shared" si="8"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F19" s="25">
         <f t="shared" si="8"/>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G19" s="25">
         <f t="shared" si="8"/>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H19" s="25">
         <f t="shared" si="8"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I19" s="25">
         <f t="shared" si="8"/>
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="J19" s="26">
         <f>SUM(C19:I19)</f>
-        <v>2440</v>
+        <v>0</v>
       </c>
       <c r="K19" s="28"/>
       <c r="M19" s="1"/>
       <c r="N19" s="7"/>
       <c r="O19" s="72">
         <f>SUM(O8:O18)</f>
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="P19" s="72">
         <f t="shared" ref="P19:U19" si="9">SUM(P8:P18)</f>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="72">
         <f t="shared" si="9"/>
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="R19" s="72">
         <f t="shared" si="9"/>
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="S19" s="72">
         <f t="shared" si="9"/>
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="T19" s="72">
         <f t="shared" si="9"/>
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="U19" s="72">
         <f t="shared" si="9"/>
-        <v>701</v>
+        <v>0</v>
       </c>
       <c r="V19" s="26">
         <f>SUM(O19:U19)</f>
-        <v>2466</v>
+        <v>0</v>
       </c>
       <c r="W19" s="28"/>
       <c r="Y19" s="33">
@@ -14051,11 +14073,11 @@
       </c>
       <c r="Z19" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>4.6749999999999998</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-4.6749999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14065,35 +14087,35 @@
       </c>
       <c r="C20" s="21">
         <f t="shared" ref="C20:J20" si="10">C19/40</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" s="21">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="21">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20" s="21">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G20" s="21">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H20" s="21">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I20" s="21">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="10"/>
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K20" s="23"/>
       <c r="M20" s="1"/>
@@ -14102,35 +14124,35 @@
       </c>
       <c r="O20" s="21">
         <f t="shared" ref="O20:V20" si="11">O19/40</f>
-        <v>2.7250000000000001</v>
+        <v>0</v>
       </c>
       <c r="P20" s="21">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="21">
         <f t="shared" si="11"/>
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R20" s="21">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S20" s="21">
         <f t="shared" si="11"/>
-        <v>8.5749999999999993</v>
+        <v>0</v>
       </c>
       <c r="T20" s="21">
         <f t="shared" si="11"/>
-        <v>4.2750000000000004</v>
+        <v>0</v>
       </c>
       <c r="U20" s="21">
         <f t="shared" si="11"/>
-        <v>17.524999999999999</v>
+        <v>0</v>
       </c>
       <c r="V20" s="22">
         <f t="shared" si="11"/>
-        <v>61.65</v>
+        <v>0</v>
       </c>
       <c r="W20" s="23"/>
       <c r="Y20" s="39">
@@ -14139,11 +14161,11 @@
       </c>
       <c r="Z20" s="40">
         <f>Z19/40</f>
-        <v>0.11687499999999999</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="41">
         <f>AA19/40</f>
-        <v>-0.11687499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">
@@ -14485,45 +14507,69 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="D8" s="11">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11">
+        <v>120</v>
+      </c>
+      <c r="G8" s="11">
+        <v>20</v>
+      </c>
+      <c r="H8" s="11">
+        <v>20</v>
+      </c>
       <c r="I8" s="11"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>12</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
+      <c r="P8" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>40</v>
+      </c>
+      <c r="S8" s="11">
+        <v>20</v>
+      </c>
+      <c r="T8" s="11">
+        <v>20</v>
+      </c>
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="W8" s="12">
+        <v>11</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -14532,45 +14578,73 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>12</v>
+      </c>
+      <c r="E9" s="11">
+        <v>15</v>
+      </c>
+      <c r="F9" s="11">
+        <v>13</v>
+      </c>
+      <c r="G9" s="11">
+        <v>70</v>
+      </c>
+      <c r="H9" s="11">
+        <v>70</v>
+      </c>
+      <c r="I9" s="11">
+        <v>60</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="K9" s="12">
+        <v>10</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>15</v>
+      </c>
+      <c r="R9" s="11">
+        <v>13</v>
+      </c>
+      <c r="S9" s="11">
+        <v>70</v>
+      </c>
+      <c r="T9" s="11">
+        <v>68</v>
+      </c>
+      <c r="U9" s="11">
+        <v>60</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>5.95</v>
+      </c>
+      <c r="W9" s="12">
+        <v>10</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -14579,45 +14653,73 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>104</v>
+      </c>
+      <c r="H10" s="11">
+        <v>60</v>
+      </c>
+      <c r="I10" s="11">
+        <v>74</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>5.95</v>
+      </c>
+      <c r="K10" s="12">
+        <v>6</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>104</v>
+      </c>
+      <c r="T10" s="11">
+        <v>50</v>
+      </c>
+      <c r="U10" s="11">
+        <v>64</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>5.45</v>
+      </c>
+      <c r="W10" s="12">
+        <v>6</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -14626,45 +14728,73 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>40</v>
+      </c>
+      <c r="E11" s="11">
+        <v>40</v>
+      </c>
+      <c r="F11" s="11">
+        <v>80</v>
+      </c>
+      <c r="G11" s="11">
+        <v>95</v>
+      </c>
+      <c r="H11" s="11">
+        <v>95</v>
+      </c>
+      <c r="I11" s="11">
+        <v>170</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>40</v>
+      </c>
+      <c r="R11" s="11">
+        <v>80</v>
+      </c>
+      <c r="S11" s="11">
+        <v>60</v>
+      </c>
+      <c r="T11" s="11">
+        <v>60</v>
+      </c>
+      <c r="U11" s="11">
+        <v>120</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -14689,30 +14819,16 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>107</v>
-      </c>
-      <c r="P12" s="11">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>106</v>
-      </c>
-      <c r="R12" s="11">
-        <v>15</v>
-      </c>
-      <c r="S12" s="11">
-        <v>51</v>
-      </c>
-      <c r="T12" s="11">
-        <v>40</v>
-      </c>
-      <c r="U12" s="11">
-        <v>40</v>
-      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>9.2249999999999996</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
@@ -14721,11 +14837,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>9.2249999999999996</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-9.2249999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -14929,79 +15045,79 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1198</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>51</v>
+        <v>254</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>369</v>
+        <v>976</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>29.95</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>9.2249999999999996</v>
+        <v>24.4</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-9.2249999999999996</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15015,31 +15131,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.875</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.3250000000000002</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.125</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>29.95</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -15048,48 +15164,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>2.6749999999999998</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.65</v>
+        <v>1.875</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0.375</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>1.2749999999999999</v>
+        <v>6.35</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>4.95</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>9.2249999999999996</v>
+        <v>24.4</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.74875000000000003</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.230625</v>
+        <v>0.61</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-0.230625</v>
+        <v>0.13874999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -15375,17 +15491,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>126</v>
+      </c>
+      <c r="E8" s="11">
+        <v>116</v>
+      </c>
+      <c r="F8" s="11">
+        <v>183</v>
+      </c>
+      <c r="G8" s="11">
+        <v>102</v>
+      </c>
+      <c r="H8" s="11">
+        <v>126</v>
+      </c>
+      <c r="I8" s="11">
+        <v>142</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>19.875</v>
+      </c>
+      <c r="K8" s="12">
+        <v>19</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -15405,7 +15535,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>19.875</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -15413,7 +15543,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>19.875</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -15422,17 +15552,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>8</v>
+      </c>
+      <c r="E9" s="11">
+        <v>10</v>
+      </c>
+      <c r="F9" s="11">
+        <v>114</v>
+      </c>
+      <c r="G9" s="11">
+        <v>86</v>
+      </c>
+      <c r="H9" s="11">
+        <v>26</v>
+      </c>
+      <c r="I9" s="11">
+        <v>120</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>9.1</v>
+      </c>
+      <c r="K9" s="12">
+        <v>20</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -15452,7 +15596,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -15460,7 +15604,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -15469,17 +15613,31 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>4</v>
+      </c>
+      <c r="E10" s="11">
+        <v>4</v>
+      </c>
+      <c r="F10" s="11">
+        <v>16</v>
+      </c>
+      <c r="G10" s="11">
+        <v>115</v>
+      </c>
+      <c r="H10" s="11">
+        <v>65</v>
+      </c>
+      <c r="I10" s="11">
+        <v>61</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>6.625</v>
+      </c>
+      <c r="K10" s="12">
+        <v>8</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -15499,7 +15657,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.625</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -15507,7 +15665,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -15516,17 +15674,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>38</v>
+      </c>
+      <c r="E11" s="11">
+        <v>28</v>
+      </c>
+      <c r="F11" s="11">
+        <v>38</v>
+      </c>
+      <c r="G11" s="11">
+        <v>179</v>
+      </c>
+      <c r="H11" s="11">
+        <v>134</v>
+      </c>
+      <c r="I11" s="11">
+        <v>139</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>13.9</v>
+      </c>
+      <c r="K11" s="12">
+        <v>9</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -15546,7 +15718,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -15554,7 +15726,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -15579,30 +15751,16 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>26</v>
-      </c>
-      <c r="P12" s="11">
-        <v>12</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>20</v>
-      </c>
-      <c r="R12" s="11">
-        <v>12</v>
-      </c>
-      <c r="S12" s="11">
-        <v>20</v>
-      </c>
-      <c r="T12" s="11">
-        <v>6</v>
-      </c>
-      <c r="U12" s="11">
-        <v>12</v>
-      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
@@ -15611,11 +15769,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -15631,10 +15789,11 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="K13" s="12">
+        <v>5</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -15669,10 +15828,11 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="K14" s="12">
+        <v>14</v>
+      </c>
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
@@ -15707,10 +15867,11 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="K15" s="12">
+        <v>10</v>
+      </c>
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
@@ -15745,10 +15906,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="K16" s="12">
+        <v>8</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -15822,79 +15984,79 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-2.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15908,31 +16070,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.7750000000000004</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.05</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8.7750000000000004</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11.55</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>SUM(J8:J16)</f>
+        <v>141.5</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -15941,48 +16103,48 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>1.2375</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>6.7500000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-6.7500000000000004E-2</v>
+        <v>1.2375</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAA2206-4CED-4F01-BBEB-3F8FCD713499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCE0EFD-3659-4EA4-986B-BD87634ACDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="21" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="22" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="59">
   <si>
     <t>Booking</t>
   </si>
@@ -593,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -749,7 +749,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -758,6 +757,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -787,6 +787,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6606,28 +6615,28 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="74" t="s">
+      <c r="O10" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="74" t="s">
+      <c r="P10" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="Q10" s="74" t="s">
+      <c r="Q10" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="R10" s="74" t="s">
+      <c r="R10" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="S10" s="74" t="s">
+      <c r="S10" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="T10" s="74" t="s">
+      <c r="T10" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="U10" s="74" t="s">
+      <c r="U10" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="V10" s="75">
+      <c r="V10" s="74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13520,13 +13529,13 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
@@ -13537,14 +13546,14 @@
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="15">
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="75">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
@@ -13567,13 +13576,13 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J18" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
@@ -13584,14 +13593,14 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="15">
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="75">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
@@ -13614,13 +13623,13 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13631,14 +13640,14 @@
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="15">
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13661,13 +13670,13 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13678,14 +13687,14 @@
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15">
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13708,13 +13717,13 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13725,14 +13734,14 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15">
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13755,13 +13764,13 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13772,14 +13781,14 @@
       <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="15">
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13793,13 +13802,13 @@
       <c r="B14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
       <c r="J14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13810,14 +13819,14 @@
       <c r="N14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="15">
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13831,13 +13840,13 @@
       <c r="B15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
       <c r="J15" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13848,14 +13857,14 @@
       <c r="N15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="15">
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13869,13 +13878,13 @@
       <c r="B16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13886,14 +13895,14 @@
       <c r="N16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="15">
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13907,13 +13916,13 @@
       <c r="B17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
       <c r="J17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13923,14 +13932,14 @@
       <c r="N17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="15">
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -14034,31 +14043,31 @@
       <c r="K19" s="28"/>
       <c r="M19" s="1"/>
       <c r="N19" s="7"/>
-      <c r="O19" s="72">
+      <c r="O19" s="71">
         <f>SUM(O8:O18)</f>
         <v>0</v>
       </c>
-      <c r="P19" s="72">
+      <c r="P19" s="71">
         <f t="shared" ref="P19:U19" si="9">SUM(P8:P18)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="72">
+      <c r="Q19" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R19" s="72">
+      <c r="R19" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S19" s="72">
+      <c r="S19" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T19" s="72">
+      <c r="T19" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U19" s="72">
+      <c r="U19" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -14193,7 +14202,7 @@
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="X27" s="73">
+      <c r="X27" s="72">
         <f>SUM(X24:X26)</f>
         <v>59884</v>
       </c>
@@ -14803,16 +14812,15 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D12" s="86" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="88"/>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -14831,17 +14839,17 @@
         <v>0</v>
       </c>
       <c r="W12" s="12"/>
-      <c r="Y12" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="Y12" s="36" t="str">
+        <f>D12</f>
+        <v>Leave</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="38">
+      <c r="AA12" s="38" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -15115,9 +15123,9 @@
         <f>SUM(Z8:Z17)</f>
         <v>24.4</v>
       </c>
-      <c r="AA18" s="35">
+      <c r="AA18" s="35" t="e">
         <f>SUM(AA8:AA17)</f>
-        <v>5.55</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15203,13 +15211,14 @@
         <f>Z18/40</f>
         <v>0.61</v>
       </c>
-      <c r="AA19" s="41">
+      <c r="AA19" s="41" t="e">
         <f>AA18/40</f>
-        <v>0.13874999999999998</v>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="D12:J12"/>
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -15522,28 +15531,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>126</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>116</v>
+      </c>
+      <c r="R8" s="11">
+        <v>183</v>
+      </c>
+      <c r="S8" s="11">
+        <v>102</v>
+      </c>
+      <c r="T8" s="11">
+        <v>126</v>
+      </c>
+      <c r="U8" s="11">
+        <v>142</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>19.875</v>
+      </c>
+      <c r="W8" s="12">
+        <v>19</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>19.875</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>19.875</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>19.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -15644,28 +15667,42 @@
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>4</v>
+      </c>
+      <c r="R10" s="11">
+        <v>16</v>
+      </c>
+      <c r="S10" s="11">
+        <v>100</v>
+      </c>
+      <c r="T10" s="11">
+        <v>53</v>
+      </c>
+      <c r="U10" s="11">
+        <v>48</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>5.625</v>
+      </c>
+      <c r="W10" s="12">
+        <v>7</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>6.625</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.625</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>6.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -15734,17 +15771,16 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C12" s="86" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="88"/>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -15763,17 +15799,17 @@
         <v>0</v>
       </c>
       <c r="W12" s="12"/>
-      <c r="Y12" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="Y12" s="36" t="str">
+        <f>C12</f>
+        <v>Leave</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="38">
+      <c r="AA12" s="38" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -16019,31 +16055,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -16052,11 +16088,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="35">
+        <v>25.5</v>
+      </c>
+      <c r="AA18" s="35" t="e">
         <f>SUM(AA8:AA17)</f>
-        <v>49.5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16065,7 +16101,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
+        <f t="shared" ref="C19:I19" si="7">C18/40</f>
         <v>0</v>
       </c>
       <c r="D19" s="21">
@@ -16107,31 +16143,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.9749999999999996</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -16140,15 +16176,16 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="41">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="AA19" s="41" t="e">
         <f>AA18/40</f>
-        <v>1.2375</v>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="C12:J12"/>
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -16430,38 +16467,52 @@
       <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>40</v>
+      </c>
+      <c r="G8" s="11">
+        <v>60</v>
+      </c>
+      <c r="H8" s="11">
+        <v>60</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="12">
+        <v>17</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="71">
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -16469,7 +16520,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -16477,46 +16528,45 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
+      <c r="C9" s="86" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="88"/>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="71">
-        <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="15">
+        <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
       <c r="W9" s="12"/>
-      <c r="Y9" s="36">
-        <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+      <c r="Y9" s="36" t="str">
+        <f>C9</f>
+        <v>Leave</v>
       </c>
       <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
-      </c>
-      <c r="AA9" s="38">
-        <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <f t="shared" ref="Z9:Z17" si="1">V9</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="38" t="e">
+        <f t="shared" ref="AA9:AA17" si="2">Y9-Z9</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -16524,46 +16574,60 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11">
+        <v>40</v>
+      </c>
+      <c r="E10" s="11">
+        <v>18</v>
+      </c>
+      <c r="F10" s="11">
+        <v>40</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <f t="shared" ref="J10:J16" si="3">SUM(C10:I10)/40</f>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="K10" s="12">
+        <v>4</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="71">
-        <f t="shared" si="1"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
+        <f t="shared" ref="Y10:Y17" si="4">J10</f>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Z10" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -16571,46 +16635,60 @@
       <c r="B11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11">
+        <v>18</v>
+      </c>
+      <c r="E11" s="11">
+        <v>6</v>
+      </c>
+      <c r="F11" s="11">
+        <v>18</v>
+      </c>
+      <c r="G11" s="11">
+        <v>32</v>
+      </c>
+      <c r="H11" s="11">
+        <v>31</v>
+      </c>
+      <c r="I11" s="11">
+        <v>30</v>
+      </c>
       <c r="J11" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <f t="shared" si="3"/>
+        <v>3.375</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="71">
-        <f t="shared" si="1"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
+        <f t="shared" si="4"/>
+        <v>3.375</v>
+      </c>
+      <c r="Z11" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.375</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -16618,46 +16696,60 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11">
+        <v>16</v>
+      </c>
+      <c r="E12" s="11">
+        <v>73</v>
+      </c>
+      <c r="F12" s="11">
+        <v>55</v>
+      </c>
+      <c r="G12" s="11">
+        <v>72</v>
+      </c>
+      <c r="H12" s="11">
+        <v>62</v>
+      </c>
+      <c r="I12" s="11">
+        <v>66</v>
+      </c>
       <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <f t="shared" si="3"/>
+        <v>8.6</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="71">
-        <f t="shared" si="1"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
+        <f t="shared" si="4"/>
+        <v>8.6</v>
+      </c>
+      <c r="Z12" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -16665,32 +16757,46 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11">
+        <v>200</v>
+      </c>
+      <c r="E13" s="11">
+        <v>280</v>
+      </c>
+      <c r="F13" s="11">
+        <v>320</v>
+      </c>
+      <c r="G13" s="11">
+        <v>440</v>
+      </c>
+      <c r="H13" s="11">
+        <v>360</v>
+      </c>
+      <c r="I13" s="11">
+        <v>520</v>
+      </c>
       <c r="J13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="K13" s="12">
+        <v>3</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="71">
-        <f t="shared" si="1"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W13" s="12"/>
@@ -16703,15 +16809,15 @@
       <c r="B14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14" s="12"/>
@@ -16720,15 +16826,15 @@
       <c r="N14" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="71">
-        <f t="shared" si="1"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W14" s="12"/>
@@ -16741,15 +16847,15 @@
       <c r="B15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K15" s="12"/>
@@ -16758,15 +16864,15 @@
       <c r="N15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="71">
-        <f t="shared" si="1"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W15" s="12"/>
@@ -16779,15 +16885,15 @@
       <c r="B16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="12"/>
@@ -16796,15 +16902,15 @@
       <c r="N16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="71">
-        <f t="shared" si="1"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W16" s="12"/>
@@ -16815,36 +16921,36 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
       <c r="J17" s="15"/>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="71"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="15"/>
       <c r="W17" s="18"/>
       <c r="Y17" s="36">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="38">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="38">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -16857,31 +16963,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>2857</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -16921,15 +17027,15 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>18.424999999999997</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="35">
+      <c r="AA18" s="35" t="e">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -16943,31 +17049,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9.4250000000000007</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11.824999999999999</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.1</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.824999999999999</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>71.424999999999997</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -17009,19 +17115,20 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.46062499999999995</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="41">
+      <c r="AA19" s="41" t="e">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="C9:J9"/>
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -17507,30 +17614,16 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>70</v>
-      </c>
-      <c r="P12" s="11">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>20</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11">
-        <v>20</v>
-      </c>
-      <c r="T12" s="11">
-        <v>10</v>
-      </c>
-      <c r="U12" s="11">
-        <v>10</v>
-      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
@@ -17539,11 +17632,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -17716,30 +17809,16 @@
       <c r="N17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="O17" s="11">
-        <v>40</v>
-      </c>
-      <c r="P17" s="11">
-        <v>199</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>200</v>
-      </c>
-      <c r="R17" s="11">
-        <v>320</v>
-      </c>
-      <c r="S17" s="11">
-        <v>280</v>
-      </c>
-      <c r="T17" s="11">
-        <v>280</v>
-      </c>
-      <c r="U17" s="11">
-        <v>300</v>
-      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="15">
         <f t="shared" si="1"/>
-        <v>40.475000000000001</v>
+        <v>0</v>
       </c>
       <c r="W17" s="12">
         <v>5</v>
@@ -17750,11 +17829,11 @@
       </c>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>40.475000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="38">
         <f t="shared" si="4"/>
-        <v>-40.475000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
@@ -17797,35 +17876,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1759</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -17834,11 +17913,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>43.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-43.975000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17885,35 +17964,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>5.2249999999999996</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>43.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -17922,11 +18001,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>1.099375</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-1.099375</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCE0EFD-3659-4EA4-986B-BD87634ACDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C045A53-A33C-4C9F-81BA-B8455580F6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="22" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="23" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -15247,11 +15247,10 @@
     <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.453125" customWidth="1"/>
     <col min="25" max="25" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -15606,28 +15605,42 @@
         <v>14</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>90</v>
+      </c>
+      <c r="S9" s="11">
+        <v>76</v>
+      </c>
+      <c r="T9" s="11">
+        <v>26</v>
+      </c>
+      <c r="U9" s="11">
+        <v>89</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V13" si="1">SUM(O9:U9)/40</f>
+        <v>7.0250000000000004</v>
+      </c>
+      <c r="W9" s="12">
+        <v>18</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>9.1</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>7.0250000000000004</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>9.1</v>
+        <v>2.0749999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -15742,28 +15755,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>28</v>
+      </c>
+      <c r="R11" s="11">
+        <v>38</v>
+      </c>
+      <c r="S11" s="11">
+        <v>135</v>
+      </c>
+      <c r="T11" s="11">
+        <v>90</v>
+      </c>
+      <c r="U11" s="11">
+        <v>95</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>10.6</v>
+      </c>
+      <c r="W11" s="12">
+        <v>7</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>13.9</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>13.9</v>
+        <v>3.3000000000000007</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -15836,17 +15863,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>1553</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1517</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1947</v>
+      </c>
+      <c r="S13" s="11">
+        <v>1657</v>
+      </c>
+      <c r="T13" s="11">
+        <v>1600</v>
+      </c>
+      <c r="U13" s="11">
+        <v>2560</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>270.85000000000002</v>
+      </c>
+      <c r="W13" s="12">
+        <v>13</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -15882,10 +15923,11 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="W14" s="12">
+        <v>14</v>
+      </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
       <c r="AA14" s="38"/>
@@ -15921,10 +15963,11 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
       <c r="V15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="W15" s="12">
+        <v>10</v>
+      </c>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
       <c r="AA15" s="38"/>
@@ -15960,10 +16003,11 @@
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="W16" s="12">
+        <v>8</v>
+      </c>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
       <c r="AA16" s="38"/>
@@ -16055,31 +16099,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>130</v>
+        <v>1721</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>1665</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>199</v>
+        <v>2274</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>202</v>
+        <v>2070</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>179</v>
+        <v>1895</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>190</v>
+        <v>2934</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1020</v>
+        <v>12559</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -16088,7 +16132,7 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>25.5</v>
+        <v>43.125</v>
       </c>
       <c r="AA18" s="35" t="e">
         <f>SUM(AA8:AA17)</f>
@@ -16138,36 +16182,36 @@
         <v>18</v>
       </c>
       <c r="O19" s="21">
-        <f t="shared" ref="O19:V19" si="8">O18/40</f>
+        <f t="shared" ref="O19:U19" si="8">O18/40</f>
         <v>0</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>3.25</v>
+        <v>43.024999999999999</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>41.625</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>4.9749999999999996</v>
+        <v>56.85</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>5.05</v>
+        <v>51.75</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>4.4749999999999996</v>
+        <v>47.375</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>4.75</v>
+        <v>73.349999999999994</v>
       </c>
       <c r="V19" s="22">
-        <f t="shared" si="8"/>
-        <v>25.5</v>
+        <f>SUM(V8:V16)</f>
+        <v>349.97500000000002</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -16176,7 +16220,7 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.63749999999999996</v>
+        <v>1.078125</v>
       </c>
       <c r="AA19" s="41" t="e">
         <f>AA18/40</f>
@@ -16499,28 +16543,40 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>60</v>
+      </c>
+      <c r="T8" s="11">
+        <v>60</v>
+      </c>
       <c r="U8" s="11"/>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="W8" s="12">
+        <v>16</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>4</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -16544,14 +16600,14 @@
       <c r="N9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="15">
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="75">
         <f t="shared" ref="V9:V16" si="0">SUM(O9:U9)/40</f>
         <v>0</v>
       </c>
@@ -16606,28 +16662,42 @@
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>18</v>
+      </c>
+      <c r="R10" s="11">
+        <v>40</v>
+      </c>
+      <c r="S10" s="11">
+        <v>0</v>
+      </c>
+      <c r="T10" s="11">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11">
+        <v>0</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="W10" s="12">
+        <v>4</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" ref="Y10:Y17" si="4">J10</f>
         <v>2.4500000000000002</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="2"/>
-        <v>2.4500000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -16667,28 +16737,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>6</v>
+      </c>
+      <c r="R11" s="11">
+        <v>6</v>
+      </c>
+      <c r="S11" s="11">
+        <v>32</v>
+      </c>
+      <c r="T11" s="11">
+        <v>31</v>
+      </c>
+      <c r="U11" s="11">
+        <v>30</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="4"/>
         <v>3.375</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="2"/>
-        <v>3.375</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -16728,28 +16812,42 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>73</v>
+      </c>
+      <c r="R12" s="11">
+        <v>55</v>
+      </c>
+      <c r="S12" s="11">
+        <v>72</v>
+      </c>
+      <c r="T12" s="11">
+        <v>62</v>
+      </c>
+      <c r="U12" s="11">
+        <v>66</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>8.6</v>
+      </c>
+      <c r="W12" s="12">
+        <v>6</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="4"/>
         <v>8.6</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="2"/>
-        <v>8.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -16789,17 +16887,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>280</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>360</v>
+      </c>
+      <c r="R13" s="11">
+        <v>400</v>
+      </c>
+      <c r="S13" s="11">
+        <v>520</v>
+      </c>
+      <c r="T13" s="11">
+        <v>440</v>
+      </c>
+      <c r="U13" s="11">
+        <v>600</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>65</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -16998,31 +17110,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>3273</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -17031,7 +17143,7 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>16.824999999999999</v>
       </c>
       <c r="AA18" s="35" t="e">
         <f>SUM(AA8:AA17)</f>
@@ -17086,31 +17198,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12.525</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14.824999999999999</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>81.825000000000003</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -17119,7 +17231,7 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.42062499999999997</v>
       </c>
       <c r="AA19" s="41" t="e">
         <f>AA18/40</f>
@@ -17409,18 +17521,34 @@
       <c r="B8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="C8" s="11">
+        <v>17</v>
+      </c>
+      <c r="D8" s="11">
+        <v>60</v>
+      </c>
+      <c r="E8" s="11">
+        <v>60</v>
+      </c>
+      <c r="F8" s="11">
+        <v>80</v>
+      </c>
+      <c r="G8" s="11">
+        <v>90</v>
+      </c>
+      <c r="H8" s="11">
+        <v>100</v>
+      </c>
+      <c r="I8" s="11">
+        <v>170</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>14.425000000000001</v>
+      </c>
+      <c r="K8" s="12">
+        <v>9</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -17440,7 +17568,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>14.425000000000001</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -17448,7 +17576,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>14.425000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -17457,17 +17585,31 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>10</v>
+      </c>
+      <c r="F9" s="11">
+        <v>20</v>
+      </c>
+      <c r="G9" s="11">
+        <v>70</v>
+      </c>
+      <c r="H9" s="11">
+        <v>80</v>
+      </c>
+      <c r="I9" s="11">
+        <v>200</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>9.5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>21</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -17487,7 +17629,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -17495,7 +17637,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -17504,17 +17646,31 @@
         <v>42</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>29</v>
+      </c>
+      <c r="E10" s="11">
+        <v>24</v>
+      </c>
+      <c r="F10" s="11">
+        <v>67</v>
+      </c>
+      <c r="G10" s="11">
+        <v>39</v>
+      </c>
+      <c r="H10" s="11">
+        <v>34</v>
+      </c>
+      <c r="I10" s="11">
+        <v>87</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="K10" s="12">
+        <v>5</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -17534,7 +17690,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -17542,7 +17698,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -17551,17 +17707,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>52</v>
+      </c>
+      <c r="H11" s="11">
+        <v>40</v>
+      </c>
+      <c r="I11" s="11">
+        <v>52</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="K11" s="12">
+        <v>5</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -17581,7 +17751,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -17589,7 +17759,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -17598,17 +17768,31 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>12</v>
+      </c>
+      <c r="E12" s="11">
+        <v>37</v>
+      </c>
+      <c r="F12" s="11">
+        <v>36</v>
+      </c>
+      <c r="G12" s="11">
+        <v>40</v>
+      </c>
+      <c r="H12" s="11">
+        <v>37</v>
+      </c>
+      <c r="I12" s="11">
+        <v>10</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>4.3</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -17628,7 +17812,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -17636,7 +17820,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -17647,15 +17831,23 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="F13" s="11">
+        <v>400</v>
+      </c>
       <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="H13" s="11">
+        <v>800</v>
+      </c>
+      <c r="I13" s="11">
+        <v>400</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K13" s="12">
+        <v>1</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -17766,10 +17958,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="K16" s="12">
+        <v>9</v>
+      </c>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
@@ -17841,35 +18034,35 @@
       <c r="B18" s="7"/>
       <c r="C18" s="25">
         <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1091</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>919</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>3153</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -17909,7 +18102,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>38.824999999999996</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -17917,7 +18110,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>38.824999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -17927,35 +18120,35 @@
       </c>
       <c r="C19" s="21">
         <f t="shared" ref="C19:J19" si="7">C18/40</f>
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.5249999999999999</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.074999999999999</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.2750000000000004</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>27.274999999999999</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22.975000000000001</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>78.825000000000003</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -17997,7 +18190,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.97062499999999985</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -18005,7 +18198,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>0.97062499999999985</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C045A53-A33C-4C9F-81BA-B8455580F6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E759F8E-3024-43F8-A60A-CE73212C8C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="23" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="24" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -17554,29 +17554,45 @@
       <c r="N8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="O8" s="11">
+        <v>17</v>
+      </c>
+      <c r="P8" s="11">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>60</v>
+      </c>
+      <c r="R8" s="11">
+        <v>70</v>
+      </c>
+      <c r="S8" s="11">
+        <v>90</v>
+      </c>
+      <c r="T8" s="11">
+        <v>100</v>
+      </c>
+      <c r="U8" s="11">
+        <v>170</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>14.175000000000001</v>
+      </c>
+      <c r="W8" s="12">
+        <v>8</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>14.425000000000001</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>14.175000000000001</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>14.425000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -17604,7 +17620,7 @@
         <v>200</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J15" si="0">SUM(C9:I9)/40</f>
         <v>9.5</v>
       </c>
       <c r="K9" s="12">
@@ -17616,28 +17632,42 @@
         <v>41</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>9</v>
+      </c>
+      <c r="R9" s="11">
+        <v>20</v>
+      </c>
+      <c r="S9" s="11">
+        <v>70</v>
+      </c>
+      <c r="T9" s="11">
+        <v>78</v>
+      </c>
+      <c r="U9" s="11">
+        <v>189</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>9.15</v>
+      </c>
+      <c r="W9" s="12">
+        <v>21</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>9.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>9.5</v>
+        <v>0.34999999999999964</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -17677,28 +17707,42 @@
         <v>42</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>24</v>
+      </c>
+      <c r="R10" s="11">
+        <v>67</v>
+      </c>
+      <c r="S10" s="11">
+        <v>39</v>
+      </c>
+      <c r="T10" s="11">
+        <v>34</v>
+      </c>
+      <c r="U10" s="11">
+        <v>87</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -17738,28 +17782,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>52</v>
+      </c>
+      <c r="T11" s="11">
+        <v>40</v>
+      </c>
+      <c r="U11" s="11">
+        <v>52</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="W11" s="12">
+        <v>5</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>3.6</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -17799,28 +17857,42 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>25</v>
+      </c>
+      <c r="R12" s="11">
+        <v>24</v>
+      </c>
+      <c r="S12" s="11">
+        <v>28</v>
+      </c>
+      <c r="T12" s="11">
+        <v>37</v>
+      </c>
+      <c r="U12" s="11">
+        <v>10</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>3.4</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>4.3</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>4.3</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -18069,35 +18141,35 @@
       <c r="N18" s="7"/>
       <c r="O18" s="25">
         <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1493</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -18106,11 +18178,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>37.325000000000003</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>38.824999999999996</v>
+        <v>1.4999999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -18157,35 +18229,35 @@
       </c>
       <c r="O19" s="21">
         <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>0</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.5249999999999999</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.5250000000000004</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.9749999999999996</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7.2249999999999996</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37.325000000000003</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -18194,11 +18266,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.93312500000000009</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.97062499999999985</v>
+        <v>3.7499999999999992E-2</v>
       </c>
     </row>
   </sheetData>
@@ -18221,7 +18293,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -18485,17 +18557,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>20</v>
+      </c>
+      <c r="E8" s="11">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11">
+        <v>40</v>
+      </c>
+      <c r="G8" s="11">
+        <v>15</v>
+      </c>
+      <c r="H8" s="11">
+        <v>10</v>
+      </c>
+      <c r="I8" s="11">
+        <v>215</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="K8" s="12">
+        <v>7</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -18515,7 +18601,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -18523,7 +18609,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -18555,21 +18641,18 @@
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
-      <c r="V9" s="15">
-        <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
+      <c r="V9" s="15"/>
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
-        <f t="shared" ref="Y9:Y17" si="2">J9</f>
+        <f t="shared" ref="Y9:Y17" si="1">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z17" si="3">V9</f>
+        <f t="shared" ref="Z9:Z17" si="2">V9</f>
         <v>0</v>
       </c>
       <c r="AA9" s="38">
-        <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
+        <f t="shared" ref="AA9:AA17" si="3">Y9-Z9</f>
         <v>0</v>
       </c>
     </row>
@@ -18580,16 +18663,27 @@
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="E10" s="11">
+        <v>88</v>
+      </c>
+      <c r="F10" s="11">
+        <v>6</v>
+      </c>
+      <c r="G10" s="11">
+        <v>6</v>
+      </c>
+      <c r="H10" s="11">
+        <v>268</v>
+      </c>
+      <c r="I10" s="11">
+        <v>264</v>
+      </c>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>108</v>
+      </c>
+      <c r="K10" s="12">
+        <v>5</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -18602,22 +18696,19 @@
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
-      <c r="V10" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="V10" s="15"/>
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="Z10" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="AA10" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -18626,17 +18717,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>65</v>
+      </c>
+      <c r="E11" s="11">
+        <v>59</v>
+      </c>
+      <c r="F11" s="11">
+        <v>84</v>
+      </c>
+      <c r="G11" s="11">
+        <v>72</v>
+      </c>
+      <c r="H11" s="11">
+        <v>66</v>
+      </c>
+      <c r="I11" s="11">
+        <v>104</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>11.25</v>
+      </c>
+      <c r="K11" s="12">
+        <v>8</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -18649,22 +18754,19 @@
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
-      <c r="V11" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="V11" s="15"/>
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
+        <f t="shared" si="1"/>
+        <v>11.25</v>
+      </c>
+      <c r="Z11" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="AA11" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -18673,59 +18775,56 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>44</v>
+      </c>
+      <c r="E12" s="11">
+        <v>4</v>
+      </c>
+      <c r="F12" s="11">
+        <v>74</v>
+      </c>
+      <c r="G12" s="11">
+        <v>36</v>
+      </c>
+      <c r="H12" s="11">
+        <v>33</v>
+      </c>
+      <c r="I12" s="11">
+        <v>33</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>5.6</v>
+      </c>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>3</v>
-      </c>
-      <c r="P12" s="11">
-        <v>6</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>12</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11">
-        <v>22</v>
-      </c>
-      <c r="T12" s="11">
-        <v>10</v>
-      </c>
-      <c r="U12" s="11">
-        <v>0</v>
-      </c>
-      <c r="V12" s="15">
-        <f t="shared" si="1"/>
-        <v>1.325</v>
-      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="15"/>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
+        <f t="shared" si="1"/>
+        <v>5.6</v>
+      </c>
+      <c r="Z12" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="AA12" s="38">
         <f t="shared" si="3"/>
-        <v>1.325</v>
-      </c>
-      <c r="AA12" s="38">
-        <f t="shared" si="4"/>
-        <v>-1.325</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -18757,10 +18856,7 @@
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
-      <c r="V13" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="V13" s="15"/>
       <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
@@ -18795,10 +18891,7 @@
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
-      <c r="V14" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="V14" s="15"/>
       <c r="W14" s="12"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
@@ -18833,10 +18926,7 @@
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
-      <c r="V15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="V15" s="15"/>
       <c r="W15" s="12"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
@@ -18871,10 +18961,7 @@
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
-      <c r="V16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="V16" s="15"/>
       <c r="W16" s="12"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
@@ -18898,130 +18985,112 @@
       <c r="N17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="O17" s="11">
-        <f>41+160</f>
-        <v>201</v>
-      </c>
-      <c r="P17" s="11">
-        <v>200</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>121</v>
-      </c>
-      <c r="R17" s="11">
-        <v>440</v>
-      </c>
-      <c r="S17" s="11">
-        <v>181</v>
-      </c>
-      <c r="T17" s="11">
-        <v>140</v>
-      </c>
-      <c r="U17" s="11">
-        <v>560</v>
-      </c>
-      <c r="V17" s="15">
-        <f t="shared" si="1"/>
-        <v>46.075000000000003</v>
-      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="15"/>
       <c r="W17" s="18">
         <v>6</v>
       </c>
       <c r="Y17" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="AA17" s="38">
         <f t="shared" si="3"/>
-        <v>46.075000000000003</v>
-      </c>
-      <c r="AA17" s="38">
-        <f t="shared" si="4"/>
-        <v>-46.075000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
       <c r="C18" s="25">
-        <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
+        <f t="shared" ref="C18:I18" si="4">SUM(C8:C17)</f>
         <v>0</v>
       </c>
       <c r="D18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>129</v>
       </c>
       <c r="E18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>171</v>
       </c>
       <c r="F18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>204</v>
       </c>
       <c r="G18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>129</v>
       </c>
       <c r="H18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>377</v>
       </c>
       <c r="I18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>616</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1626</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
-        <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
-        <v>204</v>
+        <f t="shared" ref="O18:U18" si="5">SUM(O8:O17)</f>
+        <v>0</v>
       </c>
       <c r="P18" s="25">
-        <f t="shared" si="6"/>
-        <v>206</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="Q18" s="25">
-        <f t="shared" si="6"/>
-        <v>133</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="R18" s="25">
-        <f t="shared" si="6"/>
-        <v>440</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="S18" s="25">
-        <f t="shared" si="6"/>
-        <v>203</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="T18" s="25">
-        <f t="shared" si="6"/>
-        <v>150</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="U18" s="25">
-        <f t="shared" si="6"/>
-        <v>560</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1896</v>
+        <v>0</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>132.85</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>47.400000000000006</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>-47.400000000000006</v>
+        <v>132.85</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19030,36 +19099,36 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="7">C18/40</f>
+        <f t="shared" ref="C19:J19" si="6">C18/40</f>
         <v>0</v>
       </c>
       <c r="D19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>3.2250000000000001</v>
       </c>
       <c r="E19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>4.2750000000000004</v>
       </c>
       <c r="F19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>3.2250000000000001</v>
       </c>
       <c r="H19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>9.4250000000000007</v>
       </c>
       <c r="I19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>15.4</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>40.65</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -19067,49 +19136,49 @@
         <v>18</v>
       </c>
       <c r="O19" s="21">
-        <f t="shared" ref="O19:V19" si="8">O18/40</f>
-        <v>5.0999999999999996</v>
+        <f t="shared" ref="O19:V19" si="7">O18/40</f>
+        <v>0</v>
       </c>
       <c r="P19" s="21">
-        <f t="shared" si="8"/>
-        <v>5.15</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="Q19" s="21">
-        <f t="shared" si="8"/>
-        <v>3.3250000000000002</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="R19" s="21">
-        <f t="shared" si="8"/>
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="S19" s="21">
-        <f t="shared" si="8"/>
-        <v>5.0750000000000002</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="T19" s="21">
-        <f t="shared" si="8"/>
-        <v>3.75</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="U19" s="21">
-        <f t="shared" si="8"/>
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="V19" s="22">
-        <f t="shared" si="8"/>
-        <v>47.4</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>3.32125</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>1.1850000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>-1.1850000000000001</v>
+        <v>3.32125</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E759F8E-3024-43F8-A60A-CE73212C8C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6540B9F9-97C9-412F-ABE7-6F3990B1A5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="24" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="25" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -17926,17 +17926,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>120</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>120</v>
+      </c>
+      <c r="R13" s="11">
+        <v>520</v>
+      </c>
+      <c r="S13" s="11">
+        <v>120</v>
+      </c>
+      <c r="T13" s="11">
+        <v>920</v>
+      </c>
+      <c r="U13" s="11">
+        <v>560</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>59</v>
+      </c>
+      <c r="W13" s="12">
+        <v>3</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -18145,31 +18159,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>101</v>
+        <v>221</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>118</v>
+        <v>238</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>181</v>
+        <v>701</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>279</v>
+        <v>399</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>289</v>
+        <v>1209</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>508</v>
+        <v>1068</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1493</v>
+        <v>3853</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -18233,31 +18247,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>2.5249999999999999</v>
+        <v>5.5250000000000004</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.95</v>
+        <v>5.95</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>4.5250000000000004</v>
+        <v>17.524999999999999</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>6.9749999999999996</v>
+        <v>9.9749999999999996</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>7.2249999999999996</v>
+        <v>30.225000000000001</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>12.7</v>
+        <v>26.7</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>37.325000000000003</v>
+        <v>96.325000000000003</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -18588,28 +18602,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>20</v>
+      </c>
+      <c r="R8" s="11">
+        <v>40</v>
+      </c>
+      <c r="S8" s="11">
+        <v>15</v>
+      </c>
+      <c r="T8" s="11">
+        <v>10</v>
+      </c>
+      <c r="U8" s="11">
+        <v>215</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="W8" s="12">
+        <v>7</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>8</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -18618,12 +18646,12 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
@@ -18635,24 +18663,27 @@
         <v>41</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="15"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="15">
+        <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
+        <v>0</v>
+      </c>
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
-        <f t="shared" ref="Y9:Y17" si="1">J9</f>
+        <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
-        <f t="shared" ref="Z9:Z17" si="2">V9</f>
+        <f t="shared" ref="Z9:Z17" si="3">V9</f>
         <v>0</v>
       </c>
       <c r="AA9" s="38">
-        <f t="shared" ref="AA9:AA17" si="3">Y9-Z9</f>
+        <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
         <v>0</v>
       </c>
     </row>
@@ -18679,7 +18710,8 @@
         <v>264</v>
       </c>
       <c r="J10" s="15">
-        <v>108</v>
+        <f t="shared" si="0"/>
+        <v>15.8</v>
       </c>
       <c r="K10" s="12">
         <v>5</v>
@@ -18690,25 +18722,42 @@
         <v>42</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="12"/>
+      <c r="P10" s="11">
+        <v>88</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>6</v>
+      </c>
+      <c r="R10" s="11">
+        <v>6</v>
+      </c>
+      <c r="S10" s="11">
+        <v>268</v>
+      </c>
+      <c r="T10" s="11">
+        <v>264</v>
+      </c>
+      <c r="U10" s="11">
+        <v>108</v>
+      </c>
+      <c r="V10" s="15">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="36">
-        <f t="shared" si="1"/>
-        <v>108</v>
+        <f t="shared" si="2"/>
+        <v>15.8</v>
       </c>
       <c r="Z10" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>18.5</v>
       </c>
       <c r="AA10" s="38">
-        <f t="shared" si="3"/>
-        <v>108</v>
+        <f t="shared" si="4"/>
+        <v>-2.6999999999999993</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -18748,25 +18797,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="12"/>
+      <c r="P11" s="11">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>59</v>
+      </c>
+      <c r="R11" s="11">
+        <v>84</v>
+      </c>
+      <c r="S11" s="11">
+        <v>72</v>
+      </c>
+      <c r="T11" s="11">
+        <v>66</v>
+      </c>
+      <c r="U11" s="11">
+        <v>80</v>
+      </c>
+      <c r="V11" s="15">
+        <f t="shared" si="1"/>
+        <v>10.65</v>
+      </c>
+      <c r="W11" s="12">
+        <v>6</v>
+      </c>
       <c r="Y11" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.25</v>
       </c>
       <c r="Z11" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>10.65</v>
       </c>
       <c r="AA11" s="38">
-        <f t="shared" si="3"/>
-        <v>11.25</v>
+        <f t="shared" si="4"/>
+        <v>0.59999999999999964</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -18806,25 +18872,42 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="12"/>
+      <c r="P12" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>64</v>
+      </c>
+      <c r="S12" s="11">
+        <v>36</v>
+      </c>
+      <c r="T12" s="11">
+        <v>33</v>
+      </c>
+      <c r="U12" s="11">
+        <v>33</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="1"/>
+        <v>5.15</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.6</v>
       </c>
       <c r="Z12" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>5.15</v>
       </c>
       <c r="AA12" s="38">
-        <f t="shared" si="3"/>
-        <v>5.6</v>
+        <f t="shared" si="4"/>
+        <v>0.44999999999999929</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -18856,7 +18939,10 @@
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
-      <c r="V13" s="15"/>
+      <c r="V13" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="W13" s="12"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
@@ -18891,7 +18977,10 @@
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
-      <c r="V14" s="15"/>
+      <c r="V14" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="W14" s="12"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
@@ -18926,7 +19015,10 @@
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
-      <c r="V15" s="15"/>
+      <c r="V15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="W15" s="12"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="37"/>
@@ -18961,7 +19053,10 @@
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
-      <c r="V16" s="15"/>
+      <c r="V16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="W16" s="12"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
@@ -18992,20 +19087,21 @@
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="18">
-        <v>6</v>
-      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="18"/>
       <c r="Y17" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z17" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA17" s="38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -19013,31 +19109,31 @@
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
       <c r="C18" s="25">
-        <f t="shared" ref="C18:I18" si="4">SUM(C8:C17)</f>
+        <f t="shared" ref="C18:I18" si="5">SUM(C8:C17)</f>
         <v>0</v>
       </c>
       <c r="D18" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>129</v>
       </c>
       <c r="E18" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>171</v>
       </c>
       <c r="F18" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>204</v>
       </c>
       <c r="G18" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>129</v>
       </c>
       <c r="H18" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>377</v>
       </c>
       <c r="I18" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>616</v>
       </c>
       <c r="J18" s="26">
@@ -19048,49 +19144,49 @@
       <c r="M18" s="1"/>
       <c r="N18" s="7"/>
       <c r="O18" s="25">
-        <f t="shared" ref="O18:U18" si="5">SUM(O8:O17)</f>
+        <f t="shared" ref="O18:U18" si="6">SUM(O8:O17)</f>
         <v>0</v>
       </c>
       <c r="P18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>213</v>
       </c>
       <c r="Q18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>85</v>
       </c>
       <c r="R18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>194</v>
       </c>
       <c r="S18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>391</v>
       </c>
       <c r="T18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>373</v>
       </c>
       <c r="U18" s="25">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>436</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>1692</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>132.85</v>
+        <v>40.65</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>42.3</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>132.85</v>
+        <v>-1.6500000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19099,35 +19195,35 @@
         <v>18</v>
       </c>
       <c r="C19" s="21">
-        <f t="shared" ref="C19:J19" si="6">C18/40</f>
+        <f t="shared" ref="C19:J19" si="7">C18/40</f>
         <v>0</v>
       </c>
       <c r="D19" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.2250000000000001</v>
       </c>
       <c r="E19" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.2750000000000004</v>
       </c>
       <c r="F19" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="G19" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.2250000000000001</v>
       </c>
       <c r="H19" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.4250000000000007</v>
       </c>
       <c r="I19" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15.4</v>
       </c>
       <c r="J19" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40.65</v>
       </c>
       <c r="K19" s="23"/>
@@ -19136,49 +19232,49 @@
         <v>18</v>
       </c>
       <c r="O19" s="21">
-        <f t="shared" ref="O19:V19" si="7">O18/40</f>
+        <f t="shared" ref="O19:V19" si="8">O18/40</f>
         <v>0</v>
       </c>
       <c r="P19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>5.3250000000000002</v>
       </c>
       <c r="Q19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>2.125</v>
       </c>
       <c r="R19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>4.8499999999999996</v>
       </c>
       <c r="S19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>9.7750000000000004</v>
       </c>
       <c r="T19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>9.3249999999999993</v>
       </c>
       <c r="U19" s="21">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>10.9</v>
       </c>
       <c r="V19" s="22">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>42.3</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>3.32125</v>
+        <v>1.0162499999999999</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>1.0574999999999999</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>3.32125</v>
+        <v>-4.1250000000000009E-2</v>
       </c>
     </row>
   </sheetData>
@@ -19465,17 +19561,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>15</v>
+      </c>
+      <c r="E8" s="11">
+        <v>55</v>
+      </c>
+      <c r="F8" s="11">
+        <v>102</v>
+      </c>
+      <c r="G8" s="11">
+        <v>42</v>
+      </c>
+      <c r="H8" s="11">
+        <v>70</v>
+      </c>
+      <c r="I8" s="11">
+        <v>192</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>11.9</v>
+      </c>
+      <c r="K8" s="12">
+        <v>21</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -19495,7 +19605,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -19503,7 +19613,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -19559,17 +19669,31 @@
         <v>15</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>15</v>
+      </c>
+      <c r="E10" s="11">
+        <v>12</v>
+      </c>
+      <c r="F10" s="11">
+        <v>13</v>
+      </c>
+      <c r="G10" s="11">
+        <v>93</v>
+      </c>
+      <c r="H10" s="11">
+        <v>93</v>
+      </c>
+      <c r="I10" s="11">
+        <v>92</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>7.95</v>
+      </c>
+      <c r="K10" s="12">
+        <v>8</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -19589,7 +19713,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -19597,7 +19721,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -19606,17 +19730,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>34</v>
+      </c>
+      <c r="E11" s="11">
+        <v>13</v>
+      </c>
+      <c r="F11" s="11">
+        <v>33</v>
+      </c>
+      <c r="G11" s="11">
+        <v>27</v>
+      </c>
+      <c r="H11" s="11">
+        <v>10</v>
+      </c>
+      <c r="I11" s="11">
+        <v>67</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K11" s="12">
+        <v>7</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -19636,7 +19774,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -19644,7 +19782,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -19653,17 +19791,31 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>60</v>
+      </c>
+      <c r="E12" s="11">
+        <v>20</v>
+      </c>
+      <c r="F12" s="11">
+        <v>84</v>
+      </c>
+      <c r="G12" s="11">
+        <v>56</v>
+      </c>
+      <c r="H12" s="11">
+        <v>53</v>
+      </c>
+      <c r="I12" s="11">
+        <v>53</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>8.15</v>
+      </c>
+      <c r="K12" s="12">
+        <v>8</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -19683,7 +19835,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -19691,7 +19843,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -19891,31 +20043,31 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="G18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="I18" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="J18" s="26">
         <f>SUM(C18:I18)</f>
-        <v>0</v>
+        <v>1304</v>
       </c>
       <c r="K18" s="28"/>
       <c r="M18" s="1"/>
@@ -19955,7 +20107,7 @@
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>32.6</v>
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -19963,7 +20115,7 @@
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19977,31 +20129,31 @@
       </c>
       <c r="D19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="G19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="I19" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>32.6</v>
       </c>
       <c r="K19" s="23"/>
       <c r="M19" s="1"/>
@@ -20043,7 +20195,7 @@
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
         <f>Y18/40</f>
-        <v>0</v>
+        <v>0.81500000000000006</v>
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
@@ -20051,7 +20203,7 @@
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0</v>
+        <v>0.81500000000000006</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6540B9F9-97C9-412F-ABE7-6F3990B1A5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568099E7-34C8-4ED2-8E57-5E3DBED2752E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="25" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -18933,17 +18933,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>560</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>600</v>
+      </c>
+      <c r="R13" s="11">
+        <v>640</v>
+      </c>
+      <c r="S13" s="11">
+        <v>760</v>
+      </c>
+      <c r="T13" s="11">
+        <v>760</v>
+      </c>
+      <c r="U13" s="11">
+        <v>920</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>106</v>
+      </c>
+      <c r="W13" s="12">
+        <v>5</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -19149,31 +19163,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>213</v>
+        <v>773</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>85</v>
+        <v>685</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>194</v>
+        <v>834</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>391</v>
+        <v>1151</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>373</v>
+        <v>1133</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>436</v>
+        <v>1356</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>1692</v>
+        <v>5932</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -19237,31 +19251,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>5.3250000000000002</v>
+        <v>19.324999999999999</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>2.125</v>
+        <v>17.125</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>4.8499999999999996</v>
+        <v>20.85</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>9.7750000000000004</v>
+        <v>28.774999999999999</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>9.3249999999999993</v>
+        <v>28.324999999999999</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>10.9</v>
+        <v>33.9</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>42.3</v>
+        <v>148.30000000000001</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -19822,15 +19836,27 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>32</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>43</v>
+      </c>
+      <c r="R12" s="11">
+        <v>59</v>
+      </c>
+      <c r="S12" s="11">
+        <v>93</v>
+      </c>
+      <c r="T12" s="11">
+        <v>60</v>
+      </c>
+      <c r="U12" s="11">
+        <v>67</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
@@ -19839,11 +19865,11 @@
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>8.15</v>
+        <v>-0.69999999999999929</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -20078,31 +20104,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -20111,11 +20137,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>32.6</v>
+        <v>23.750000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20166,31 +20192,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.075</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.3250000000000002</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.675</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -20199,11 +20225,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0</v>
+        <v>0.22125</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.81500000000000006</v>
+        <v>0.59375000000000011</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568099E7-34C8-4ED2-8E57-5E3DBED2752E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74495F96-3A08-409B-9A3A-3C9BBE9C700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="25" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="26" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -19606,28 +19606,42 @@
         <v>13</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>55</v>
+      </c>
+      <c r="R8" s="11">
+        <v>102</v>
+      </c>
+      <c r="S8" s="11">
+        <v>42</v>
+      </c>
+      <c r="T8" s="11">
+        <v>70</v>
+      </c>
+      <c r="U8" s="11">
+        <v>192</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>11.9</v>
+      </c>
+      <c r="W8" s="12">
+        <v>21</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>11.9</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>11.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -19714,28 +19728,42 @@
         <v>15</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>12</v>
+      </c>
+      <c r="R10" s="11">
+        <v>13</v>
+      </c>
+      <c r="S10" s="11">
+        <v>86</v>
+      </c>
+      <c r="T10" s="11">
+        <v>87</v>
+      </c>
+      <c r="U10" s="11">
+        <v>85</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>7.45</v>
+      </c>
+      <c r="W10" s="12">
+        <v>8</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>7.95</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>7.95</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -19775,28 +19803,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>20</v>
+      </c>
+      <c r="S11" s="11">
+        <v>27</v>
+      </c>
+      <c r="T11" s="11">
+        <v>10</v>
+      </c>
+      <c r="U11" s="11">
+        <v>67</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>3.6</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>4.5999999999999996</v>
+        <v>0.99999999999999956</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -19858,7 +19900,9 @@
         <f t="shared" si="1"/>
         <v>8.85</v>
       </c>
-      <c r="W12" s="12"/>
+      <c r="W12" s="12">
+        <v>8</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>8.15</v>
@@ -19895,17 +19939,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>40</v>
+      </c>
+      <c r="R13" s="11">
+        <v>40</v>
+      </c>
+      <c r="S13" s="11">
+        <v>40</v>
+      </c>
+      <c r="T13" s="11">
+        <v>40</v>
+      </c>
+      <c r="U13" s="11">
+        <v>40</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W13" s="12">
+        <v>1</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -20104,31 +20162,31 @@
       </c>
       <c r="P18" s="25">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="Q18" s="25">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="R18" s="25">
         <f t="shared" si="6"/>
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>93</v>
+        <v>288</v>
       </c>
       <c r="T18" s="25">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>267</v>
       </c>
       <c r="U18" s="25">
         <f t="shared" si="6"/>
-        <v>67</v>
+        <v>451</v>
       </c>
       <c r="V18" s="26">
         <f>SUM(O18:U18)</f>
-        <v>354</v>
+        <v>1512</v>
       </c>
       <c r="W18" s="28"/>
       <c r="Y18" s="33">
@@ -20137,11 +20195,11 @@
       </c>
       <c r="Z18" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>8.85</v>
+        <v>31.800000000000004</v>
       </c>
       <c r="AA18" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>23.750000000000004</v>
+        <v>0.80000000000000027</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20192,31 +20250,31 @@
       </c>
       <c r="P19" s="21">
         <f t="shared" si="8"/>
-        <v>0.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q19" s="21">
         <f t="shared" si="8"/>
-        <v>1.075</v>
+        <v>3.75</v>
       </c>
       <c r="R19" s="21">
         <f t="shared" si="8"/>
-        <v>1.4750000000000001</v>
+        <v>5.85</v>
       </c>
       <c r="S19" s="21">
         <f t="shared" si="8"/>
-        <v>2.3250000000000002</v>
+        <v>7.2</v>
       </c>
       <c r="T19" s="21">
         <f t="shared" si="8"/>
-        <v>1.5</v>
+        <v>6.6749999999999998</v>
       </c>
       <c r="U19" s="21">
         <f t="shared" si="8"/>
-        <v>1.675</v>
+        <v>11.275</v>
       </c>
       <c r="V19" s="22">
         <f t="shared" si="8"/>
-        <v>8.85</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="W19" s="23"/>
       <c r="Y19" s="39">
@@ -20225,11 +20283,11 @@
       </c>
       <c r="Z19" s="40">
         <f>Z18/40</f>
-        <v>0.22125</v>
+        <v>0.79500000000000015</v>
       </c>
       <c r="AA19" s="41">
         <f>AA18/40</f>
-        <v>0.59375000000000011</v>
+        <v>2.0000000000000007E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20255,8 +20313,7 @@
     <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.36328125" bestFit="1" customWidth="1"/>
@@ -20518,14 +20575,22 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="G8" s="11">
+        <v>800</v>
+      </c>
+      <c r="H8" s="11">
+        <v>720</v>
+      </c>
+      <c r="I8" s="11">
+        <v>880</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="K8" s="12">
+        <v>1</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -20545,7 +20610,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -20553,7 +20618,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -20562,17 +20627,31 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>105</v>
+      </c>
+      <c r="E9" s="11">
+        <v>80</v>
+      </c>
+      <c r="F9" s="11">
+        <v>65</v>
+      </c>
+      <c r="G9" s="11">
+        <v>60</v>
+      </c>
+      <c r="H9" s="11">
+        <v>20</v>
+      </c>
+      <c r="I9" s="11">
+        <v>50</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>9.5</v>
+      </c>
+      <c r="K9" s="12">
+        <v>19</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -20592,7 +20671,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y20" si="2">J9</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z20" si="3">V9</f>
@@ -20600,7 +20679,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA20" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -20609,17 +20688,31 @@
         <v>42</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11">
+        <v>25</v>
+      </c>
+      <c r="F10" s="11">
+        <v>105</v>
+      </c>
+      <c r="G10" s="11">
+        <v>227</v>
+      </c>
+      <c r="H10" s="11">
+        <v>164</v>
+      </c>
+      <c r="I10" s="11">
+        <v>125</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>16.8</v>
+      </c>
+      <c r="K10" s="12">
+        <v>9</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -20639,7 +20732,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -20647,7 +20740,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -20656,17 +20749,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>40</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>40</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="K11" s="12">
+        <v>1</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -20686,7 +20793,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -20694,7 +20801,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -20703,17 +20810,31 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>40</v>
+      </c>
+      <c r="E12" s="11">
+        <v>28</v>
+      </c>
+      <c r="F12" s="11">
+        <v>34</v>
+      </c>
+      <c r="G12" s="11">
+        <v>80</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>80</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>6.55</v>
+      </c>
+      <c r="K12" s="12">
+        <v>4</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -20733,7 +20854,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -20741,7 +20862,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -20750,17 +20871,31 @@
         <v>16</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="D13" s="11">
+        <v>840</v>
+      </c>
+      <c r="E13" s="11">
+        <v>680</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1040</v>
+      </c>
+      <c r="G13" s="11">
+        <v>760</v>
+      </c>
+      <c r="H13" s="11">
+        <v>640</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1000</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>124</v>
+      </c>
+      <c r="K13" s="12">
+        <v>9</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -21034,31 +21169,31 @@
       </c>
       <c r="D21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="F21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="G21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1967</v>
       </c>
       <c r="H21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1544</v>
       </c>
       <c r="I21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2175</v>
       </c>
       <c r="J21" s="26">
         <f>SUM(C21:I21)</f>
-        <v>0</v>
+        <v>8754</v>
       </c>
       <c r="K21" s="28"/>
       <c r="M21" s="1"/>
@@ -21098,7 +21233,7 @@
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
         <f>SUM(Y8:Y20)</f>
-        <v>0</v>
+        <v>94.85</v>
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z20)</f>
@@ -21106,7 +21241,7 @@
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA20)</f>
-        <v>0</v>
+        <v>94.85</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21120,31 +21255,31 @@
       </c>
       <c r="D22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>25.274999999999999</v>
       </c>
       <c r="E22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20.324999999999999</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>49.174999999999997</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>38.6</v>
       </c>
       <c r="I22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>54.375</v>
       </c>
       <c r="J22" s="22">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>218.85</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1"/>
@@ -21186,7 +21321,7 @@
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
         <f>Y21/40</f>
-        <v>0</v>
+        <v>2.3712499999999999</v>
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
@@ -21194,7 +21329,7 @@
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>0</v>
+        <v>2.3712499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74495F96-3A08-409B-9A3A-3C9BBE9C700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6960D3-7DB1-4C10-A60D-241880DFA654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="26" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="28" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -20575,18 +20575,12 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="11">
-        <v>800</v>
-      </c>
-      <c r="H8" s="11">
-        <v>720</v>
-      </c>
-      <c r="I8" s="11">
-        <v>880</v>
-      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K8" s="12">
         <v>1</v>
@@ -20610,7 +20604,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -20618,7 +20612,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -20627,27 +20621,15 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11">
-        <v>105</v>
-      </c>
-      <c r="E9" s="11">
-        <v>80</v>
-      </c>
-      <c r="F9" s="11">
-        <v>65</v>
-      </c>
-      <c r="G9" s="11">
-        <v>60</v>
-      </c>
-      <c r="H9" s="11">
-        <v>20</v>
-      </c>
-      <c r="I9" s="11">
-        <v>50</v>
-      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="K9" s="12">
         <v>19</v>
@@ -20671,7 +20653,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y20" si="2">J9</f>
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z20" si="3">V9</f>
@@ -20679,7 +20661,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA20" si="4">Y9-Z9</f>
-        <v>9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -20688,27 +20670,15 @@
         <v>42</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11">
-        <v>26</v>
-      </c>
-      <c r="E10" s="11">
-        <v>25</v>
-      </c>
-      <c r="F10" s="11">
-        <v>105</v>
-      </c>
-      <c r="G10" s="11">
-        <v>227</v>
-      </c>
-      <c r="H10" s="11">
-        <v>164</v>
-      </c>
-      <c r="I10" s="11">
-        <v>125</v>
-      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="K10" s="12">
         <v>9</v>
@@ -20732,7 +20702,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -20740,7 +20710,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>16.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -20749,27 +20719,15 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11">
-        <v>40</v>
-      </c>
-      <c r="H11" s="11">
-        <v>0</v>
-      </c>
-      <c r="I11" s="11">
-        <v>40</v>
-      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12">
         <v>1</v>
@@ -20793,7 +20751,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -20801,7 +20759,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -20810,27 +20768,15 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11">
-        <v>40</v>
-      </c>
-      <c r="E12" s="11">
-        <v>28</v>
-      </c>
-      <c r="F12" s="11">
-        <v>34</v>
-      </c>
-      <c r="G12" s="11">
-        <v>80</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0</v>
-      </c>
-      <c r="I12" s="11">
-        <v>80</v>
-      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12">
         <v>4</v>
@@ -20854,7 +20800,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -20862,7 +20808,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -20871,27 +20817,15 @@
         <v>16</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11">
-        <v>840</v>
-      </c>
-      <c r="E13" s="11">
-        <v>680</v>
-      </c>
-      <c r="F13" s="11">
-        <v>1040</v>
-      </c>
-      <c r="G13" s="11">
-        <v>760</v>
-      </c>
-      <c r="H13" s="11">
-        <v>640</v>
-      </c>
-      <c r="I13" s="11">
-        <v>1000</v>
-      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12">
         <v>9</v>
@@ -21169,31 +21103,31 @@
       </c>
       <c r="D21" s="25">
         <f t="shared" si="5"/>
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="5"/>
-        <v>813</v>
+        <v>0</v>
       </c>
       <c r="F21" s="25">
         <f t="shared" si="5"/>
-        <v>1244</v>
+        <v>0</v>
       </c>
       <c r="G21" s="25">
         <f t="shared" si="5"/>
-        <v>1967</v>
+        <v>0</v>
       </c>
       <c r="H21" s="25">
         <f t="shared" si="5"/>
-        <v>1544</v>
+        <v>0</v>
       </c>
       <c r="I21" s="25">
         <f t="shared" si="5"/>
-        <v>2175</v>
+        <v>0</v>
       </c>
       <c r="J21" s="26">
         <f>SUM(C21:I21)</f>
-        <v>8754</v>
+        <v>0</v>
       </c>
       <c r="K21" s="28"/>
       <c r="M21" s="1"/>
@@ -21233,7 +21167,7 @@
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
         <f>SUM(Y8:Y20)</f>
-        <v>94.85</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z20)</f>
@@ -21241,7 +21175,7 @@
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA20)</f>
-        <v>94.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21255,31 +21189,31 @@
       </c>
       <c r="D22" s="21">
         <f t="shared" si="7"/>
-        <v>25.274999999999999</v>
+        <v>0</v>
       </c>
       <c r="E22" s="21">
         <f t="shared" si="7"/>
-        <v>20.324999999999999</v>
+        <v>0</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" si="7"/>
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="7"/>
-        <v>49.174999999999997</v>
+        <v>0</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="7"/>
-        <v>38.6</v>
+        <v>0</v>
       </c>
       <c r="I22" s="21">
         <f t="shared" si="7"/>
-        <v>54.375</v>
+        <v>0</v>
       </c>
       <c r="J22" s="22">
         <f t="shared" si="7"/>
-        <v>218.85</v>
+        <v>0</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1"/>
@@ -21321,7 +21255,7 @@
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
         <f>Y21/40</f>
-        <v>2.3712499999999999</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
@@ -21329,7 +21263,7 @@
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>2.3712499999999999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21619,12 +21553,18 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="G8" s="11">
+        <v>800</v>
+      </c>
+      <c r="H8" s="11">
+        <v>720</v>
+      </c>
+      <c r="I8" s="11">
+        <v>880</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="13"/>
@@ -21646,7 +21586,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -21654,7 +21594,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -21663,15 +21603,27 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>105</v>
+      </c>
+      <c r="E9" s="11">
+        <v>80</v>
+      </c>
+      <c r="F9" s="11">
+        <v>65</v>
+      </c>
+      <c r="G9" s="11">
+        <v>60</v>
+      </c>
+      <c r="H9" s="11">
+        <v>20</v>
+      </c>
+      <c r="I9" s="11">
+        <v>50</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
@@ -21693,7 +21645,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
@@ -21701,7 +21653,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -21710,15 +21662,27 @@
         <v>42</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11">
+        <v>25</v>
+      </c>
+      <c r="F10" s="11">
+        <v>105</v>
+      </c>
+      <c r="G10" s="11">
+        <v>227</v>
+      </c>
+      <c r="H10" s="11">
+        <v>164</v>
+      </c>
+      <c r="I10" s="11">
+        <v>125</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="13"/>
@@ -21740,7 +21704,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -21748,7 +21712,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -21757,15 +21721,27 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>40</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>40</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="13"/>
@@ -21787,7 +21763,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -21795,7 +21771,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -21804,15 +21780,27 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>40</v>
+      </c>
+      <c r="E12" s="11">
+        <v>28</v>
+      </c>
+      <c r="F12" s="11">
+        <v>34</v>
+      </c>
+      <c r="G12" s="11">
+        <v>80</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>80</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
@@ -21834,7 +21822,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -21842,7 +21830,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -21851,15 +21839,27 @@
         <v>16</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="D13" s="11">
+        <v>840</v>
+      </c>
+      <c r="E13" s="11">
+        <v>680</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1040</v>
+      </c>
+      <c r="G13" s="11">
+        <v>760</v>
+      </c>
+      <c r="H13" s="11">
+        <v>640</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1000</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="13"/>
@@ -21971,10 +21971,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
-      <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="J16" s="15"/>
       <c r="K16" s="12"/>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
@@ -22009,10 +22006,7 @@
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
-      <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="J17" s="15"/>
       <c r="K17" s="18"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
@@ -22026,9 +22020,7 @@
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
       <c r="V17" s="15"/>
-      <c r="W17" s="12">
-        <v>2</v>
-      </c>
+      <c r="W17" s="12"/>
       <c r="Y17" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -22054,9 +22046,7 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
-      <c r="J18" s="15">
-        <v>13</v>
-      </c>
+      <c r="J18" s="15"/>
       <c r="K18" s="18"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17"/>
@@ -22085,12 +22075,8 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="15">
-        <v>17</v>
-      </c>
-      <c r="K19" s="18">
-        <v>13</v>
-      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="18"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
       <c r="O19" s="11"/>
@@ -22118,12 +22104,8 @@
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
-      <c r="J20" s="15">
-        <v>7</v>
-      </c>
-      <c r="K20" s="18">
-        <v>8</v>
-      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="18"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
       <c r="O20" s="11"/>
@@ -22148,31 +22130,31 @@
       </c>
       <c r="D21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="F21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="G21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1967</v>
       </c>
       <c r="H21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1544</v>
       </c>
       <c r="I21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2175</v>
       </c>
       <c r="J21" s="26">
         <f>SUM(C21:I21)</f>
-        <v>0</v>
+        <v>8754</v>
       </c>
       <c r="K21" s="28"/>
       <c r="M21" s="1"/>
@@ -22212,7 +22194,7 @@
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
         <f>SUM(Y8:Y17)</f>
-        <v>0</v>
+        <v>94.85</v>
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z17)</f>
@@ -22220,7 +22202,7 @@
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>0</v>
+        <v>94.85</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22234,31 +22216,31 @@
       </c>
       <c r="D22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>25.274999999999999</v>
       </c>
       <c r="E22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20.324999999999999</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>49.174999999999997</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>38.6</v>
       </c>
       <c r="I22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>54.375</v>
       </c>
       <c r="J22" s="22">
         <f>SUM(J8:J20)</f>
-        <v>37</v>
+        <v>218.85</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1"/>
@@ -22300,7 +22282,7 @@
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
         <f>Y21/40</f>
-        <v>0</v>
+        <v>2.3712499999999999</v>
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
@@ -22308,7 +22290,7 @@
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>0</v>
+        <v>2.3712499999999999</v>
       </c>
     </row>
   </sheetData>
@@ -22594,17 +22576,31 @@
         <v>40</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>35</v>
+      </c>
+      <c r="E8" s="11">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11">
+        <v>55</v>
+      </c>
+      <c r="G8" s="11">
+        <v>90</v>
+      </c>
+      <c r="H8" s="11">
+        <v>75</v>
+      </c>
+      <c r="I8" s="11">
+        <v>135</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>10.5</v>
+      </c>
+      <c r="K8" s="12">
+        <v>9</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -22624,7 +22620,7 @@
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -22632,7 +22628,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -22641,17 +22637,31 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>55</v>
+      </c>
+      <c r="E9" s="11">
+        <v>50</v>
+      </c>
+      <c r="F9" s="11">
+        <v>95</v>
+      </c>
+      <c r="G9" s="11">
+        <v>95</v>
+      </c>
+      <c r="H9" s="11">
+        <v>50</v>
+      </c>
+      <c r="I9" s="11">
+        <v>55</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K9" s="12">
+        <v>27</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -22671,7 +22681,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y20" si="2">J9</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z20" si="3">V9</f>
@@ -22679,7 +22689,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA20" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22688,17 +22698,31 @@
         <v>42</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>92</v>
+      </c>
+      <c r="E10" s="11">
+        <v>92</v>
+      </c>
+      <c r="F10" s="11">
+        <v>86</v>
+      </c>
+      <c r="G10" s="11">
+        <v>114</v>
+      </c>
+      <c r="H10" s="11">
+        <v>113</v>
+      </c>
+      <c r="I10" s="11">
+        <v>113</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>15.25</v>
+      </c>
+      <c r="K10" s="12">
+        <v>7</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -22718,7 +22742,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -22726,7 +22750,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -22735,17 +22759,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>4</v>
+      </c>
+      <c r="E11" s="11">
+        <v>54</v>
+      </c>
+      <c r="F11" s="11">
+        <v>54</v>
+      </c>
+      <c r="G11" s="11">
+        <v>111</v>
+      </c>
+      <c r="H11" s="11">
+        <v>60</v>
+      </c>
+      <c r="I11" s="11">
+        <v>121</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>10.1</v>
+      </c>
+      <c r="K11" s="12">
+        <v>9</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -22765,7 +22803,7 @@
       <c r="W11" s="12"/>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -22773,7 +22811,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -22782,17 +22820,31 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>10</v>
+      </c>
+      <c r="E12" s="11">
+        <v>45</v>
+      </c>
+      <c r="F12" s="11">
+        <v>140</v>
+      </c>
+      <c r="G12" s="11">
+        <v>43</v>
+      </c>
+      <c r="H12" s="11">
+        <v>40</v>
+      </c>
+      <c r="I12" s="11">
+        <v>12</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>7.25</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -22812,7 +22864,7 @@
       <c r="W12" s="12"/>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -22820,7 +22872,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22829,17 +22881,31 @@
         <v>16</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="D13" s="11">
+        <v>400</v>
+      </c>
+      <c r="E13" s="11">
+        <v>320</v>
+      </c>
+      <c r="F13" s="11">
+        <v>440</v>
+      </c>
+      <c r="G13" s="11">
+        <v>1080</v>
+      </c>
+      <c r="H13" s="11">
+        <v>1000</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1120</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>109</v>
+      </c>
+      <c r="K13" s="12">
+        <v>6</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -23027,9 +23093,7 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
-      <c r="J18" s="15">
-        <v>20</v>
-      </c>
+      <c r="J18" s="15"/>
       <c r="K18" s="12"/>
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
@@ -23064,12 +23128,8 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="15">
-        <v>30</v>
-      </c>
-      <c r="K19" s="12">
-        <v>15</v>
-      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="12"/>
       <c r="L19" s="13"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17" t="s">
@@ -23103,12 +23163,8 @@
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
-      <c r="J20" s="15">
-        <v>6</v>
-      </c>
-      <c r="K20" s="18">
-        <v>8</v>
-      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="18"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
         <v>44</v>
@@ -23127,7 +23183,7 @@
       <c r="W20" s="18"/>
       <c r="Y20" s="36">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="37">
         <f t="shared" si="3"/>
@@ -23135,7 +23191,7 @@
       </c>
       <c r="AA20" s="38">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.35">
@@ -23147,31 +23203,31 @@
       </c>
       <c r="D21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="F21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="G21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="H21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1338</v>
       </c>
       <c r="I21" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1556</v>
       </c>
       <c r="J21" s="26">
         <f>SUM(C21:I21)</f>
-        <v>0</v>
+        <v>6484</v>
       </c>
       <c r="K21" s="28"/>
       <c r="M21" s="1"/>
@@ -23211,7 +23267,7 @@
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
         <f>SUM(Y8:Y20)</f>
-        <v>6</v>
+        <v>53.1</v>
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z20)</f>
@@ -23219,7 +23275,7 @@
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA20)</f>
-        <v>6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23233,31 +23289,31 @@
       </c>
       <c r="D22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="E22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.775</v>
       </c>
       <c r="F22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21.75</v>
       </c>
       <c r="G22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>38.325000000000003</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="I22" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>38.9</v>
       </c>
       <c r="J22" s="22">
         <f>SUM(J8:J20)</f>
-        <v>56</v>
+        <v>162.1</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="1" t="s">
@@ -23301,7 +23357,7 @@
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
         <f>Y21/40</f>
-        <v>0.15</v>
+        <v>1.3275000000000001</v>
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
@@ -23309,7 +23365,7 @@
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>0.15</v>
+        <v>1.3275000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6960D3-7DB1-4C10-A60D-241880DFA654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FD5847-1AE3-4E09-A69D-65EB71627C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="28" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="27" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -20582,9 +20582,7 @@
         <f>SUM(C8:I8)/40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="12">
-        <v>1</v>
-      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -20631,9 +20629,7 @@
         <f t="shared" ref="J9:J16" si="0">SUM(C9:I9)/40</f>
         <v>0</v>
       </c>
-      <c r="K9" s="12">
-        <v>19</v>
-      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -20680,9 +20676,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="12">
-        <v>9</v>
-      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -20729,9 +20723,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="12">
-        <v>1</v>
-      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -20778,9 +20770,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="12">
-        <v>4</v>
-      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -20827,9 +20817,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="12">
-        <v>9</v>
-      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -21037,9 +21025,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="15"/>
-      <c r="K19" s="12">
-        <v>20</v>
-      </c>
+      <c r="K19" s="12"/>
       <c r="L19" s="13"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
@@ -21622,7 +21608,7 @@
         <v>50</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J17" si="0">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J15" si="0">SUM(C9:I9)/40</f>
         <v>9.5</v>
       </c>
       <c r="K9" s="12"/>
@@ -21632,28 +21618,42 @@
         <v>41</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>95</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>70</v>
+      </c>
+      <c r="R9" s="11">
+        <v>55</v>
+      </c>
+      <c r="S9" s="11">
+        <v>50</v>
+      </c>
+      <c r="T9" s="11">
+        <v>10</v>
+      </c>
+      <c r="U9" s="11">
+        <v>40</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V16" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="W9" s="12">
+        <v>18</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y17" si="2">J9</f>
         <v>9.5</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z17" si="3">V9</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA17" si="4">Y9-Z9</f>
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -21691,28 +21691,42 @@
         <v>42</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>25</v>
+      </c>
+      <c r="R10" s="11">
+        <v>105</v>
+      </c>
+      <c r="S10" s="11">
+        <v>147</v>
+      </c>
+      <c r="T10" s="11">
+        <v>164</v>
+      </c>
+      <c r="U10" s="11">
+        <v>125</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>14.8</v>
+      </c>
+      <c r="W10" s="12">
+        <v>8</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>16.8</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>16.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -21809,28 +21823,42 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>22</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>22</v>
+      </c>
+      <c r="R12" s="11">
+        <v>22</v>
+      </c>
+      <c r="S12" s="11">
+        <v>80</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>80</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>5.65</v>
+      </c>
+      <c r="W12" s="12">
+        <v>3</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>6.55</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>6.55</v>
+        <v>0.89999999999999947</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22165,31 +22193,31 @@
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>0</v>
+        <v>1138</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
@@ -22198,11 +22226,11 @@
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>0</v>
+        <v>28.450000000000003</v>
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>94.85</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22253,31 +22281,31 @@
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3.5750000000000002</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.9249999999999998</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.9249999999999998</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.125</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>28.45</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
@@ -22286,11 +22314,11 @@
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
-        <v>0</v>
+        <v>0.71125000000000005</v>
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>2.3712499999999999</v>
+        <v>1.6600000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FD5847-1AE3-4E09-A69D-65EB71627C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D25D93C-39AD-495D-93BA-E85C31F31D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" activeTab="27" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" firstSheet="3" activeTab="30" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <sheet name="28" sheetId="28" r:id="rId28"/>
     <sheet name="29" sheetId="29" r:id="rId29"/>
     <sheet name="30" sheetId="30" r:id="rId30"/>
-    <sheet name="31" sheetId="31" r:id="rId31"/>
+    <sheet name="10-01" sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="60">
   <si>
     <t>Booking</t>
   </si>
@@ -233,12 +233,15 @@
   <si>
     <t>G</t>
   </si>
+  <si>
+    <t>Aqib</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,6 +359,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -593,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -796,6 +807,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21562,25 +21576,33 @@
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="S8" s="11">
+        <v>800</v>
+      </c>
+      <c r="T8" s="11">
+        <v>720</v>
+      </c>
+      <c r="U8" s="11">
+        <v>880</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="W8" s="12">
+        <v>1</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>60</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -21896,17 +21918,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>600</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>520</v>
+      </c>
+      <c r="R13" s="11">
+        <v>860</v>
+      </c>
+      <c r="S13" s="11">
+        <v>600</v>
+      </c>
+      <c r="T13" s="11">
+        <v>600</v>
+      </c>
+      <c r="U13" s="11">
+        <v>840</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>100.5</v>
+      </c>
+      <c r="W13" s="12">
+        <v>6</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -22193,31 +22229,31 @@
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>143</v>
+        <v>743</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>117</v>
+        <v>637</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
-        <v>182</v>
+        <v>1042</v>
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>277</v>
+        <v>1677</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>174</v>
+        <v>1494</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>245</v>
+        <v>1965</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>1138</v>
+        <v>7558</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
@@ -22226,11 +22262,11 @@
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z17)</f>
-        <v>28.450000000000003</v>
+        <v>88.45</v>
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA17)</f>
-        <v>66.400000000000006</v>
+        <v>6.3999999999999995</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22281,31 +22317,31 @@
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>3.5750000000000002</v>
+        <v>18.574999999999999</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>2.9249999999999998</v>
+        <v>15.925000000000001</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
-        <v>4.55</v>
+        <v>26.05</v>
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>6.9249999999999998</v>
+        <v>41.924999999999997</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>4.3499999999999996</v>
+        <v>37.35</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>6.125</v>
+        <v>49.125</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>28.45</v>
+        <v>188.95</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
@@ -22314,11 +22350,11 @@
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
-        <v>0.71125000000000005</v>
+        <v>2.2112500000000002</v>
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>1.6600000000000001</v>
+        <v>0.15999999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -22635,28 +22671,42 @@
         <v>40</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>33</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>30</v>
+      </c>
+      <c r="R8" s="11">
+        <v>55</v>
+      </c>
+      <c r="S8" s="11">
+        <v>70</v>
+      </c>
+      <c r="T8" s="11">
+        <v>60</v>
+      </c>
+      <c r="U8" s="11">
+        <v>110</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="W8" s="12">
+        <v>8</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>10.5</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>10.5</v>
+        <v>1.5500000000000007</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -22696,28 +22746,42 @@
         <v>41</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>55</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>50</v>
+      </c>
+      <c r="R9" s="11">
+        <v>95</v>
+      </c>
+      <c r="S9" s="11">
+        <v>95</v>
+      </c>
+      <c r="T9" s="11">
+        <v>50</v>
+      </c>
+      <c r="U9" s="11">
+        <v>55</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" ref="V9:V20" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="W9" s="12">
+        <v>15</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y20" si="2">J9</f>
         <v>10</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z20" si="3">V9</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA20" si="4">Y9-Z9</f>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -22757,28 +22821,42 @@
         <v>42</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>46</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>46</v>
+      </c>
+      <c r="R10" s="11">
+        <v>46</v>
+      </c>
+      <c r="S10" s="11">
+        <v>74</v>
+      </c>
+      <c r="T10" s="11">
+        <v>73</v>
+      </c>
+      <c r="U10" s="11">
+        <v>73</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="W10" s="12">
+        <v>5</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>15.25</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>15.25</v>
+        <v>6.3000000000000007</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -22818,28 +22896,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>54</v>
+      </c>
+      <c r="R11" s="11">
+        <v>54</v>
+      </c>
+      <c r="S11" s="11">
+        <v>87</v>
+      </c>
+      <c r="T11" s="11">
+        <v>56</v>
+      </c>
+      <c r="U11" s="11">
+        <v>97</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="W11" s="12">
+        <v>8</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>10.1</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>10.1</v>
+        <v>1.2999999999999989</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -22879,28 +22971,42 @@
         <v>37</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>40</v>
+      </c>
+      <c r="R12" s="11">
+        <v>120</v>
+      </c>
+      <c r="S12" s="11">
+        <v>40</v>
+      </c>
+      <c r="T12" s="11">
+        <v>40</v>
+      </c>
+      <c r="U12" s="11">
+        <v>0</v>
+      </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W12" s="12">
+        <v>2</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>7.25</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>7.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -22940,17 +23046,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>330</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>320</v>
+      </c>
+      <c r="R13" s="11">
+        <v>520</v>
+      </c>
+      <c r="S13" s="11">
+        <v>1080</v>
+      </c>
+      <c r="T13" s="11">
+        <v>986</v>
+      </c>
+      <c r="U13" s="11">
+        <v>1200</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>110.9</v>
+      </c>
+      <c r="W13" s="12">
+        <v>5</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -23102,9 +23222,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="12">
-        <v>2</v>
-      </c>
+      <c r="W17" s="12"/>
       <c r="Y17" s="36"/>
       <c r="Z17" s="37"/>
       <c r="AA17" s="38"/>
@@ -23266,31 +23384,31 @@
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="R21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="S21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1446</v>
       </c>
       <c r="T21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1265</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="V21" s="26">
         <f>SUM(O21:U21)</f>
-        <v>0</v>
+        <v>6144</v>
       </c>
       <c r="W21" s="28"/>
       <c r="Y21" s="33">
@@ -23299,11 +23417,11 @@
       </c>
       <c r="Z21" s="34">
         <f>SUM(Z8:Z20)</f>
-        <v>0</v>
+        <v>42.7</v>
       </c>
       <c r="AA21" s="35">
         <f>SUM(AA8:AA20)</f>
-        <v>53.1</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23356,31 +23474,31 @@
       </c>
       <c r="P22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Q22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="S22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36.15</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>31.625</v>
       </c>
       <c r="U22" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>38.375</v>
       </c>
       <c r="V22" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>153.6</v>
       </c>
       <c r="W22" s="23"/>
       <c r="Y22" s="39">
@@ -23389,11 +23507,11 @@
       </c>
       <c r="Z22" s="40">
         <f>Z21/40</f>
-        <v>0</v>
+        <v>1.0675000000000001</v>
       </c>
       <c r="AA22" s="41">
         <f>AA21/40</f>
-        <v>1.3275000000000001</v>
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -24725,28 +24843,42 @@
         <v>40</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>30</v>
+      </c>
+      <c r="R8" s="11">
+        <v>20</v>
+      </c>
+      <c r="S8" s="11">
+        <v>15</v>
+      </c>
+      <c r="T8" s="11">
+        <v>20</v>
+      </c>
+      <c r="U8" s="11">
+        <v>35</v>
+      </c>
       <c r="V8" s="15">
         <f>SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>3.75</v>
+      </c>
+      <c r="W8" s="12">
+        <v>16</v>
+      </c>
       <c r="Y8" s="36">
         <f>J8</f>
         <v>0</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>0</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -24772,28 +24904,42 @@
         <v>41</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>195</v>
+      </c>
+      <c r="R9" s="11">
+        <v>180</v>
+      </c>
+      <c r="S9" s="11">
+        <v>75</v>
+      </c>
+      <c r="T9" s="11">
+        <v>105</v>
+      </c>
+      <c r="U9" s="11">
+        <v>60</v>
+      </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9:V17" si="1">SUM(O9:U9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <f t="shared" ref="V9:V18" si="1">SUM(O9:U9)/40</f>
+        <v>17</v>
+      </c>
+      <c r="W9" s="12">
+        <v>30</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y21" si="2">J9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z21" si="3">V9</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA21" si="4">Y9-Z9</f>
-        <v>0</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -24819,28 +24965,42 @@
         <v>42</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>10</v>
+      </c>
+      <c r="R10" s="11">
+        <v>20</v>
+      </c>
+      <c r="S10" s="11">
+        <v>0</v>
+      </c>
+      <c r="T10" s="11">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11">
+        <v>20</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>1.5</v>
+      </c>
+      <c r="W10" s="12">
+        <v>2</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -24866,28 +25026,42 @@
         <v>39</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>10</v>
+      </c>
+      <c r="R11" s="11">
+        <v>15</v>
+      </c>
+      <c r="S11" s="11">
+        <v>35</v>
+      </c>
+      <c r="T11" s="11">
+        <v>30</v>
+      </c>
+      <c r="U11" s="11">
+        <v>55</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="W11" s="12">
+        <v>2</v>
+      </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -24912,43 +25086,43 @@
       <c r="N12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="11">
-        <v>50</v>
-      </c>
+      <c r="O12" s="11"/>
       <c r="P12" s="11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q12" s="11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R12" s="11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S12" s="11">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="T12" s="11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U12" s="11">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="V12" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="W12" s="12"/>
+        <v>2.4249999999999998</v>
+      </c>
+      <c r="W12" s="12">
+        <v>5</v>
+      </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2.4249999999999998</v>
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-3</v>
+        <v>-2.4249999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -25125,38 +25299,22 @@
       <c r="N17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O17" s="11">
-        <v>80</v>
-      </c>
-      <c r="P17" s="11">
-        <v>80</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>80</v>
-      </c>
-      <c r="R17" s="11">
-        <v>40</v>
-      </c>
-      <c r="S17" s="11">
-        <v>80</v>
-      </c>
-      <c r="T17" s="11">
-        <v>40</v>
-      </c>
-      <c r="U17" s="11">
-        <v>80</v>
-      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="15">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="W17" s="12">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W17" s="12"/>
       <c r="Y17" s="36"/>
       <c r="Z17" s="37">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="38"/>
     </row>
@@ -25172,24 +25330,39 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
-      <c r="J18" s="15">
-        <v>12</v>
-      </c>
+      <c r="J18" s="15"/>
       <c r="K18" s="12"/>
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="12"/>
+      <c r="P18" s="11">
+        <v>28</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>24</v>
+      </c>
+      <c r="R18" s="11">
+        <v>34</v>
+      </c>
+      <c r="S18" s="11">
+        <v>23</v>
+      </c>
+      <c r="T18" s="11">
+        <v>12</v>
+      </c>
+      <c r="U18" s="11">
+        <v>17</v>
+      </c>
+      <c r="V18" s="15">
+        <f t="shared" si="1"/>
+        <v>3.45</v>
+      </c>
+      <c r="W18" s="12">
+        <v>6</v>
+      </c>
       <c r="Y18" s="36"/>
       <c r="Z18" s="37"/>
       <c r="AA18" s="38"/>
@@ -25206,12 +25379,8 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="15">
-        <v>10</v>
-      </c>
-      <c r="K19" s="12">
-        <v>8</v>
-      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="12"/>
       <c r="L19" s="13"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17" t="s">
@@ -25242,12 +25411,8 @@
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
-      <c r="J20" s="15">
-        <v>5</v>
-      </c>
-      <c r="K20" s="12">
-        <v>7</v>
-      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="12"/>
       <c r="L20" s="13"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17" t="s">
@@ -25345,35 +25510,35 @@
       <c r="N22" s="7"/>
       <c r="O22" s="25">
         <f t="shared" ref="O22:U22" si="6">SUM(O8:O21)</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="P22" s="25">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="Q22" s="25">
         <f t="shared" si="6"/>
-        <v>96</v>
+        <v>282</v>
       </c>
       <c r="R22" s="25">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>311</v>
       </c>
       <c r="S22" s="25">
         <f t="shared" si="6"/>
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="T22" s="25">
         <f t="shared" si="6"/>
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="U22" s="25">
         <f t="shared" si="6"/>
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="V22" s="26">
         <f>SUM(O22:U22)</f>
-        <v>600</v>
+        <v>1285</v>
       </c>
       <c r="W22" s="28"/>
       <c r="Y22" s="33">
@@ -25382,11 +25547,11 @@
       </c>
       <c r="Z22" s="34">
         <f>SUM(Z8:Z21)</f>
-        <v>15</v>
+        <v>28.675000000000001</v>
       </c>
       <c r="AA22" s="35">
         <f>SUM(AA8:AA21)</f>
-        <v>-3</v>
+        <v>-28.675000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25424,11 +25589,11 @@
       </c>
       <c r="J23" s="22">
         <f>SUM(J8:J20)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K23" s="22">
         <f>SUM(K8:K20)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="20" t="s">
@@ -25436,35 +25601,35 @@
       </c>
       <c r="O23" s="21">
         <f t="shared" ref="O23:V23" si="8">O22/40</f>
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P23" s="21">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="Q23" s="21">
         <f t="shared" si="8"/>
-        <v>2.4</v>
+        <v>7.05</v>
       </c>
       <c r="R23" s="21">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>7.7750000000000004</v>
       </c>
       <c r="S23" s="21">
         <f t="shared" si="8"/>
-        <v>2.6749999999999998</v>
+        <v>3.7</v>
       </c>
       <c r="T23" s="21">
         <f t="shared" si="8"/>
-        <v>1.2749999999999999</v>
+        <v>4.1749999999999998</v>
       </c>
       <c r="U23" s="21">
         <f t="shared" si="8"/>
-        <v>2.4</v>
+        <v>5.2750000000000004</v>
       </c>
       <c r="V23" s="22">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>32.125</v>
       </c>
       <c r="W23" s="23"/>
       <c r="Y23" s="39">
@@ -25473,11 +25638,11 @@
       </c>
       <c r="Z23" s="40">
         <f>Z22/40</f>
-        <v>0.375</v>
+        <v>0.71687500000000004</v>
       </c>
       <c r="AA23" s="41">
         <f>AA22/40</f>
-        <v>-7.4999999999999997E-2</v>
+        <v>-0.71687500000000004</v>
       </c>
     </row>
   </sheetData>
@@ -25496,10 +25661,10 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9DEC90-B3AB-443E-9C2F-99376CA7B8EA}">
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" customWidth="1"/>
     <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.90625" bestFit="1" customWidth="1"/>
@@ -25515,8 +25680,10 @@
     <col min="27" max="27" width="6.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:27" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="89">
+        <v>46296</v>
+      </c>
       <c r="B1" s="77" t="s">
         <v>0</v>
       </c>
@@ -25736,33 +25903,31 @@
       <c r="B7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="11">
-        <v>693</v>
-      </c>
+      <c r="C7" s="11"/>
       <c r="D7" s="11">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E7" s="11">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F7" s="11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G7" s="11">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="H7" s="11">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="I7" s="11">
-        <v>283</v>
+        <v>170</v>
       </c>
       <c r="J7" s="15">
         <f>SUM(C7:I7)/40</f>
-        <v>34.924999999999997</v>
+        <v>8.5</v>
       </c>
       <c r="K7" s="12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L7" s="13"/>
       <c r="M7" s="14"/>
@@ -25783,7 +25948,7 @@
       <c r="W7" s="12"/>
       <c r="Y7" s="36">
         <f>J7</f>
-        <v>34.924999999999997</v>
+        <v>8.5</v>
       </c>
       <c r="Z7" s="37">
         <f>V7</f>
@@ -25791,7 +25956,7 @@
       </c>
       <c r="AA7" s="38">
         <f>Y7-Z7</f>
-        <v>34.924999999999997</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
@@ -25800,17 +25965,31 @@
         <v>41</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>110</v>
+      </c>
+      <c r="H8" s="11">
+        <v>100</v>
+      </c>
+      <c r="I8" s="11">
+        <v>70</v>
+      </c>
       <c r="J8" s="15">
-        <f t="shared" ref="J8:J20" si="0">SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <f t="shared" ref="J8:J19" si="0">SUM(C8:I8)/40</f>
+        <v>7</v>
+      </c>
+      <c r="K8" s="12">
+        <v>3</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -25824,21 +26003,21 @@
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
       <c r="V8" s="15">
-        <f t="shared" ref="V8:V16" si="1">SUM(O8:U8)/40</f>
+        <f t="shared" ref="V8:V15" si="1">SUM(O8:U8)/40</f>
         <v>0</v>
       </c>
       <c r="W8" s="12"/>
       <c r="Y8" s="36">
-        <f t="shared" ref="Y8:Y20" si="2">J8</f>
-        <v>0</v>
+        <f t="shared" ref="Y8:Y19" si="2">J8</f>
+        <v>7</v>
       </c>
       <c r="Z8" s="37">
-        <f t="shared" ref="Z8:Z20" si="3">V8</f>
+        <f t="shared" ref="Z8:Z19" si="3">V8</f>
         <v>0</v>
       </c>
       <c r="AA8" s="38">
-        <f t="shared" ref="AA8:AA20" si="4">Y8-Z8</f>
-        <v>0</v>
+        <f t="shared" ref="AA8:AA19" si="4">Y8-Z8</f>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -25847,17 +26026,31 @@
         <v>42</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>19</v>
+      </c>
+      <c r="E9" s="11">
+        <v>16</v>
+      </c>
+      <c r="F9" s="11">
+        <v>17</v>
+      </c>
+      <c r="G9" s="11">
+        <v>41</v>
+      </c>
+      <c r="H9" s="11">
+        <v>34</v>
+      </c>
+      <c r="I9" s="11">
+        <v>59</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K9" s="12">
+        <v>7</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -25877,7 +26070,7 @@
       <c r="W9" s="12"/>
       <c r="Y9" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" si="3"/>
@@ -25885,7 +26078,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -25894,17 +26087,31 @@
         <v>22</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>12</v>
+      </c>
+      <c r="H10" s="11">
+        <v>92</v>
+      </c>
+      <c r="I10" s="11">
+        <v>92</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K10" s="12">
+        <v>3</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="16"/>
       <c r="N10" s="17" t="s">
@@ -25924,7 +26131,7 @@
       <c r="W10" s="12"/>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -25932,30 +26139,44 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>9</v>
+      </c>
+      <c r="E11" s="11">
+        <v>9</v>
+      </c>
+      <c r="F11" s="11">
+        <v>9</v>
+      </c>
+      <c r="G11" s="11">
+        <v>50</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>10</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>2.1749999999999998</v>
+      </c>
+      <c r="K11" s="12">
+        <v>4</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -25969,40 +26190,45 @@
         <v>0</v>
       </c>
       <c r="W11" s="12"/>
-      <c r="Y11" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="37"/>
+      <c r="AA11" s="38"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>730</v>
+      </c>
+      <c r="E12" s="11">
+        <v>640</v>
+      </c>
+      <c r="F12" s="11">
+        <v>800</v>
+      </c>
+      <c r="G12" s="11">
+        <v>510</v>
+      </c>
+      <c r="H12" s="11">
+        <v>380</v>
+      </c>
+      <c r="I12" s="11">
+        <v>400</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>86.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>1</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
@@ -26023,7 +26249,7 @@
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -26040,7 +26266,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
@@ -26061,7 +26287,7 @@
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -26078,7 +26304,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -26099,7 +26325,7 @@
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -26116,7 +26342,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -26137,7 +26363,7 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -26147,14 +26373,13 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="13"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -26163,10 +26388,7 @@
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
-      <c r="V16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="V16" s="15"/>
       <c r="W16" s="12"/>
       <c r="Y16" s="36"/>
       <c r="Z16" s="37"/>
@@ -26175,7 +26397,7 @@
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
@@ -26185,13 +26407,13 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12"/>
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -26209,7 +26431,7 @@
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -26219,13 +26441,13 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12"/>
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
@@ -26242,9 +26464,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="16"/>
-      <c r="B19" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="B19" s="17"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
@@ -26252,13 +26472,13 @@
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="13"/>
+      <c r="J19" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="18"/>
       <c r="M19" s="16"/>
-      <c r="N19" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="N19" s="17"/>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -26267,223 +26487,193 @@
       <c r="T19" s="11"/>
       <c r="U19" s="11"/>
       <c r="V19" s="15"/>
-      <c r="W19" s="12"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="37"/>
-      <c r="AA19" s="38"/>
+      <c r="W19" s="18"/>
+      <c r="Y19" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="18"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="18"/>
-      <c r="Y20" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="38">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="25">
+        <f t="shared" ref="C20:I20" si="5">SUM(C7:C19)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="25">
+        <f t="shared" si="5"/>
+        <v>768</v>
+      </c>
+      <c r="E20" s="25">
+        <f t="shared" si="5"/>
+        <v>675</v>
+      </c>
+      <c r="F20" s="25">
+        <f t="shared" si="5"/>
+        <v>926</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" si="5"/>
+        <v>773</v>
+      </c>
+      <c r="H20" s="25">
+        <f t="shared" si="5"/>
+        <v>606</v>
+      </c>
+      <c r="I20" s="25">
+        <f t="shared" si="5"/>
+        <v>801</v>
+      </c>
+      <c r="J20" s="26">
+        <f>SUM(C20:I20)</f>
+        <v>4549</v>
+      </c>
+      <c r="K20" s="28"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="25">
+        <f t="shared" ref="O20:U20" si="6">SUM(O7:O19)</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="26">
+        <f>SUM(O20:U20)</f>
+        <v>0</v>
+      </c>
+      <c r="W20" s="28"/>
+      <c r="Y20" s="33">
+        <f>SUM(Y7:Y19)</f>
+        <v>25.049999999999997</v>
+      </c>
+      <c r="Z20" s="34">
+        <f>SUM(Z7:Z19)</f>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="35">
+        <f>SUM(AA7:AA19)</f>
+        <v>25.049999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25">
-        <f t="shared" ref="C21:I21" si="5">SUM(C7:C20)</f>
-        <v>693</v>
-      </c>
-      <c r="D21" s="25">
-        <f t="shared" si="5"/>
-        <v>70</v>
-      </c>
-      <c r="E21" s="25">
-        <f t="shared" si="5"/>
-        <v>70</v>
-      </c>
-      <c r="F21" s="25">
-        <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="G21" s="25">
-        <f t="shared" si="5"/>
-        <v>103</v>
-      </c>
-      <c r="H21" s="25">
-        <f t="shared" si="5"/>
-        <v>98</v>
-      </c>
-      <c r="I21" s="25">
-        <f t="shared" si="5"/>
-        <v>283</v>
-      </c>
-      <c r="J21" s="26">
-        <f>SUM(C21:I21)</f>
-        <v>1397</v>
-      </c>
-      <c r="K21" s="28"/>
+      <c r="B21" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="21">
+        <f t="shared" ref="C21:I21" si="7">C20/40</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="21">
+        <f t="shared" si="7"/>
+        <v>19.2</v>
+      </c>
+      <c r="E21" s="21">
+        <f t="shared" si="7"/>
+        <v>16.875</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="7"/>
+        <v>23.15</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="7"/>
+        <v>19.324999999999999</v>
+      </c>
+      <c r="H21" s="21">
+        <f t="shared" si="7"/>
+        <v>15.15</v>
+      </c>
+      <c r="I21" s="21">
+        <f t="shared" si="7"/>
+        <v>20.024999999999999</v>
+      </c>
+      <c r="J21" s="22">
+        <f>SUM(J7:J17)</f>
+        <v>113.72499999999999</v>
+      </c>
+      <c r="K21" s="22">
+        <f>SUM(K7:K18)</f>
+        <v>27</v>
+      </c>
       <c r="M21" s="1"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="25">
-        <f t="shared" ref="O21:U21" si="6">SUM(O7:O20)</f>
-        <v>0</v>
-      </c>
-      <c r="P21" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R21" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="26">
-        <f>SUM(O21:U21)</f>
-        <v>0</v>
-      </c>
-      <c r="W21" s="28"/>
-      <c r="Y21" s="33">
-        <f>SUM(Y7:Y20)</f>
-        <v>34.924999999999997</v>
-      </c>
-      <c r="Z21" s="34">
-        <f>SUM(Z7:Z20)</f>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="35">
-        <f>SUM(AA7:AA20)</f>
-        <v>34.924999999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="1"/>
-      <c r="B22" s="20" t="s">
+      <c r="N21" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="21">
-        <f t="shared" ref="C22:I22" si="7">C21/40</f>
-        <v>17.324999999999999</v>
-      </c>
-      <c r="D22" s="21">
-        <f t="shared" si="7"/>
-        <v>1.75</v>
-      </c>
-      <c r="E22" s="21">
-        <f t="shared" si="7"/>
-        <v>1.75</v>
-      </c>
-      <c r="F22" s="21">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="G22" s="21">
-        <f t="shared" si="7"/>
-        <v>2.5750000000000002</v>
-      </c>
-      <c r="H22" s="21">
-        <f t="shared" si="7"/>
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="I22" s="21">
-        <f t="shared" si="7"/>
-        <v>7.0750000000000002</v>
-      </c>
-      <c r="J22" s="22">
-        <f>SUM(J7:J18)</f>
-        <v>56.924999999999997</v>
-      </c>
-      <c r="K22" s="22">
-        <f>SUM(K7:K19)</f>
-        <v>18</v>
-      </c>
-      <c r="M22" s="1"/>
-      <c r="N22" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="21">
-        <f t="shared" ref="O22:V22" si="8">O21/40</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="21">
+      <c r="O21" s="21">
+        <f t="shared" ref="O21:V21" si="8">O20/40</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="21">
+      <c r="Q21" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R22" s="21">
+      <c r="R21" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S22" s="21">
+      <c r="S21" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T22" s="21">
+      <c r="T21" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U22" s="21">
+      <c r="U21" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V22" s="22">
+      <c r="V21" s="22">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W22" s="23"/>
-      <c r="Y22" s="39">
-        <f>Y21/40</f>
-        <v>0.87312499999999993</v>
-      </c>
-      <c r="Z22" s="40">
-        <f>Z21/40</f>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="41">
-        <f>AA21/40</f>
-        <v>0.87312499999999993</v>
+      <c r="W21" s="23"/>
+      <c r="Y21" s="39">
+        <f>Y20/40</f>
+        <v>0.62624999999999997</v>
+      </c>
+      <c r="Z21" s="40">
+        <f>Z20/40</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="41">
+        <f>AA20/40</f>
+        <v>0.62624999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D25D93C-39AD-495D-93BA-E85C31F31D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2CBE77-C38A-435A-A428-40DAAEB31E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" firstSheet="3" activeTab="30" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -769,6 +769,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -807,9 +810,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1175,103 +1175,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="76" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -1288,16 +1288,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -1305,16 +1305,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -2225,103 +2225,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -2338,16 +2338,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -2355,16 +2355,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -3268,103 +3268,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -3381,16 +3381,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -3398,16 +3398,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -3639,15 +3639,15 @@
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="86"/>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4288,103 +4288,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -4401,16 +4401,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -4418,16 +4418,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -5364,103 +5364,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -5477,16 +5477,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -5494,16 +5494,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -6251,103 +6251,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -6364,16 +6364,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -6381,16 +6381,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -7264,103 +7264,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -7377,16 +7377,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -7394,16 +7394,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -8326,103 +8326,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -8439,16 +8439,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -8456,16 +8456,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -9374,103 +9374,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -9487,16 +9487,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -9504,16 +9504,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -10425,103 +10425,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -10538,16 +10538,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -10555,16 +10555,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -11440,103 +11440,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -11553,16 +11553,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -11570,16 +11570,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -12435,10 +12435,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="L1" s="80" t="s">
+      <c r="L1" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="80"/>
+      <c r="M1" s="81"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -12450,103 +12450,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -12563,16 +12563,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -12580,16 +12580,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -13324,103 +13324,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -13437,16 +13437,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -13454,16 +13454,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -14310,103 +14310,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -14423,16 +14423,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -14440,16 +14440,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -14826,15 +14826,15 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="86" t="s">
+      <c r="D12" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="89"/>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -15293,103 +15293,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -15406,16 +15406,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -15423,16 +15423,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -15812,16 +15812,16 @@
       <c r="B12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="89"/>
       <c r="K12" s="12"/>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
@@ -16306,103 +16306,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -16419,16 +16419,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -16436,16 +16436,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -16598,16 +16598,16 @@
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="89"/>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
@@ -17316,103 +17316,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -17429,16 +17429,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -17446,16 +17446,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -18365,103 +18365,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -18478,16 +18478,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -18495,16 +18495,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -19369,103 +19369,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -19482,16 +19482,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -19499,16 +19499,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -20366,103 +20366,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -20479,16 +20479,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -20496,16 +20496,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -21330,103 +21330,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -21443,16 +21443,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -21460,16 +21460,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -22420,103 +22420,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -22533,16 +22533,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -22550,16 +22550,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -23580,103 +23580,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -23693,16 +23693,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -23710,16 +23710,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -24606,103 +24606,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -24719,16 +24719,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -24736,16 +24736,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -25148,17 +25148,31 @@
         <v>16</v>
       </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="P13" s="11">
+        <v>400</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>320</v>
+      </c>
+      <c r="R13" s="11">
+        <v>400</v>
+      </c>
+      <c r="S13" s="11">
+        <v>480</v>
+      </c>
+      <c r="T13" s="11">
+        <v>360</v>
+      </c>
+      <c r="U13" s="11">
+        <v>600</v>
+      </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="12"/>
+        <v>64</v>
+      </c>
+      <c r="W13" s="12">
+        <v>4</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="37"/>
       <c r="AA13" s="38"/>
@@ -25514,31 +25528,31 @@
       </c>
       <c r="P22" s="25">
         <f t="shared" si="6"/>
-        <v>166</v>
+        <v>566</v>
       </c>
       <c r="Q22" s="25">
         <f t="shared" si="6"/>
-        <v>282</v>
+        <v>602</v>
       </c>
       <c r="R22" s="25">
         <f t="shared" si="6"/>
-        <v>311</v>
+        <v>711</v>
       </c>
       <c r="S22" s="25">
         <f t="shared" si="6"/>
-        <v>148</v>
+        <v>628</v>
       </c>
       <c r="T22" s="25">
         <f t="shared" si="6"/>
-        <v>167</v>
+        <v>527</v>
       </c>
       <c r="U22" s="25">
         <f t="shared" si="6"/>
-        <v>211</v>
+        <v>811</v>
       </c>
       <c r="V22" s="26">
         <f>SUM(O22:U22)</f>
-        <v>1285</v>
+        <v>3845</v>
       </c>
       <c r="W22" s="28"/>
       <c r="Y22" s="33">
@@ -25605,31 +25619,31 @@
       </c>
       <c r="P23" s="21">
         <f t="shared" si="8"/>
-        <v>4.1500000000000004</v>
+        <v>14.15</v>
       </c>
       <c r="Q23" s="21">
         <f t="shared" si="8"/>
-        <v>7.05</v>
+        <v>15.05</v>
       </c>
       <c r="R23" s="21">
         <f t="shared" si="8"/>
-        <v>7.7750000000000004</v>
+        <v>17.774999999999999</v>
       </c>
       <c r="S23" s="21">
         <f t="shared" si="8"/>
-        <v>3.7</v>
+        <v>15.7</v>
       </c>
       <c r="T23" s="21">
         <f t="shared" si="8"/>
-        <v>4.1749999999999998</v>
+        <v>13.175000000000001</v>
       </c>
       <c r="U23" s="21">
         <f t="shared" si="8"/>
-        <v>5.2750000000000004</v>
+        <v>20.274999999999999</v>
       </c>
       <c r="V23" s="22">
         <f t="shared" si="8"/>
-        <v>32.125</v>
+        <v>96.125</v>
       </c>
       <c r="W23" s="23"/>
       <c r="Y23" s="39">
@@ -25681,106 +25695,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="89">
+      <c r="A1" s="76">
         <v>46296</v>
       </c>
-      <c r="B1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
+      <c r="B1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="77" t="s">
+      <c r="N1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="Y2" s="81" t="s">
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="Y2" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="78"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="78"/>
-      <c r="T4" s="78"/>
-      <c r="U4" s="78"/>
-      <c r="V4" s="78"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="79"/>
+      <c r="V4" s="79"/>
       <c r="Y4" s="29" t="s">
         <v>0</v>
       </c>
@@ -25797,16 +25811,16 @@
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79" t="s">
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5"/>
       <c r="M5" s="1"/>
@@ -25814,16 +25828,16 @@
       <c r="O5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="79" t="s">
+      <c r="P5" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79" t="s">
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="79"/>
-      <c r="U5" s="79"/>
+      <c r="T5" s="80"/>
+      <c r="U5" s="80"/>
       <c r="V5" s="4"/>
       <c r="W5" s="5"/>
       <c r="Y5" s="30"/>
@@ -25935,28 +25949,42 @@
         <v>40</v>
       </c>
       <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+      <c r="P7" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11">
+        <v>80</v>
+      </c>
+      <c r="S7" s="11">
+        <v>50</v>
+      </c>
+      <c r="T7" s="11">
+        <v>0</v>
+      </c>
+      <c r="U7" s="11">
+        <v>170</v>
+      </c>
       <c r="V7" s="15">
         <f>SUM(O7:U7)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="12"/>
+        <v>7.5</v>
+      </c>
+      <c r="W7" s="12">
+        <v>8</v>
+      </c>
       <c r="Y7" s="36">
         <f>J7</f>
         <v>8.5</v>
       </c>
       <c r="Z7" s="37">
         <f>V7</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" s="38">
         <f>Y7-Z7</f>
-        <v>8.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.35">
@@ -25996,28 +26024,42 @@
         <v>41</v>
       </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>95</v>
+      </c>
+      <c r="T8" s="11">
+        <v>90</v>
+      </c>
+      <c r="U8" s="11">
+        <v>55</v>
+      </c>
       <c r="V8" s="15">
         <f t="shared" ref="V8:V15" si="1">SUM(O8:U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="W8" s="12">
+        <v>2</v>
+      </c>
       <c r="Y8" s="36">
         <f t="shared" ref="Y8:Y19" si="2">J8</f>
         <v>7</v>
       </c>
       <c r="Z8" s="37">
         <f t="shared" ref="Z8:Z19" si="3">V8</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA8" s="38">
         <f t="shared" ref="AA8:AA19" si="4">Y8-Z8</f>
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -26057,28 +26099,42 @@
         <v>42</v>
       </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="P9" s="11">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>16</v>
+      </c>
+      <c r="R9" s="11">
+        <v>17</v>
+      </c>
+      <c r="S9" s="11">
+        <v>41</v>
+      </c>
+      <c r="T9" s="11">
+        <v>34</v>
+      </c>
+      <c r="U9" s="11">
+        <v>59</v>
+      </c>
       <c r="V9" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="12"/>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="W9" s="12">
+        <v>7</v>
+      </c>
       <c r="Y9" s="36">
         <f t="shared" si="2"/>
         <v>4.6500000000000004</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="AA9" s="38">
         <f t="shared" si="4"/>
-        <v>4.6500000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -26118,28 +26174,42 @@
         <v>22</v>
       </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>12</v>
+      </c>
+      <c r="T10" s="11">
+        <v>92</v>
+      </c>
+      <c r="U10" s="11">
+        <v>92</v>
+      </c>
       <c r="V10" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="12"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W10" s="12">
+        <v>3</v>
+      </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
         <v>4.9000000000000004</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>4.9000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -26179,17 +26249,31 @@
         <v>37</v>
       </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="P11" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>9</v>
+      </c>
+      <c r="R11" s="11">
+        <v>9</v>
+      </c>
+      <c r="S11" s="11">
+        <v>50</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <v>10</v>
+      </c>
       <c r="V11" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="12"/>
+        <v>2.1749999999999998</v>
+      </c>
+      <c r="W11" s="12">
+        <v>4</v>
+      </c>
       <c r="Y11" s="36"/>
       <c r="Z11" s="37"/>
       <c r="AA11" s="38"/>
@@ -26545,31 +26629,31 @@
       </c>
       <c r="P20" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q20" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R20" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="S20" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="T20" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="U20" s="25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="V20" s="26">
         <f>SUM(O20:U20)</f>
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="W20" s="28"/>
       <c r="Y20" s="33">
@@ -26578,11 +26662,11 @@
       </c>
       <c r="Z20" s="34">
         <f>SUM(Z7:Z19)</f>
-        <v>0</v>
+        <v>23.049999999999997</v>
       </c>
       <c r="AA20" s="35">
         <f>SUM(AA7:AA19)</f>
-        <v>25.049999999999997</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26636,31 +26720,31 @@
       </c>
       <c r="P21" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Q21" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="R21" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S21" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="T21" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="U21" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="V21" s="22">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>25.225000000000001</v>
       </c>
       <c r="W21" s="23"/>
       <c r="Y21" s="39">
@@ -26669,11 +26753,11 @@
       </c>
       <c r="Z21" s="40">
         <f>Z20/40</f>
-        <v>0</v>
+        <v>0.57624999999999993</v>
       </c>
       <c r="AA21" s="41">
         <f>AA20/40</f>
-        <v>0.62624999999999997</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -26742,103 +26826,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -26855,16 +26939,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -26872,16 +26956,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -27709,111 +27793,111 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="K2" s="44"/>
       <c r="L2" s="44"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="44"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="K3" s="44"/>
       <c r="L3" s="44"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="44"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="K4" s="44"/>
       <c r="L4" s="44"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="44"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -27830,16 +27914,16 @@
       <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82" t="s">
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
       <c r="J6" s="47"/>
       <c r="K6" s="48"/>
       <c r="L6" s="44"/>
@@ -27848,16 +27932,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -28696,103 +28780,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -28809,16 +28893,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -28826,16 +28910,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -29578,103 +29662,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -29691,16 +29775,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -29708,16 +29792,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -30650,103 +30734,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -30763,16 +30847,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -30780,16 +30864,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>
@@ -31712,103 +31796,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="B2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="77" t="s">
+      <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="Y3" s="81" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="Y3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="79"/>
       <c r="Y5" s="29" t="s">
         <v>0</v>
       </c>
@@ -31825,16 +31909,16 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
       <c r="M6" s="1"/>
@@ -31842,16 +31926,16 @@
       <c r="O6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="79" t="s">
+      <c r="P6" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79" t="s">
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
       <c r="V6" s="4"/>
       <c r="W6" s="5"/>
       <c r="Y6" s="30"/>

--- a/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
+++ b/Sep_2026/daily Reports/Daily Booking VS Execution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2CBE77-C38A-435A-A428-40DAAEB31E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5242B4-7474-4E69-BEDC-F96C77497164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="860" firstSheet="3" activeTab="30" xr2:uid="{B0E336F2-AB38-4CE9-B7A3-449981D50C07}"/>
   </bookViews>
@@ -604,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -809,6 +809,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -24594,7 +24597,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="L1" s="90">
+        <v>46295</v>
+      </c>
+      <c r="M1" s="81"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -24617,7 +24623,8 @@
       <c r="H2" s="78"/>
       <c r="I2" s="78"/>
       <c r="J2" s="78"/>
-      <c r="M2" s="1"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
       <c r="N2" s="78" t="s">
         <v>1</v>
       </c>
@@ -24826,17 +24833,31 @@
         <v>40</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="D8" s="11">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11">
+        <v>20</v>
+      </c>
+      <c r="G8" s="11">
+        <v>15</v>
+      </c>
+      <c r="H8" s="11">
+        <v>20</v>
+      </c>
+      <c r="I8" s="11">
+        <v>35</v>
+      </c>
       <c r="J8" s="15">
         <f>SUM(C8:I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="12"/>
+        <v>3.75</v>
+      </c>
+      <c r="K8" s="12">
+        <v>16</v>
+      </c>
       <c r="L8" s="13"/>
       <c r="M8" s="14"/>
       <c r="N8" s="7" t="s">
@@ -24870,7 +24891,7 @@
       </c>
       <c r="Y8" s="36">
         <f>J8</f>
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Z8" s="37">
         <f>V8</f>
@@ -24878,7 +24899,7 @@
       </c>
       <c r="AA8" s="38">
         <f>Y8-Z8</f>
-        <v>-3.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
@@ -24887,17 +24908,31 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="D9" s="11">
+        <v>65</v>
+      </c>
+      <c r="E9" s="11">
+        <v>195</v>
+      </c>
+      <c r="F9" s="11">
+        <v>180</v>
+      </c>
+      <c r="G9" s="11">
+        <v>75</v>
+      </c>
+      <c r="H9" s="11">
+        <v>105</v>
+      </c>
+      <c r="I9" s="11">
+        <v>60</v>
+      </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:J21" si="0">SUM(C9:I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="K9" s="12">
+        <v>30</v>
+      </c>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
       <c r="N9" s="7" t="s">
@@ -24931,7 +24966,7 @@
       </c>
       <c r="Y9" s="36">
         <f t="shared" ref="Y9:Y21" si="2">J9</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z9" s="37">
         <f t="shared" ref="Z9:Z21" si="3">V9</f>
@@ -24939,7 +24974,7 @@
       </c>
       <c r="AA9" s="38">
         <f t="shared" ref="AA9:AA21" si="4">Y9-Z9</f>
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.35">
@@ -24948,17 +24983,31 @@
         <v>42</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="D10" s="11">
+        <v>10</v>
+      </c>
+      <c r="E10" s="11">
+        <v>10</v>
+      </c>
+      <c r="F10" s="11">
+        <v>20</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>20</v>
+      </c>
       <c r="J10" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="12"/>
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="12">
+        <v>2</v>
+      </c>
       <c r="L10" s="13"/>
       <c r="M10" s="14"/>
       <c r="N10" s="7" t="s">
@@ -24992,7 +25041,7 @@
       </c>
       <c r="Y10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" s="37">
         <f t="shared" si="3"/>
@@ -25000,7 +25049,7 @@
       </c>
       <c r="AA10" s="38">
         <f t="shared" si="4"/>
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -25009,17 +25058,31 @@
         <v>39</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="D11" s="11">
+        <v>15</v>
+      </c>
+      <c r="E11" s="11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="11">
+        <v>15</v>
+      </c>
+      <c r="G11" s="11">
+        <v>35</v>
+      </c>
+      <c r="H11" s="11">
+        <v>30</v>
+      </c>
+      <c r="I11" s="11">
+        <v>55</v>
+      </c>
       <c r="J11" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="K11" s="12">
+        <v>2</v>
+      </c>
       <c r="L11" s="13"/>
       <c r="M11" s="16"/>
       <c r="N11" s="17" t="s">
@@ -25053,7 +25116,7 @@
       </c>
       <c r="Y11" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z11" s="37">
         <f t="shared" si="3"/>
@@ -25061,7 +25124,7 @@
       </c>
       <c r="AA11" s="38">
         <f t="shared" si="4"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -25070,17 +25133,31 @@
         <v>37</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="D12" s="11">
+        <v>18</v>
+      </c>
+      <c r="E12" s="11">
+        <v>13</v>
+      </c>
+      <c r="F12" s="11">
+        <v>42</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>24</v>
+      </c>
       <c r="J12" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="12"/>
+        <v>2.4249999999999998</v>
+      </c>
+      <c r="K12" s="12">
+        <v>5</v>
+      </c>
       <c r="L12" s="13"/>
       <c r="M12" s="16"/>
       <c r="N12" s="17" t="s">
@@ -25114,7 +25191,7 @@
       </c>
       <c r="Y12" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.4249999999999998</v>
       </c>
       <c r="Z12" s="37">
         <f t="shared" si="3"/>
@@ -25122,7 +25199,7 @@
       </c>
       <c r="AA12" s="38">
         <f t="shared" si="4"/>
-        <v>-2.4249999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
@@ -25131,17 +25208,31 @@
         <v>16</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="D13" s="11">
+        <v>400</v>
+      </c>
+      <c r="E13" s="11">
+        <v>221</v>
+      </c>
+      <c r="F13" s="11">
+        <v>399</v>
+      </c>
+      <c r="G13" s="11">
+        <v>479</v>
+      </c>
+      <c r="H13" s="11">
+        <v>357</v>
+      </c>
+      <c r="I13" s="11">
+        <v>597</v>
+      </c>
       <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12"/>
+        <v>61.325000000000003</v>
+      </c>
+      <c r="K13" s="12">
+        <v>4</v>
+      </c>
       <c r="L13" s="13"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17" t="s">
@@ -25152,23 +25243,23 @@
         <v>400</v>
       </c>
       <c r="Q13" s="11">
-        <v>320</v>
+        <v>221</v>
       </c>
       <c r="R13" s="11">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="S13" s="11">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="T13" s="11">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="U13" s="11">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="V13" s="15">
         <f t="shared" si="1"/>
-        <v>64</v>
+        <v>61.325000000000003</v>
       </c>
       <c r="W13" s="12">
         <v>4</v>
@@ -25338,14 +25429,31 @@
         <v>45</v>
       </c>
       <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="12"/>
+      <c r="D18" s="11">
+        <v>28</v>
+      </c>
+      <c r="E18" s="11">
+        <v>24</v>
+      </c>
+      <c r="F18" s="11">
+        <v>34</v>
+      </c>
+      <c r="G18" s="11">
+        <v>23</v>
+      </c>
+      <c r="H18" s="11">
+        <v>12</v>
+      </c>
+      <c r="I18" s="11">
+        <v>40</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="K18" s="12">
+        <v>7</v>
+      </c>
       <c r="L18" s="13"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17" t="s">
@@ -25493,31 +25601,31 @@
       </c>
       <c r="D22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="E22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="F22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="G22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="H22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="I22" s="25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="J22" s="26">
         <f>SUM(C22:I22)</f>
-        <v>0</v>
+        <v>3761</v>
       </c>
       <c r="K22" s="28"/>
       <c r="M22" s="1"/>
@@ -25532,32 +25640,32 @@
       </c>
       <c r="Q22" s="25">
         <f t="shared" si="6"/>
-        <v>602</v>
+        <v>503</v>
       </c>
       <c r="R22" s="25">
         <f t="shared" si="6"/>
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="S22" s="25">
         <f t="shared" si="6"/>
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="T22" s="25">
         <f t="shared" si="6"/>
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="U22" s="25">
         <f t="shared" si="6"/>
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="V22" s="26">
         <f>SUM(O22:U22)</f>
-        <v>3845</v>
+        <v>3738</v>
       </c>
       <c r="W22" s="28"/>
       <c r="Y22" s="33">
         <f>SUM(Y8:Y21)</f>
-        <v>0</v>
+        <v>28.675000000000001</v>
       </c>
       <c r="Z22" s="34">
         <f>SUM(Z8:Z21)</f>
@@ -25565,7 +25673,7 @@
       </c>
       <c r="AA22" s="35">
         <f>SUM(AA8:AA21)</f>
-        <v>-28.675000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25579,35 +25687,35 @@
       </c>
       <c r="D23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.15</v>
       </c>
       <c r="E23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.574999999999999</v>
       </c>
       <c r="F23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="G23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.675000000000001</v>
       </c>
       <c r="H23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="I23" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20.774999999999999</v>
       </c>
       <c r="J23" s="22">
         <f>SUM(J8:J20)</f>
-        <v>0</v>
+        <v>94.025000000000006</v>
       </c>
       <c r="K23" s="22">
         <f>SUM(K8:K20)</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="20" t="s">
@@ -25623,32 +25731,32 @@
       </c>
       <c r="Q23" s="21">
         <f t="shared" si="8"/>
-        <v>15.05</v>
+        <v>12.574999999999999</v>
       </c>
       <c r="R23" s="21">
         <f t="shared" si="8"/>
-        <v>17.774999999999999</v>
+        <v>17.75</v>
       </c>
       <c r="S23" s="21">
         <f t="shared" si="8"/>
-        <v>15.7</v>
+        <v>15.675000000000001</v>
       </c>
       <c r="T23" s="21">
         <f t="shared" si="8"/>
-        <v>13.175000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="U23" s="21">
         <f t="shared" si="8"/>
-        <v>20.274999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="V23" s="22">
         <f t="shared" si="8"/>
-        <v>96.125</v>
+        <v>93.45</v>
       </c>
       <c r="W23" s="23"/>
       <c r="Y23" s="39">
         <f>Y22/40</f>
-        <v>0</v>
+        <v>0.71687500000000004</v>
       </c>
       <c r="Z23" s="40">
         <f>Z22/40</f>
@@ -25656,11 +25764,11 @@
       </c>
       <c r="AA23" s="41">
         <f>AA22/40</f>
-        <v>-0.71687500000000004</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Y3:AA4"/>
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="N2:V5"/>
@@ -25668,6 +25776,7 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="S6:U6"/>
+    <mergeCell ref="L1:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
